--- a/tame_output/ON/bt/strategyON_20240712.xlsx
+++ b/tame_output/ON/bt/strategyON_20240712.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>58.1%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.6%</t>
+          <t>-72.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.3%</t>
+          <t>110.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.2%</t>
+          <t>124.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-50.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.5%</t>
+          <t>-66.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>91.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.6%</t>
+          <t>457.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-493.0%</t>
+          <t>-493.7%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.6%</t>
+          <t>-36.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-152.3%</t>
+          <t>-152.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.2%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-28.9%</t>
+          <t>-29.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-124.8%</t>
+          <t>-125.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-150.1%</t>
+          <t>-159.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-45.2%</t>
+          <t>-50.9%</t>
         </is>
       </c>
     </row>
@@ -46171,10 +46171,10 @@
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.563307164238187</v>
+        <v>-3.325059991139006</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.188704783387815</v>
+        <v>1.284003652627488</v>
       </c>
       <c r="F1940" t="n">
         <v>0.3108149843130435</v>
@@ -46194,10 +46194,10 @@
         <v>2.617515458616743</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.529643618765906</v>
+        <v>-3.291396445666725</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.205301586796634</v>
+        <v>1.300600456036306</v>
       </c>
       <c r="F1941" t="n">
         <v>0.3444785297853253</v>
@@ -46217,10 +46217,10 @@
         <v>2.627687845048876</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.469790999562183</v>
+        <v>-3.231543826463001</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.239415020910255</v>
+        <v>1.334713890149928</v>
       </c>
       <c r="F1942" t="n">
         <v>0.3444785297853253</v>
@@ -46240,10 +46240,10 @@
         <v>2.622634115622736</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.383547536535805</v>
+        <v>-3.145300363436624</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.268858676694667</v>
+        <v>1.364157545934339</v>
       </c>
       <c r="F1943" t="n">
         <v>0.3444785297853253</v>
@@ -46263,10 +46263,10 @@
         <v>2.614409891067262</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.428854355934785</v>
+        <v>-3.190607182835604</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.2425117243796</v>
+        <v>1.337810593619273</v>
       </c>
       <c r="F1944" t="n">
         <v>0.3036683667760945</v>
@@ -46286,10 +46286,10 @@
         <v>2.614961764100363</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.457887460637087</v>
+        <v>-3.219640287537905</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.231450355531781</v>
+        <v>1.326749224771454</v>
       </c>
       <c r="F1945" t="n">
         <v>0.3036683667760945</v>
@@ -46309,10 +46309,10 @@
         <v>2.544234455991729</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.365076979186227</v>
+        <v>-3.126829806087046</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.197847240003491</v>
+        <v>1.293146109243163</v>
       </c>
       <c r="F1946" t="n">
         <v>0.3964788482269539</v>
@@ -46332,10 +46332,10 @@
         <v>2.54610793191633</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.409466448515655</v>
+        <v>-3.171219275416473</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.18196492819632</v>
+        <v>1.277263797435993</v>
       </c>
       <c r="F1947" t="n">
         <v>0.3520893788975262</v>
@@ -46355,10 +46355,10 @@
         <v>2.541183640428053</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.296795230279405</v>
+        <v>-3.058548057180223</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.222109124002543</v>
+        <v>1.317407993242216</v>
       </c>
       <c r="F1948" t="n">
         <v>0.4647605971337764</v>
@@ -46378,10 +46378,10 @@
         <v>2.54667493625872</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.184418229096732</v>
+        <v>-2.946171055997551</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.27255122030628</v>
+        <v>1.367850089545952</v>
       </c>
       <c r="F1949" t="n">
         <v>0.4647605971337764</v>
@@ -46401,10 +46401,10 @@
         <v>2.558172138027259</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.212198626998085</v>
+        <v>-2.973951453898904</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.272936262914278</v>
+        <v>1.36823513215395</v>
       </c>
       <c r="F1950" t="n">
         <v>0.4369801992324234</v>
@@ -46424,10 +46424,10 @@
         <v>2.396527858027912</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.295199908023364</v>
+        <v>-3.056952734924183</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.078091470504819</v>
+        <v>1.173390339744492</v>
       </c>
       <c r="F1951" t="n">
         <v>0.4184093147052496</v>
@@ -46447,10 +46447,10 @@
         <v>2.516677518747118</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.403813986466695</v>
+        <v>-3.165566813367514</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.154795499846692</v>
+        <v>1.250094369086365</v>
       </c>
       <c r="F1952" t="n">
         <v>0.4184093147052496</v>
@@ -46470,10 +46470,10 @@
         <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.368404948218553</v>
+        <v>-3.130157775119371</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.183472141248272</v>
+        <v>1.278771010487945</v>
       </c>
       <c r="F1953" t="n">
         <v>0.4184093147052496</v>
@@ -46493,10 +46493,10 @@
         <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.330021285660401</v>
+        <v>-3.09177411256122</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.196245047613901</v>
+        <v>1.291543916853574</v>
       </c>
       <c r="F1954" t="n">
         <v>0.4567929772634008</v>
@@ -46516,10 +46516,10 @@
         <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.152904955625235</v>
+        <v>-2.914657782526054</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.26382060847327</v>
+        <v>1.359119477712943</v>
       </c>
       <c r="F1955" t="n">
         <v>0.4567929772634008</v>
@@ -46539,10 +46539,10 @@
         <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.197997200458781</v>
+        <v>-2.9597500273596</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.246467102301765</v>
+        <v>1.341765971541438</v>
       </c>
       <c r="F1956" t="n">
         <v>0.394896934094011</v>
@@ -46562,10 +46562,10 @@
         <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.018621779220013</v>
+        <v>-2.780374606120832</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.312004246103687</v>
+        <v>1.407303115343359</v>
       </c>
       <c r="F1957" t="n">
         <v>0.5516736922647296</v>
@@ -46585,10 +46585,10 @@
         <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.06363599274062</v>
+        <v>-2.825388819641438</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.274806016027034</v>
+        <v>1.370104885266707</v>
       </c>
       <c r="F1958" t="n">
         <v>0.521324796950125</v>
@@ -46608,10 +46608,10 @@
         <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.330640503013055</v>
+        <v>-3.092393329913874</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.173695774257006</v>
+        <v>1.268994643496678</v>
       </c>
       <c r="F1959" t="n">
         <v>0.3269617589071764</v>
@@ -46631,10 +46631,10 @@
         <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.431838284450228</v>
+        <v>-3.193591111351046</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.132420583578638</v>
+        <v>1.22771945281831</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2585529453618572</v>
@@ -46654,10 +46654,10 @@
         <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.425327317835915</v>
+        <v>-3.187080144736734</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.13262493177868</v>
+        <v>1.227923801018352</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2585529453618572</v>
@@ -46677,10 +46677,10 @@
         <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.406289190128618</v>
+        <v>-3.168042017029436</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.136764902069843</v>
+        <v>1.232063771309516</v>
       </c>
       <c r="F1962" t="n">
         <v>0.2003693340306627</v>
@@ -46700,10 +46700,10 @@
         <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.437415821279236</v>
+        <v>-3.199168648180054</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.301896118548277</v>
+        <v>1.397194987787949</v>
       </c>
       <c r="F1963" t="n">
         <v>0.2003693340306627</v>
@@ -46723,10 +46723,10 @@
         <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.451282582613153</v>
+        <v>-3.213035409513972</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.297182743000843</v>
+        <v>1.392481612240516</v>
       </c>
       <c r="F1964" t="n">
         <v>0.1625114172968398</v>
@@ -46746,10 +46746,10 @@
         <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.406478411073223</v>
+        <v>-3.168231237974042</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.321112942013741</v>
+        <v>1.416411811253414</v>
       </c>
       <c r="F1965" t="n">
         <v>0.1625114172968398</v>
@@ -46769,10 +46769,10 @@
         <v>2.582010952033977</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.258735440838221</v>
+        <v>-3.02048826773904</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.278160351384942</v>
+        <v>1.373459220624614</v>
       </c>
       <c r="F1966" t="n">
         <v>0.3303187745317229</v>
@@ -46792,10 +46792,10 @@
         <v>2.584804573565458</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.360750123369442</v>
+        <v>-3.122502950270261</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.240148099903934</v>
+        <v>1.335446969143607</v>
       </c>
       <c r="F1967" t="n">
         <v>0.3303187745317229</v>
@@ -46815,10 +46815,10 @@
         <v>2.585466921957117</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.354597417316658</v>
+        <v>-3.116350244217476</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.243271530716706</v>
+        <v>1.338570399956379</v>
       </c>
       <c r="F1968" t="n">
         <v>0.3364714805845072</v>
@@ -46838,10 +46838,10 @@
         <v>2.584547398697227</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.371406715467159</v>
+        <v>-3.133159542367978</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.235628288196616</v>
+        <v>1.330927157436289</v>
       </c>
       <c r="F1969" t="n">
         <v>0.3196621824340056</v>
@@ -46861,10 +46861,10 @@
         <v>2.650882952494048</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.309108716691037</v>
+        <v>-3.070861543591856</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.326883041503886</v>
+        <v>1.422181910743558</v>
       </c>
       <c r="F1970" t="n">
         <v>0.3196621824340056</v>
@@ -46884,10 +46884,10 @@
         <v>2.453174954208175</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.107318519025879</v>
+        <v>-2.869071345926698</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.209891122284076</v>
+        <v>1.305189991523749</v>
       </c>
       <c r="F1971" t="n">
         <v>0.51768037460316</v>
@@ -46907,10 +46907,10 @@
         <v>2.52346518653035</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.942505515947032</v>
+        <v>-2.704258342847851</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.34610655583779</v>
+        <v>1.441405425077463</v>
       </c>
       <c r="F1972" t="n">
         <v>0.6824933776820069</v>
@@ -46930,10 +46930,10 @@
         <v>2.538092922646394</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.040246060572007</v>
+        <v>-2.801998887472825</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.321638074103844</v>
+        <v>1.416936943343516</v>
       </c>
       <c r="F1973" t="n">
         <v>0.6666040995490268</v>
@@ -46953,10 +46953,10 @@
         <v>2.536628903471065</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.216583820694936</v>
+        <v>-2.978336647595754</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.249638950879344</v>
+        <v>1.344937820119016</v>
       </c>
       <c r="F1974" t="n">
         <v>0.4902663394260973</v>
@@ -46976,10 +46976,10 @@
         <v>2.535120521510994</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.140161774263009</v>
+        <v>-2.901914601163828</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.278699387492043</v>
+        <v>1.373998256731716</v>
       </c>
       <c r="F1975" t="n">
         <v>0.4902663394260973</v>
@@ -46999,10 +46999,10 @@
         <v>2.53498338894643</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.095788642624441</v>
+        <v>-2.857541469525259</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.296311507582907</v>
+        <v>1.391610376822579</v>
       </c>
       <c r="F1976" t="n">
         <v>0.5346394710646659</v>
@@ -47022,10 +47022,10 @@
         <v>2.529377183085021</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.972954421737273</v>
+        <v>-2.734707248638092</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.339838990076364</v>
+        <v>1.435137859316037</v>
       </c>
       <c r="F1977" t="n">
         <v>0.5346394710646659</v>
@@ -47045,10 +47045,10 @@
         <v>2.535758940112825</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.925298691176217</v>
+        <v>-2.687051518077036</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.365283039328591</v>
+        <v>1.460581908568264</v>
       </c>
       <c r="F1978" t="n">
         <v>0.5822952016257216</v>
@@ -47068,10 +47068,10 @@
         <v>2.54065131348755</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.824780532677463</v>
+        <v>-2.586533359578281</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.410382676102818</v>
+        <v>1.505681545342491</v>
       </c>
       <c r="F1979" t="n">
         <v>0.6828133601244761</v>
@@ -47091,10 +47091,10 @@
         <v>2.527405985963422</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.885447123079852</v>
+        <v>-2.64719994998067</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.372870712417734</v>
+        <v>1.468169581657407</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6011150434059425</v>
@@ -47114,10 +47114,10 @@
         <v>2.531503688574051</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.840608721471454</v>
+        <v>-2.602361548372272</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.394903775671722</v>
+        <v>1.490202644911395</v>
       </c>
       <c r="F1981" t="n">
         <v>0.6056584763508119</v>
@@ -47137,10 +47137,10 @@
         <v>2.535664628205129</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.941367357228452</v>
+        <v>-2.703120184129271</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.358761261000001</v>
+        <v>1.454060130239673</v>
       </c>
       <c r="F1982" t="n">
         <v>0.5168329076238065</v>
@@ -47160,10 +47160,10 @@
         <v>2.541544230732966</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.897164520142552</v>
+        <v>-2.65891734704337</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.382321998362198</v>
+        <v>1.477620867601871</v>
       </c>
       <c r="F1983" t="n">
         <v>0.561035744709707</v>
@@ -47183,10 +47183,10 @@
         <v>2.539954231202214</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.934143547805995</v>
+        <v>-2.695896374706813</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.365940387766069</v>
+        <v>1.461239257005741</v>
       </c>
       <c r="F1984" t="n">
         <v>0.5980096465010375</v>
@@ -47206,10 +47206,10 @@
         <v>2.591201996385253</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.775852130266723</v>
+        <v>-2.537604957167541</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.480504719964817</v>
+        <v>1.575803589204489</v>
       </c>
       <c r="F1985" t="n">
         <v>0.5980096465010375</v>
@@ -47229,10 +47229,10 @@
         <v>2.589642700979506</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.568210126632247</v>
+        <v>-2.329962953533065</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.562002226012861</v>
+        <v>1.657301095252533</v>
       </c>
       <c r="F1986" t="n">
         <v>0.8056516501355137</v>
@@ -47252,10 +47252,10 @@
         <v>2.584590929217776</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.517178033909719</v>
+        <v>-2.278930860810537</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.577363291340142</v>
+        <v>1.672662160579814</v>
       </c>
       <c r="F1987" t="n">
         <v>0.8566837428580416</v>
@@ -47275,10 +47275,10 @@
         <v>2.601778333310481</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.451953852782513</v>
+        <v>-2.213706679683331</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.620640367883729</v>
+        <v>1.715939237123402</v>
       </c>
       <c r="F1988" t="n">
         <v>0.9219079239852472</v>
@@ -47298,10 +47298,10 @@
         <v>2.597739305609762</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.414526832711379</v>
+        <v>-2.176279659612197</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.631572148211463</v>
+        <v>1.726871017451136</v>
       </c>
       <c r="F1989" t="n">
         <v>0.9271594620144289</v>
@@ -47321,10 +47321,10 @@
         <v>2.598996097941002</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.434638488746087</v>
+        <v>-2.196391315646906</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.62478427812882</v>
+        <v>1.720083147368493</v>
       </c>
       <c r="F1990" t="n">
         <v>0.9381868070118481</v>
@@ -47344,10 +47344,10 @@
         <v>2.759553868962213</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.380893674318882</v>
+        <v>-2.142646501219701</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.806839974920913</v>
+        <v>1.902138844160585</v>
       </c>
       <c r="F1991" t="n">
         <v>0.9482501164523101</v>
@@ -47367,10 +47367,10 @@
         <v>2.87966677818003</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.35710210571274</v>
+        <v>-2.118854932613559</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.936469511581187</v>
+        <v>2.031768380820859</v>
       </c>
       <c r="F1992" t="n">
         <v>0.9720416850584523</v>
@@ -47390,10 +47390,10 @@
         <v>2.871374754193889</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.331018021448932</v>
+        <v>-2.092770848349751</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.938611121300569</v>
+        <v>2.033909990540241</v>
       </c>
       <c r="F1993" t="n">
         <v>0.9720416850584523</v>
@@ -47413,10 +47413,10 @@
         <v>2.869567949777668</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.252886840599985</v>
+        <v>-2.014639667500804</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.968056789223927</v>
+        <v>2.0633556584636</v>
       </c>
       <c r="F1994" t="n">
         <v>1.046218495942137</v>
@@ -47436,10 +47436,10 @@
         <v>2.88712235550446</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.243994379206702</v>
+        <v>-2.005747206107521</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.989168179508032</v>
+        <v>2.084467048747705</v>
       </c>
       <c r="F1995" t="n">
         <v>1.046218495942137</v>
@@ -47459,10 +47459,10 @@
         <v>2.878977402909044</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.41247049617658</v>
+        <v>-2.174223323077398</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.913632780124665</v>
+        <v>2.008931649364337</v>
       </c>
       <c r="F1996" t="n">
         <v>1.018270660225556</v>
@@ -47482,10 +47482,10 @@
         <v>2.860247100096906</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.714670967314997</v>
+        <v>-1.476423794215815</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.174022288857159</v>
+        <v>2.269321158096832</v>
       </c>
       <c r="F1997" t="n">
         <v>0.9479226008551453</v>
@@ -47505,10 +47505,10 @@
         <v>2.85091112259381</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.691949863631844</v>
+        <v>-1.453702690532662</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.173774752827325</v>
+        <v>2.269073622066998</v>
       </c>
       <c r="F1998" t="n">
         <v>0.9479226008551453</v>
@@ -47528,10 +47528,10 @@
         <v>3.009817248444979</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.690224820341801</v>
+        <v>-1.451977647242619</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.333370895994512</v>
+        <v>2.428669765234185</v>
       </c>
       <c r="F1999" t="n">
         <v>0.9496476441451891</v>
@@ -47551,10 +47551,10 @@
         <v>3.046895070938626</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.845005827120056</v>
+        <v>-1.606758654020874</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.308536315776856</v>
+        <v>2.403835185016529</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9162799700907129</v>
@@ -47574,10 +47574,10 @@
         <v>3.043570426928171</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.793570493735396</v>
+        <v>-1.555323320636214</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.325785805120265</v>
+        <v>2.421084674359938</v>
       </c>
       <c r="F2001" t="n">
         <v>0.9677153034753726</v>
@@ -47597,10 +47597,10 @@
         <v>3.053576580572912</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.766619269408908</v>
+        <v>-1.528372096309726</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.346572448495602</v>
+        <v>2.441871317735274</v>
       </c>
       <c r="F2002" t="n">
         <v>0.9825956495030918</v>
@@ -47620,10 +47620,10 @@
         <v>3.237679712717872</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.902572277465225</v>
+        <v>-1.664325104366043</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.476294377418035</v>
+        <v>2.571593246657708</v>
       </c>
       <c r="F2003" t="n">
         <v>0.9825956495030918</v>
@@ -47643,10 +47643,10 @@
         <v>3.229796407620865</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.924980395270097</v>
+        <v>-1.686733222170915</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.45944782519908</v>
+        <v>2.554746694438752</v>
       </c>
       <c r="F2004" t="n">
         <v>0.9825956495030918</v>
@@ -47666,10 +47666,10 @@
         <v>3.231850407170503</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.072986162749496</v>
+        <v>-1.834738989650314</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.402299517756957</v>
+        <v>2.49759838699663</v>
       </c>
       <c r="F2005" t="n">
         <v>0.8958686406395503</v>
@@ -47689,10 +47689,10 @@
         <v>3.28810412489235</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.082427088638026</v>
+        <v>-1.844179915538844</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.454776865123392</v>
+        <v>2.550075734363065</v>
       </c>
       <c r="F2006" t="n">
         <v>1.018295758182942</v>
@@ -47712,10 +47712,10 @@
         <v>3.290995219437651</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.081140325098469</v>
+        <v>-1.842893151999287</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.458182665084516</v>
+        <v>2.553481534324189</v>
       </c>
       <c r="F2007" t="n">
         <v>1.019582521722498</v>
@@ -47735,10 +47735,10 @@
         <v>3.289107032331426</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.082697379087761</v>
+        <v>-1.844450205988578</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.455671656382575</v>
+        <v>2.550970525622247</v>
       </c>
       <c r="F2008" t="n">
         <v>1.019582521722498</v>
@@ -47758,10 +47758,10 @@
         <v>3.283927261934288</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.089969264611225</v>
+        <v>-1.851722091512043</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.447583131776051</v>
+        <v>2.542882001015724</v>
       </c>
       <c r="F2009" t="n">
         <v>1.012310636199033</v>
@@ -47781,10 +47781,10 @@
         <v>3.282361272144441</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.088128245552974</v>
+        <v>-1.849881072453792</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.446753549609504</v>
+        <v>2.542052418849177</v>
       </c>
       <c r="F2010" t="n">
         <v>1.013578862870502</v>
@@ -47804,10 +47804,10 @@
         <v>3.295434679010359</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.095036951052655</v>
+        <v>-1.856789777953472</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.45706347427555</v>
+        <v>2.552362343515223</v>
       </c>
       <c r="F2011" t="n">
         <v>1.013578862870502</v>
@@ -47827,10 +47827,10 @@
         <v>3.295434679010359</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.096598593867514</v>
+        <v>-1.858351420768332</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.456438817149606</v>
+        <v>2.551737686389279</v>
       </c>
       <c r="F2012" t="n">
         <v>1.013578862870502</v>
@@ -47850,10 +47850,10 @@
         <v>3.293958720137361</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.124499380976987</v>
+        <v>-1.886252207877805</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.443802543432819</v>
+        <v>2.539101412672492</v>
       </c>
       <c r="F2013" t="n">
         <v>0.9789819387275672</v>
@@ -47873,10 +47873,10 @@
         <v>3.29072316411456</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.127532378489661</v>
+        <v>-1.889285205390479</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.439353788404948</v>
+        <v>2.534652657644621</v>
       </c>
       <c r="F2014" t="n">
         <v>0.9759489412148934</v>
@@ -47896,10 +47896,10 @@
         <v>3.357429123705064</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.147593699766168</v>
+        <v>-1.909346526666986</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.498035219484849</v>
+        <v>2.593334088724522</v>
       </c>
       <c r="F2015" t="n">
         <v>0.9558876199383863</v>
@@ -47919,10 +47919,10 @@
         <v>3.497740842706911</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.404314517760992</v>
+        <v>-2.16606734466181</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.535658611288767</v>
+        <v>2.63095748052844</v>
       </c>
       <c r="F2016" t="n">
         <v>0.8474730457945715</v>
@@ -47942,10 +47942,10 @@
         <v>3.566721111852551</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.558300935537133</v>
+        <v>-2.320053762437951</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.54304431332395</v>
+        <v>2.638343182563623</v>
       </c>
       <c r="F2017" t="n">
         <v>0.8474730457945715</v>
@@ -47965,10 +47965,10 @@
         <v>3.552772313972671</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.507779031709467</v>
+        <v>-2.269531858610285</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.549304276975137</v>
+        <v>2.64460314621481</v>
       </c>
       <c r="F2018" t="n">
         <v>0.8474730457945715</v>
@@ -47988,10 +47988,10 @@
         <v>3.564642803028085</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.760254185717192</v>
+        <v>-2.522007012618009</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.460184704427462</v>
+        <v>2.555483573667135</v>
       </c>
       <c r="F2019" t="n">
         <v>0.8474730457945715</v>
@@ -48011,10 +48011,10 @@
         <v>3.565853337547029</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.0297269876389</v>
+        <v>-2.791479814539717</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.353606118177722</v>
+        <v>2.448904987417395</v>
       </c>
       <c r="F2020" t="n">
         <v>0.8474730457945715</v>
@@ -48034,10 +48034,10 @@
         <v>3.569975079774351</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.187271059368341</v>
+        <v>-2.949023886269158</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.294710231713267</v>
+        <v>2.39000910095294</v>
       </c>
       <c r="F2021" t="n">
         <v>0.7805712406542971</v>
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.745931726308571</v>
+        <v>3.861339765497009</v>
       </c>
       <c r="C2022" t="n">
         <v>3.56505293251054</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.314353375922315</v>
+        <v>-3.320886454498555</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.238955157827867</v>
+        <v>2.236341926397371</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.7388436116152308</v>
+        <v>0.6431961534646777</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.008359099479678</v>
+        <v>3.950970624589347</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240712.xlsx
+++ b/tame_output/ON/bt/strategyON_20240712.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>20.1%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.1%</t>
+          <t>-71.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.3%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.0%</t>
+          <t>122.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.9%</t>
+          <t>-50.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.3%</t>
+          <t>-67.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.5%</t>
+          <t>452.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-493.7%</t>
+          <t>-495.8%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-36.3%</t>
+          <t>-35.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-152.6%</t>
+          <t>-153.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-11.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-29.5%</t>
+          <t>-28.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>125.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-125.4%</t>
+          <t>-124.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-159.7%</t>
+          <t>-150.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>77.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-50.9%</t>
+          <t>-45.1%</t>
         </is>
       </c>
     </row>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611567</v>
+        <v>3.768951674611565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955326</v>
+        <v>3.728577929955324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311944</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097239</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017767</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839721</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.595175067534991</v>
+        <v>-7.621579320495826</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1126898988876692</v>
+        <v>0.1021281977033355</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.585066311048055</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388724</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.554990769168801</v>
+        <v>-7.581395022129636</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1291072421219868</v>
+        <v>0.118545540937653</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.544882012681864</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.85616175162647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.391590898229438</v>
+        <v>-7.417995151190273</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1938340117184887</v>
+        <v>0.1832723105341549</v>
       </c>
       <c r="F1902" t="n">
         <v>-1.381482141742502</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.78733042929181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.15810967599984</v>
+        <v>-7.184513928960675</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2951509294481807</v>
+        <v>0.2845892282638465</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.148000919512903</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.801637122785785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.008443284992325</v>
+        <v>-7.034847537953159</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3521252755382274</v>
+        <v>0.3415635743538936</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.055097428270367</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.763182248390426</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.876167811361438</v>
+        <v>-6.902572064322273</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4004029517376089</v>
+        <v>0.3898412505532751</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.9228219546394807</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.78471879410595</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.720429478801696</v>
+        <v>-6.746833731762531</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4655133454491427</v>
+        <v>0.4549516442648085</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.7670836220797391</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960984</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.471429680118115</v>
+        <v>-6.49783393307895</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5780196061462335</v>
+        <v>0.5674579049618997</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.7670836220797391</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.57701966989122</v>
+        <v>-6.603423922852055</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4078076806377733</v>
+        <v>0.3972459794534391</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.8726736118528435</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.595754572009817</v>
+        <v>-6.622158824970652</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4488580616674209</v>
+        <v>0.4382963604830867</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.8782696215129748</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.447814530602217</v>
+        <v>-6.474218783563052</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3881551555422931</v>
+        <v>0.3775934543579589</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.8579487056044173</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.394845008348229</v>
+        <v>-6.421249261309064</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4006289781904102</v>
+        <v>0.390067277006076</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.8049791833504284</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.351296601577539</v>
+        <v>-6.377700854538373</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4110877288035932</v>
+        <v>0.400526027619259</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.8049791833504284</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.10914820812368</v>
+        <v>-6.135552461084515</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5224094405662796</v>
+        <v>0.5118477393819454</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.8049791833504284</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.000889071001159</v>
+        <v>-6.027293323961993</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5602452158744833</v>
+        <v>0.5496835146901491</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.8049791833504284</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.877597936184028</v>
+        <v>-5.904002189144863</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6070597638119124</v>
+        <v>0.5964980626275787</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.6816880485332979</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.856448737280584</v>
+        <v>-5.882852990241419</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6232204216106152</v>
+        <v>0.612658720426281</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.6605388496298545</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.61268329529714</v>
+        <v>-5.639087548257975</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7165073067510432</v>
+        <v>0.7059456055667095</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.6605388496298545</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.510920475019845</v>
+        <v>-5.53732472798068</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7593367487819775</v>
+        <v>0.7487750475976434</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.6473197812374258</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.261070081070771</v>
+        <v>-5.287474334031605</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8520189813453092</v>
+        <v>0.8414572801609754</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.6473197812374258</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.085177988603338</v>
+        <v>-5.111582241564173</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9259749418529313</v>
+        <v>0.9154132406685971</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.6473197812374258</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.913731525580874</v>
+        <v>-4.94013577854171</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.00788103311647</v>
+        <v>0.9973193319321361</v>
       </c>
       <c r="F1921" t="n">
         <v>-0.4758733182149627</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.839441959842535</v>
+        <v>-4.865846212803371</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.036617337028103</v>
+        <v>1.026055635843769</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.4015837524766234</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.775806217608601</v>
+        <v>-4.802210470569436</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.066766434975994</v>
+        <v>1.05620473379166</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.3379480102426889</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.664379458282681</v>
+        <v>-4.690783711243516</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.092531397490158</v>
+        <v>1.081969696305823</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.3379480102426889</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.79769488424229</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.42394896147782</v>
+        <v>-4.450353214438656</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.190446672836979</v>
+        <v>1.179884971652645</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.09751751343782861</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.351706393306626</v>
+        <v>-4.378110646267461</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.223273013940277</v>
+        <v>1.212711312755943</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.09751751343782861</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.298708071025238</v>
+        <v>-4.325112323986073</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.245150926770172</v>
+        <v>1.234589225585838</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.04218125443588977</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502336</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.189903185545511</v>
+        <v>-4.216307438506346</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.285670952182057</v>
+        <v>1.275109250997722</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.04218125443588977</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.9698823875085</v>
+        <v>-3.996286640469335</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.375258308407475</v>
+        <v>1.364696607223141</v>
       </c>
       <c r="F1929" t="n">
         <v>0.09903859063209047</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.837014698445222</v>
+        <v>-3.863418951406057</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.44429956683461</v>
+        <v>1.433737865650276</v>
       </c>
       <c r="F1930" t="n">
         <v>0.09903859063209047</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.716841615080723</v>
+        <v>-3.743245868041559</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.493514644620711</v>
+        <v>1.482952943436377</v>
       </c>
       <c r="F1931" t="n">
         <v>0.2192116739965894</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.572169469980985</v>
+        <v>-3.598573722941821</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.561471605222046</v>
+        <v>1.550909904037712</v>
       </c>
       <c r="F1932" t="n">
         <v>0.3638838190963268</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.7358392229421</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.632044297338678</v>
+        <v>-3.658448550299513</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.523559165680395</v>
+        <v>1.512997464496061</v>
       </c>
       <c r="F1933" t="n">
         <v>0.3040089917386347</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.51222406642784</v>
+        <v>-3.538628319388676</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.586776427278938</v>
+        <v>1.576214726094604</v>
       </c>
       <c r="F1934" t="n">
         <v>0.3040089917386347</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430692</v>
+        <v>3.72914639843069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.514693772889646</v>
+        <v>-3.541098025850482</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.493432744016657</v>
+        <v>1.482871042832323</v>
       </c>
       <c r="F1935" t="n">
         <v>0.3015392852768286</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.583063959213656</v>
+        <v>-3.609468212174492</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.385346530972355</v>
+        <v>1.374784829788021</v>
       </c>
       <c r="F1936" t="n">
         <v>0.3108149843130435</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.596852012060703</v>
+        <v>-3.623256265021539</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.370268018465428</v>
+        <v>1.359706317281093</v>
       </c>
       <c r="F1937" t="n">
         <v>0.3108149843130435</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.627845171389408</v>
+        <v>-3.654249424350244</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.182580319774332</v>
+        <v>1.172018618589998</v>
       </c>
       <c r="F1938" t="n">
         <v>0.3108149843130435</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.452370911596939</v>
+        <v>-3.478775164557775</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.257337255683108</v>
+        <v>1.246775554498774</v>
       </c>
       <c r="F1939" t="n">
         <v>0.3108149843130435</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.325059991139006</v>
+        <v>-3.589711417199023</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.284003652627488</v>
+        <v>1.178143082203481</v>
       </c>
       <c r="F1940" t="n">
         <v>0.3108149843130435</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.617515458616743</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.291396445666725</v>
+        <v>-3.556047871726741</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.300600456036306</v>
+        <v>1.194739885612299</v>
       </c>
       <c r="F1941" t="n">
         <v>0.3444785297853253</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.627687845048876</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.231543826463001</v>
+        <v>-3.496195252523018</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.334713890149928</v>
+        <v>1.228853319725921</v>
       </c>
       <c r="F1942" t="n">
         <v>0.3444785297853253</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.622634115622736</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.145300363436624</v>
+        <v>-3.409951789496641</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.364157545934339</v>
+        <v>1.258296975510332</v>
       </c>
       <c r="F1943" t="n">
         <v>0.3444785297853253</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.614409891067262</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.190607182835604</v>
+        <v>-3.455258608895621</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.337810593619273</v>
+        <v>1.231950023195266</v>
       </c>
       <c r="F1944" t="n">
         <v>0.3036683667760945</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.614961764100363</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.219640287537905</v>
+        <v>-3.484291713597922</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.326749224771454</v>
+        <v>1.220888654347447</v>
       </c>
       <c r="F1945" t="n">
         <v>0.3036683667760945</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.544234455991729</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.126829806087046</v>
+        <v>-3.391481232147063</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.293146109243163</v>
+        <v>1.187285538819156</v>
       </c>
       <c r="F1946" t="n">
         <v>0.3964788482269539</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.54610793191633</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.171219275416473</v>
+        <v>-3.435870701476491</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.277263797435993</v>
+        <v>1.171403227011986</v>
       </c>
       <c r="F1947" t="n">
         <v>0.3520893788975262</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.541183640428053</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.058548057180223</v>
+        <v>-3.323199483240241</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.317407993242216</v>
+        <v>1.211547422818209</v>
       </c>
       <c r="F1948" t="n">
         <v>0.4647605971337764</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.54667493625872</v>
       </c>
       <c r="D1949" t="n">
-        <v>-2.946171055997551</v>
+        <v>-3.210822482057568</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.367850089545952</v>
+        <v>1.261989519121945</v>
       </c>
       <c r="F1949" t="n">
         <v>0.4647605971337764</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.558172138027259</v>
       </c>
       <c r="D1950" t="n">
-        <v>-2.973951453898904</v>
+        <v>-3.238602879958921</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.36823513215395</v>
+        <v>1.262374561729943</v>
       </c>
       <c r="F1950" t="n">
         <v>0.4369801992324234</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.396527858027912</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.056952734924183</v>
+        <v>-3.3216041609842</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.173390339744492</v>
+        <v>1.067529769320485</v>
       </c>
       <c r="F1951" t="n">
         <v>0.4184093147052496</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.516677518747118</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.165566813367514</v>
+        <v>-3.430218239427531</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.250094369086365</v>
+        <v>1.144233798662358</v>
       </c>
       <c r="F1952" t="n">
         <v>0.4184093147052496</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.130157775119371</v>
+        <v>-3.394809201179388</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.278771010487945</v>
+        <v>1.172910440063938</v>
       </c>
       <c r="F1953" t="n">
         <v>0.4184093147052496</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913426</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.09177411256122</v>
+        <v>-3.356425538621237</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.291543916853574</v>
+        <v>1.185683346429567</v>
       </c>
       <c r="F1954" t="n">
         <v>0.4567929772634008</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-2.914657782526054</v>
+        <v>-3.179309208586071</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.359119477712943</v>
+        <v>1.253258907288936</v>
       </c>
       <c r="F1955" t="n">
         <v>0.4567929772634008</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-2.9597500273596</v>
+        <v>-3.224401453419617</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.341765971541438</v>
+        <v>1.235905401117431</v>
       </c>
       <c r="F1956" t="n">
         <v>0.394896934094011</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-2.780374606120832</v>
+        <v>-3.045026032180849</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.407303115343359</v>
+        <v>1.301442544919352</v>
       </c>
       <c r="F1957" t="n">
         <v>0.5516736922647296</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-2.825388819641438</v>
+        <v>-3.090040245701455</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.370104885266707</v>
+        <v>1.2642443148427</v>
       </c>
       <c r="F1958" t="n">
         <v>0.521324796950125</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.092393329913874</v>
+        <v>-3.357044755973891</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.268994643496678</v>
+        <v>1.163134073072671</v>
       </c>
       <c r="F1959" t="n">
         <v>0.3269617589071764</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.193591111351046</v>
+        <v>-3.458242537411063</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.22771945281831</v>
+        <v>1.121858882394303</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2585529453618572</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.187080144736734</v>
+        <v>-3.451731570796751</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.227923801018352</v>
+        <v>1.122063230594345</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2585529453618572</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.168042017029436</v>
+        <v>-3.432693443089454</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.232063771309516</v>
+        <v>1.126203200885509</v>
       </c>
       <c r="F1962" t="n">
         <v>0.2003693340306627</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131249</v>
       </c>
       <c r="C1963" t="n">
         <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.199168648180054</v>
+        <v>-3.463820074240072</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.397194987787949</v>
+        <v>1.291334417363942</v>
       </c>
       <c r="F1963" t="n">
         <v>0.2003693340306627</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.213035409513972</v>
+        <v>-3.477686835573989</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.392481612240516</v>
+        <v>1.286621041816509</v>
       </c>
       <c r="F1964" t="n">
         <v>0.1625114172968398</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.168231237974042</v>
+        <v>-3.432882664034059</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.416411811253414</v>
+        <v>1.310551240829407</v>
       </c>
       <c r="F1965" t="n">
         <v>0.1625114172968398</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.582010952033977</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.02048826773904</v>
+        <v>-3.285139693799057</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.373459220624614</v>
+        <v>1.267598650200607</v>
       </c>
       <c r="F1966" t="n">
         <v>0.3303187745317229</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.584804573565458</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.122502950270261</v>
+        <v>-3.387154376330278</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.335446969143607</v>
+        <v>1.2295863987196</v>
       </c>
       <c r="F1967" t="n">
         <v>0.3303187745317229</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
         <v>2.585466921957117</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.116350244217476</v>
+        <v>-3.381001670277493</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.338570399956379</v>
+        <v>1.232709829532372</v>
       </c>
       <c r="F1968" t="n">
         <v>0.3364714805845072</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.584547398697227</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.133159542367978</v>
+        <v>-3.397810968427995</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.330927157436289</v>
+        <v>1.225066587012282</v>
       </c>
       <c r="F1969" t="n">
         <v>0.3196621824340056</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.650882952494048</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.070861543591856</v>
+        <v>-3.335512969651873</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.422181910743558</v>
+        <v>1.316321340319551</v>
       </c>
       <c r="F1970" t="n">
         <v>0.3196621824340056</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.453174954208175</v>
       </c>
       <c r="D1971" t="n">
-        <v>-2.869071345926698</v>
+        <v>-3.133722771986715</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.305189991523749</v>
+        <v>1.199329421099742</v>
       </c>
       <c r="F1971" t="n">
         <v>0.51768037460316</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.52346518653035</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.704258342847851</v>
+        <v>-2.968909768907868</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.441405425077463</v>
+        <v>1.335544854653456</v>
       </c>
       <c r="F1972" t="n">
         <v>0.6824933776820069</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.538092922646394</v>
       </c>
       <c r="D1973" t="n">
-        <v>-2.801998887472825</v>
+        <v>-3.066650313532842</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.416936943343516</v>
+        <v>1.311076372919509</v>
       </c>
       <c r="F1973" t="n">
         <v>0.6666040995490268</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.536628903471065</v>
       </c>
       <c r="D1974" t="n">
-        <v>-2.978336647595754</v>
+        <v>-3.242988073655772</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.344937820119016</v>
+        <v>1.23907724969501</v>
       </c>
       <c r="F1974" t="n">
         <v>0.4902663394260973</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.535120521510994</v>
       </c>
       <c r="D1975" t="n">
-        <v>-2.901914601163828</v>
+        <v>-3.166566027223845</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.373998256731716</v>
+        <v>1.268137686307709</v>
       </c>
       <c r="F1975" t="n">
         <v>0.4902663394260973</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
         <v>2.53498338894643</v>
       </c>
       <c r="D1976" t="n">
-        <v>-2.857541469525259</v>
+        <v>-3.122192895585276</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.391610376822579</v>
+        <v>1.285749806398572</v>
       </c>
       <c r="F1976" t="n">
         <v>0.5346394710646659</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
         <v>2.529377183085021</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.734707248638092</v>
+        <v>-2.999358674698109</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.435137859316037</v>
+        <v>1.32927728889203</v>
       </c>
       <c r="F1977" t="n">
         <v>0.5346394710646659</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
         <v>2.535758940112825</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.687051518077036</v>
+        <v>-2.951702944137053</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.460581908568264</v>
+        <v>1.354721338144257</v>
       </c>
       <c r="F1978" t="n">
         <v>0.5822952016257216</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
         <v>2.54065131348755</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.586533359578281</v>
+        <v>-2.851184785638298</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.505681545342491</v>
+        <v>1.399820974918484</v>
       </c>
       <c r="F1979" t="n">
         <v>0.6828133601244761</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.82880887755729</v>
       </c>
       <c r="C1980" t="n">
         <v>2.527405985963422</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.64719994998067</v>
+        <v>-2.911851376040687</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.468169581657407</v>
+        <v>1.3623090112334</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6011150434059425</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.531503688574051</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.602361548372272</v>
+        <v>-2.867012974432289</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.490202644911395</v>
+        <v>1.384342074487388</v>
       </c>
       <c r="F1981" t="n">
         <v>0.6056584763508119</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.81793235491705</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.535664628205129</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.703120184129271</v>
+        <v>-2.967771610189288</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.454060130239673</v>
+        <v>1.348199559815667</v>
       </c>
       <c r="F1982" t="n">
         <v>0.5168329076238065</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405957</v>
       </c>
       <c r="C1983" t="n">
         <v>2.541544230732966</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.65891734704337</v>
+        <v>-2.923568773103387</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.477620867601871</v>
+        <v>1.371760297177864</v>
       </c>
       <c r="F1983" t="n">
         <v>0.561035744709707</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.539954231202214</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.695896374706813</v>
+        <v>-2.960547800766831</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.461239257005741</v>
+        <v>1.355378686581734</v>
       </c>
       <c r="F1984" t="n">
         <v>0.5980096465010375</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.591201996385253</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.537604957167541</v>
+        <v>-2.802256383227558</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.575803589204489</v>
+        <v>1.469943018780483</v>
       </c>
       <c r="F1985" t="n">
         <v>0.5980096465010375</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
         <v>2.589642700979506</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.329962953533065</v>
+        <v>-2.594614379593082</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.657301095252533</v>
+        <v>1.551440524828526</v>
       </c>
       <c r="F1986" t="n">
         <v>0.8056516501355137</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
         <v>2.584590929217776</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.278930860810537</v>
+        <v>-2.543582286870554</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.672662160579814</v>
+        <v>1.566801590155807</v>
       </c>
       <c r="F1987" t="n">
         <v>0.8566837428580416</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.84254736040485</v>
       </c>
       <c r="C1988" t="n">
         <v>2.601778333310481</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.213706679683331</v>
+        <v>-2.478358105743348</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.715939237123402</v>
+        <v>1.610078666699395</v>
       </c>
       <c r="F1988" t="n">
         <v>0.9219079239852472</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
         <v>2.597739305609762</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.176279659612197</v>
+        <v>-2.440931085672215</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.726871017451136</v>
+        <v>1.621010447027129</v>
       </c>
       <c r="F1989" t="n">
         <v>0.9271594620144289</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992657</v>
       </c>
       <c r="C1990" t="n">
         <v>2.598996097941002</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.196391315646906</v>
+        <v>-2.461042741706923</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.720083147368493</v>
+        <v>1.614222576944486</v>
       </c>
       <c r="F1990" t="n">
         <v>0.9381868070118481</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
         <v>2.759553868962213</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.142646501219701</v>
+        <v>-2.407297927279718</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.902138844160585</v>
+        <v>1.796278273736578</v>
       </c>
       <c r="F1991" t="n">
         <v>0.9482501164523101</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>2.87966677818003</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.118854932613559</v>
+        <v>-2.383506358673576</v>
       </c>
       <c r="E1992" t="n">
-        <v>2.031768380820859</v>
+        <v>1.925907810396852</v>
       </c>
       <c r="F1992" t="n">
         <v>0.9720416850584523</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
         <v>2.871374754193889</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.092770848349751</v>
+        <v>-2.357422274409768</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.033909990540241</v>
+        <v>1.928049420116235</v>
       </c>
       <c r="F1993" t="n">
         <v>0.9720416850584523</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896925</v>
       </c>
       <c r="C1994" t="n">
         <v>2.869567949777668</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.014639667500804</v>
+        <v>-2.279291093560821</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.0633556584636</v>
+        <v>1.957495088039593</v>
       </c>
       <c r="F1994" t="n">
         <v>1.046218495942137</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959854</v>
       </c>
       <c r="C1995" t="n">
         <v>2.88712235550446</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.005747206107521</v>
+        <v>-2.270398632167538</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.084467048747705</v>
+        <v>1.978606478323697</v>
       </c>
       <c r="F1995" t="n">
         <v>1.046218495942137</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>2.878977402909044</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.174223323077398</v>
+        <v>-2.438874749137416</v>
       </c>
       <c r="E1996" t="n">
-        <v>2.008931649364337</v>
+        <v>1.90307107894033</v>
       </c>
       <c r="F1996" t="n">
         <v>1.018270660225556</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782705</v>
       </c>
       <c r="C1997" t="n">
         <v>2.860247100096906</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.476423794215815</v>
+        <v>-1.741075220275833</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.269321158096832</v>
+        <v>2.163460587672825</v>
       </c>
       <c r="F1997" t="n">
         <v>0.9479226008551453</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632636</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>2.85091112259381</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.453702690532662</v>
+        <v>-1.71835411659268</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.269073622066998</v>
+        <v>2.163213051642991</v>
       </c>
       <c r="F1998" t="n">
         <v>0.9479226008551453</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
         <v>3.009817248444979</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.451977647242619</v>
+        <v>-1.716629073302636</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.428669765234185</v>
+        <v>2.322809194810177</v>
       </c>
       <c r="F1999" t="n">
         <v>0.9496476441451891</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644413</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
         <v>3.046895070938626</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.606758654020874</v>
+        <v>-1.871410080080892</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.403835185016529</v>
+        <v>2.297974614592522</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9162799700907129</v>
@@ -47568,16 +47568,16 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799964</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>3.043570426928171</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.555323320636214</v>
+        <v>-1.819974746696232</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.421084674359938</v>
+        <v>2.315224103935931</v>
       </c>
       <c r="F2001" t="n">
         <v>0.9677153034753726</v>
@@ -47591,16 +47591,16 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
         <v>3.053576580572912</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.528372096309726</v>
+        <v>-1.793023522369744</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.441871317735274</v>
+        <v>2.336010747311267</v>
       </c>
       <c r="F2002" t="n">
         <v>0.9825956495030918</v>
@@ -47614,16 +47614,16 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.237679712717872</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.664325104366043</v>
+        <v>-1.92897653042606</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.571593246657708</v>
+        <v>2.465732676233701</v>
       </c>
       <c r="F2003" t="n">
         <v>0.9825956495030918</v>
@@ -47637,16 +47637,16 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714426</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.229796407620865</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.686733222170915</v>
+        <v>-1.951384648230932</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.554746694438752</v>
+        <v>2.448886124014745</v>
       </c>
       <c r="F2004" t="n">
         <v>0.9825956495030918</v>
@@ -47660,16 +47660,16 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155034</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
         <v>3.231850407170503</v>
       </c>
       <c r="D2005" t="n">
-        <v>-1.834738989650314</v>
+        <v>-2.099390415710332</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.49759838699663</v>
+        <v>2.391737816572623</v>
       </c>
       <c r="F2005" t="n">
         <v>0.8958686406395503</v>
@@ -47683,16 +47683,16 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161979</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
         <v>3.28810412489235</v>
       </c>
       <c r="D2006" t="n">
-        <v>-1.844179915538844</v>
+        <v>-2.108831341598862</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.550075734363065</v>
+        <v>2.444215163939058</v>
       </c>
       <c r="F2006" t="n">
         <v>1.018295758182942</v>
@@ -47706,16 +47706,16 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321636</v>
+        <v>3.714941193321632</v>
       </c>
       <c r="C2007" t="n">
         <v>3.290995219437651</v>
       </c>
       <c r="D2007" t="n">
-        <v>-1.842893151999287</v>
+        <v>-2.107544578059305</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.553481534324189</v>
+        <v>2.447620963900182</v>
       </c>
       <c r="F2007" t="n">
         <v>1.019582521722498</v>
@@ -47729,16 +47729,16 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347704</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.289107032331426</v>
       </c>
       <c r="D2008" t="n">
-        <v>-1.844450205988578</v>
+        <v>-2.109101632048596</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.550970525622247</v>
+        <v>2.44510995519824</v>
       </c>
       <c r="F2008" t="n">
         <v>1.019582521722498</v>
@@ -47752,16 +47752,16 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887748</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.283927261934288</v>
       </c>
       <c r="D2009" t="n">
-        <v>-1.851722091512043</v>
+        <v>-2.116373517572061</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.542882001015724</v>
+        <v>2.437021430591717</v>
       </c>
       <c r="F2009" t="n">
         <v>1.012310636199033</v>
@@ -47775,16 +47775,16 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343066</v>
+        <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
         <v>3.282361272144441</v>
       </c>
       <c r="D2010" t="n">
-        <v>-1.849881072453792</v>
+        <v>-2.11453249851381</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.542052418849177</v>
+        <v>2.436191848425169</v>
       </c>
       <c r="F2010" t="n">
         <v>1.013578862870502</v>
@@ -47798,16 +47798,16 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647107</v>
+        <v>3.754911907647103</v>
       </c>
       <c r="C2011" t="n">
         <v>3.295434679010359</v>
       </c>
       <c r="D2011" t="n">
-        <v>-1.856789777953472</v>
+        <v>-2.12144120401349</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.552362343515223</v>
+        <v>2.446501773091216</v>
       </c>
       <c r="F2011" t="n">
         <v>1.013578862870502</v>
@@ -47821,16 +47821,16 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763533</v>
+        <v>3.74989685176353</v>
       </c>
       <c r="C2012" t="n">
         <v>3.295434679010359</v>
       </c>
       <c r="D2012" t="n">
-        <v>-1.858351420768332</v>
+        <v>-2.12300284682835</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.551737686389279</v>
+        <v>2.445877115965272</v>
       </c>
       <c r="F2012" t="n">
         <v>1.013578862870502</v>
@@ -47844,16 +47844,16 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392117</v>
+        <v>3.715834055392113</v>
       </c>
       <c r="C2013" t="n">
         <v>3.293958720137361</v>
       </c>
       <c r="D2013" t="n">
-        <v>-1.886252207877805</v>
+        <v>-2.150903633937823</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.539101412672492</v>
+        <v>2.433240842248485</v>
       </c>
       <c r="F2013" t="n">
         <v>0.9789819387275672</v>
@@ -47867,16 +47867,16 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172528</v>
+        <v>3.684909939172524</v>
       </c>
       <c r="C2014" t="n">
         <v>3.29072316411456</v>
       </c>
       <c r="D2014" t="n">
-        <v>-1.889285205390479</v>
+        <v>-2.153936631450497</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.534652657644621</v>
+        <v>2.428792087220614</v>
       </c>
       <c r="F2014" t="n">
         <v>0.9759489412148934</v>
@@ -47890,16 +47890,16 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971081</v>
+        <v>3.619362241971077</v>
       </c>
       <c r="C2015" t="n">
         <v>3.357429123705064</v>
       </c>
       <c r="D2015" t="n">
-        <v>-1.909346526666986</v>
+        <v>-2.173997952727004</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.593334088724522</v>
+        <v>2.487473518300515</v>
       </c>
       <c r="F2015" t="n">
         <v>0.9558876199383863</v>
@@ -47913,16 +47913,16 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199807</v>
+        <v>3.640764248199804</v>
       </c>
       <c r="C2016" t="n">
         <v>3.497740842706911</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.16606734466181</v>
+        <v>-2.430718770721828</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.63095748052844</v>
+        <v>2.525096910104432</v>
       </c>
       <c r="F2016" t="n">
         <v>0.8474730457945715</v>
@@ -47936,16 +47936,16 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622238</v>
+        <v>3.668303164622235</v>
       </c>
       <c r="C2017" t="n">
         <v>3.566721111852551</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.320053762437951</v>
+        <v>-2.584705188497968</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.638343182563623</v>
+        <v>2.532482612139616</v>
       </c>
       <c r="F2017" t="n">
         <v>0.8474730457945715</v>
@@ -47959,16 +47959,16 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808531</v>
+        <v>3.619937176808527</v>
       </c>
       <c r="C2018" t="n">
         <v>3.552772313972671</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.269531858610285</v>
+        <v>-2.534183284670303</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.64460314621481</v>
+        <v>2.538742575790804</v>
       </c>
       <c r="F2018" t="n">
         <v>0.8474730457945715</v>
@@ -47982,16 +47982,16 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994896</v>
+        <v>3.656346893994892</v>
       </c>
       <c r="C2019" t="n">
         <v>3.564642803028085</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.522007012618009</v>
+        <v>-2.786658438678027</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.555483573667135</v>
+        <v>2.449623003243127</v>
       </c>
       <c r="F2019" t="n">
         <v>0.8474730457945715</v>
@@ -48005,16 +48005,16 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358299</v>
+        <v>3.674042696358296</v>
       </c>
       <c r="C2020" t="n">
         <v>3.565853337547029</v>
       </c>
       <c r="D2020" t="n">
-        <v>-2.791479814539717</v>
+        <v>-3.056131240599735</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.448904987417395</v>
+        <v>2.343044416993388</v>
       </c>
       <c r="F2020" t="n">
         <v>0.8474730457945715</v>
@@ -48028,16 +48028,16 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637088</v>
+        <v>3.663523617637084</v>
       </c>
       <c r="C2021" t="n">
         <v>3.569975079774351</v>
       </c>
       <c r="D2021" t="n">
-        <v>-2.949023886269158</v>
+        <v>-3.213675312329177</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.39000910095294</v>
+        <v>2.284148530528933</v>
       </c>
       <c r="F2021" t="n">
         <v>0.7805712406542971</v>
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.861339765497009</v>
+        <v>3.482255899460319</v>
       </c>
       <c r="C2022" t="n">
         <v>3.56505293251054</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.320886454498555</v>
+        <v>-3.342525863031223</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.236341926397371</v>
+        <v>2.227686162984304</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.6431961534646777</v>
+        <v>0.7395778318035755</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.950970624589347</v>
+        <v>4.008799631592685</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240712.xlsx
+++ b/tame_output/ON/bt/strategyON_20240712.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>58.8%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.7%</t>
+          <t>-69.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>108.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.2%</t>
+          <t>120.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.3%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-49.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.4%</t>
+          <t>-64.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.3%</t>
+          <t>457.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-495.8%</t>
+          <t>-466.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.6%</t>
+          <t>-34.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-153.5%</t>
+          <t>-141.9%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.2%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.4%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-28.9%</t>
+          <t>-28.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>125.2%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-124.2%</t>
+          <t>-130.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-150.0%</t>
+          <t>-136.2%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>80.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>94.5%</t>
+          <t>94.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.9%</t>
+          <t>-24.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-17.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-45.1%</t>
+          <t>-36.8%</t>
         </is>
       </c>
     </row>
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.339982228858227</v>
+        <v>-7.076625841947135</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1808128389655548</v>
+        <v>0.2861553937299917</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.019894149117834</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.422191348780327</v>
+        <v>2.505225665351893</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.526701937167529</v>
+        <v>-7.263345550256438</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1020986511074309</v>
+        <v>0.2074412058718673</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.019894149117834</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.418165044245924</v>
+        <v>2.501199360817489</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.909703325910161</v>
+        <v>-7.646346938999069</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.05120400571120598</v>
+        <v>0.0541385490532309</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.019894149117834</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.41806294292434</v>
+        <v>2.501097259495905</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.091573116895196</v>
+        <v>-7.828216729984105</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.12138040613379</v>
+        <v>-0.0160378513693531</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.340154467722146</v>
+        <v>-1.201763940102869</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.311512584304749</v>
+        <v>2.394546900876314</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.451103439399198</v>
+        <v>-8.187747052488106</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.2598422318373403</v>
+        <v>-0.1544996770729039</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.340154467722146</v>
+        <v>-1.201763940102869</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.316862887602799</v>
+        <v>2.399897204174365</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.50145250285342</v>
+        <v>-8.238096115942328</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.2720658372618519</v>
+        <v>-0.166723282497415</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.390503531176368</v>
+        <v>-1.252113003557092</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.294569469487443</v>
+        <v>2.377603786059009</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.599071780274816</v>
+        <v>-8.335715393363724</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.3080717976086413</v>
+        <v>-0.2027292428442045</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.488122808597764</v>
+        <v>-1.349732280978488</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.239039653656374</v>
+        <v>2.32207397022794</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.746597868280459</v>
+        <v>-8.483241481369367</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.3641886764893263</v>
+        <v>-0.2588461217248894</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.635648896603408</v>
+        <v>-1.497258368984132</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.15341755717456</v>
+        <v>2.236451873746126</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.950856043610322</v>
+        <v>-8.687499656699231</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.4403787495026292</v>
+        <v>-0.3350361947381928</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.763287841217397</v>
+        <v>-1.624897313598121</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.082347387524809</v>
+        <v>2.165381704096375</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.984508882118796</v>
+        <v>-8.721152495207704</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.4493573304215825</v>
+        <v>-0.3440147756571461</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.863701209134434</v>
+        <v>-1.725310681515158</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.026581921259023</v>
+        <v>2.109616237830588</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.911039050451347</v>
+        <v>-8.647682663540255</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.4045976962611819</v>
+        <v>-0.2992551414967455</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.790231377466986</v>
+        <v>-1.65184084984771</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.086035521752913</v>
+        <v>2.169069838324479</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.08616346783789</v>
+        <v>-8.822807080926799</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.4600922424682823</v>
+        <v>-0.3547496877038459</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.965355794853529</v>
+        <v>-1.826965267234253</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.995516092068503</v>
+        <v>2.078550408640069</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.32061556185238</v>
+        <v>-9.057259174941288</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.5610922449756743</v>
+        <v>-0.4557496902112379</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.965355794853529</v>
+        <v>-1.826965267234253</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.988296927166908</v>
+        <v>2.071331243738473</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.424990292878826</v>
+        <v>-9.161633905967735</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.6095143281602291</v>
+        <v>-0.5041717733957927</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.069730525879975</v>
+        <v>-1.931339998260699</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.918999897777064</v>
+        <v>2.00203421434863</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.477776448479153</v>
+        <v>-9.214420061568061</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.6295130005618033</v>
+        <v>-0.5241704457973668</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.165406012462372</v>
+        <v>-2.027015484843096</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.862710395666182</v>
+        <v>1.945744712237747</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.603813241847442</v>
+        <v>-9.340456854936351</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6772339892800043</v>
+        <v>-0.5718914345155679</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.14015438965263</v>
+        <v>-2.001763862033354</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.880555097981142</v>
+        <v>1.963589414552708</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.546741469951511</v>
+        <v>-9.28338508304042</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.6504149448352314</v>
+        <v>-0.5450723900707946</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.14015438965263</v>
+        <v>-2.001763862033354</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.884545433667543</v>
+        <v>1.967579750239109</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.688413311675632</v>
+        <v>-9.42505692476454</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.7085589084236212</v>
+        <v>-0.6032163536591844</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.14015438965263</v>
+        <v>-2.001763862033354</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.883070206768801</v>
+        <v>1.966104523340367</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.638822467250797</v>
+        <v>-9.375466080339706</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.673669160488815</v>
+        <v>-0.5683266057243785</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.090563545227796</v>
+        <v>-1.95217301760852</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.927878123588574</v>
+        <v>2.01091244016014</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.489904132778941</v>
+        <v>-9.226547745867849</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.6271529603467556</v>
+        <v>-0.5218104055823187</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.059313954492623</v>
+        <v>-1.920923426873347</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.933576744382995</v>
+        <v>2.01661106095456</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.264058980059531</v>
+        <v>-9.000702593148439</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.5272358262227828</v>
+        <v>-0.4218932714583463</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.017387278905459</v>
+        <v>-1.878996751286183</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.968311822771502</v>
+        <v>2.051346139343067</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.139480323721939</v>
+        <v>-8.876123936810847</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4762652191316872</v>
+        <v>-0.3709226643672507</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.017387278905459</v>
+        <v>-1.878996751286183</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.96945096732756</v>
+        <v>2.052485283899126</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.192375611766225</v>
+        <v>-8.929019224855134</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4947895601872943</v>
+        <v>-0.3894470054228574</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.012431932817013</v>
+        <v>-1.874041405197737</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.975057949142736</v>
+        <v>2.058092265714301</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611565</v>
+        <v>3.768951674611567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.120242436478344</v>
+        <v>-8.856886049567253</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.460202585833505</v>
+        <v>-0.3548600310690686</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.012431932817013</v>
+        <v>-1.874041405197737</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.980791653381372</v>
+        <v>2.063825969952938</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955324</v>
+        <v>3.728577929955326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.048876043868697</v>
+        <v>-8.785519656957606</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.4413932911835117</v>
+        <v>-0.3360507364190748</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.941065540207365</v>
+        <v>-1.802675012588089</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.013874226553296</v>
+        <v>2.096908543124862</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232409</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.955417009883472</v>
+        <v>-8.692060622972381</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.4138931589023294</v>
+        <v>-0.3085506041378925</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.941065540207365</v>
+        <v>-1.802675012588089</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.003990745240388</v>
+        <v>2.087025061811954</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436225</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.688175209015075</v>
+        <v>-8.424818822103983</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3088309990543441</v>
+        <v>-0.2034884442899072</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.941065540207365</v>
+        <v>-1.802675012588089</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.002156184741015</v>
+        <v>2.08519050131258</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311944</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.590268170338584</v>
+        <v>-8.326911783427493</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2699684985572084</v>
+        <v>-0.164625943792772</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.873079790346809</v>
+        <v>-1.734689262727533</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.042647319683887</v>
+        <v>2.125681636255453</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097239</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.566314629362626</v>
+        <v>-8.302958242451535</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2597185760213319</v>
+        <v>-0.154376021256895</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.849126249370851</v>
+        <v>-1.710735721751575</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.057687950414956</v>
+        <v>2.140722266986521</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017767</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.302254691039829</v>
+        <v>-8.038898304128738</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1673549168539652</v>
+        <v>-0.06201236208952832</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.585066311048055</v>
+        <v>-1.446675783428779</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.202863597246881</v>
+        <v>2.285897913818447</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839721</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.621579320495826</v>
+        <v>-7.3318186806239</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1021281977033355</v>
+        <v>0.2180324536521061</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.585066311048055</v>
+        <v>-1.446675783428779</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.20007656358658</v>
+        <v>2.283110880158146</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388724</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.581395022129636</v>
+        <v>-7.291634382257709</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.118545540937653</v>
+        <v>0.2344497968864236</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.544882012681864</v>
+        <v>-1.406491485062588</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.224530766494136</v>
+        <v>2.307565083065702</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85616175162647</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.417995151190273</v>
+        <v>-7.128234511318347</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1832723105341549</v>
+        <v>0.2991765664829256</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.381482141742502</v>
+        <v>-1.243091614123226</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.321937510278511</v>
+        <v>2.404971826850076</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.184513928960675</v>
+        <v>-6.894753289088748</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2845892282638465</v>
+        <v>0.4004934842126171</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.148000919512903</v>
+        <v>-1.009610391893627</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.469950672454122</v>
+        <v>2.552984989025688</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785785</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.034847537953159</v>
+        <v>-6.745086898081233</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3415635743538936</v>
+        <v>0.4574678303026642</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.055097428270367</v>
+        <v>-0.9167069006510913</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.522800556886684</v>
+        <v>2.60583487345825</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390426</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.902572064322273</v>
+        <v>-6.612811424450347</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3898412505532751</v>
+        <v>0.5057455065020457</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.9228219546394807</v>
+        <v>-0.7844314270202046</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.597533327812243</v>
+        <v>2.680567644383809</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.78471879410595</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.746833731762531</v>
+        <v>-6.457073091890605</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4549516442648085</v>
+        <v>0.5708559002135791</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.7670836220797391</v>
+        <v>-0.6286930944604631</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.693791388035725</v>
+        <v>2.776825704607291</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960984</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.49783393307895</v>
+        <v>-6.208073293207024</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5674579049618997</v>
+        <v>0.6833621609106704</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.7670836220797391</v>
+        <v>-0.6286930944604631</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.706697729259384</v>
+        <v>2.78973204583095</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607642</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.603423922852055</v>
+        <v>-6.313663282980128</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3972459794534391</v>
+        <v>0.5131502354022097</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.8726736118528435</v>
+        <v>-0.7342830842335675</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.515367805796302</v>
+        <v>2.598402122367868</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.622158824970652</v>
+        <v>-6.332398185098725</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4382963604830867</v>
+        <v>0.5542006164318574</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.8782696215129748</v>
+        <v>-0.7398790938936988</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.56055454187731</v>
+        <v>2.643588858448876</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.474218783563052</v>
+        <v>-6.184458143691126</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3775934543579589</v>
+        <v>0.4934977103067295</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.8579487056044173</v>
+        <v>-0.7195581779851412</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.452868168734277</v>
+        <v>2.535902485305843</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.421249261309064</v>
+        <v>-6.131488621437137</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.390067277006076</v>
+        <v>0.5059715329548466</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.8049791833504284</v>
+        <v>-0.6665886557311523</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.475935895833192</v>
+        <v>2.558970212404758</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.377700854538373</v>
+        <v>-6.087940214666447</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.400526027619259</v>
+        <v>0.5164302835680297</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.8049791833504284</v>
+        <v>-0.6665886557311523</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.468975283738099</v>
+        <v>2.552009600309665</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.135552461084515</v>
+        <v>-5.845791821212589</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5118477393819454</v>
+        <v>0.627751995330716</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.8049791833504284</v>
+        <v>-0.6665886557311523</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.483437638119242</v>
+        <v>2.566471954690808</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.027293323961993</v>
+        <v>-5.737532684090067</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5496835146901491</v>
+        <v>0.6655877706389197</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.8049791833504284</v>
+        <v>-0.6665886557311523</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.477969758578437</v>
+        <v>2.561004075150003</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.904002189144863</v>
+        <v>-5.614241549272936</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5964980626275787</v>
+        <v>0.7124023185763493</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.6816880485332979</v>
+        <v>-0.5432975209140218</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.549442533479292</v>
+        <v>2.632476850050858</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919906</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.882852990241419</v>
+        <v>-5.593092350369493</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.612658720426281</v>
+        <v>0.7285629763750516</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.6605388496298545</v>
+        <v>-0.5221483220105785</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.569833031058684</v>
+        <v>2.652867347630249</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.639087548257975</v>
+        <v>-5.349326908386049</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7059456055667095</v>
+        <v>0.8218498615154801</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.6605388496298545</v>
+        <v>-0.5221483220105785</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.565613739405734</v>
+        <v>2.6486480559773</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.53732472798068</v>
+        <v>-5.247564088108754</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7487750475976434</v>
+        <v>0.864679303546414</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.6473197812374258</v>
+        <v>-0.5089292536181498</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.575669494361208</v>
+        <v>2.658703810932773</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279183</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.287474334031605</v>
+        <v>-4.997713694159679</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8414572801609754</v>
+        <v>0.9573615361097461</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.6473197812374258</v>
+        <v>-0.5089292536181498</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.56841156934491</v>
+        <v>2.651445885916475</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.111582241564173</v>
+        <v>-4.821821601692246</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9154132406685971</v>
+        <v>1.031317496617368</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.6473197812374258</v>
+        <v>-0.5089292536181498</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.572010692865558</v>
+        <v>2.655045009437124</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.94013577854171</v>
+        <v>-4.650375138669783</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9973193319321361</v>
+        <v>1.113223587880907</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.4758733182149627</v>
+        <v>-0.3374827905956866</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.68820607673359</v>
+        <v>2.771240393305156</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.865846212803371</v>
+        <v>-4.576085572931444</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.026055635843769</v>
+        <v>1.14195989179254</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.4015837524766234</v>
+        <v>-0.2631932248573474</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.731800293792891</v>
+        <v>2.814834610364456</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.802210470569436</v>
+        <v>-4.512449830697509</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.05620473379166</v>
+        <v>1.172108989740431</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.3379480102426889</v>
+        <v>-0.1995574826234128</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.774676540187568</v>
+        <v>2.857710856759134</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074779</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.690783711243516</v>
+        <v>-4.401023071371589</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.081969696305823</v>
+        <v>1.197873952254594</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.3379480102426889</v>
+        <v>-0.1995574826234128</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.755870798971364</v>
+        <v>2.83890511554293</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769488424229</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.450353214438656</v>
+        <v>-4.160592574566729</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.179884971652645</v>
+        <v>1.295789227601416</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.09751751343782861</v>
+        <v>0.04087301418144745</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.901872173679158</v>
+        <v>2.984906490250723</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.378110646267461</v>
+        <v>-4.088350006395534</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.212711312755943</v>
+        <v>1.328615568704714</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.09751751343782861</v>
+        <v>0.04087301418144745</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.905801487513978</v>
+        <v>2.988835804085543</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.325112323986073</v>
+        <v>-4.035351684114146</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.234589225585838</v>
+        <v>1.350493481534609</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.04218125443588977</v>
+        <v>0.09620927318338629</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.939681826832481</v>
+        <v>3.022716143404047</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502334</v>
+        <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.216307438506346</v>
+        <v>-3.92654679863442</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.275109250997722</v>
+        <v>1.391013506946493</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.04218125443588977</v>
+        <v>0.09620927318338629</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.936679898052475</v>
+        <v>3.01971421462404</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.996286640469335</v>
+        <v>-3.706526000597409</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.364696607223141</v>
+        <v>1.480600863171912</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.09903859063209047</v>
+        <v>0.2374291182513665</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.022990842103877</v>
+        <v>3.106025158675442</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.863418951406057</v>
+        <v>-3.57365831153413</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.433737865650276</v>
+        <v>1.549642121599046</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.09903859063209047</v>
+        <v>0.2374291182513665</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.0388850249057</v>
+        <v>3.121919341477266</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496258</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.743245868041559</v>
+        <v>-3.453485228169631</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.482952943436377</v>
+        <v>1.598857199385148</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.2192116739965894</v>
+        <v>0.3576022016158655</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.112134719364701</v>
+        <v>3.195169035936267</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576995</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.598573722941821</v>
+        <v>-3.308813083069894</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.550909904037712</v>
+        <v>1.666814159986483</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.3638838190963268</v>
+        <v>0.5022743467156029</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.209026108985984</v>
+        <v>3.292060425557549</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.7358392229421</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.658448550299513</v>
+        <v>-3.368687910427586</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.512997464496061</v>
+        <v>1.628901720444832</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.3040089917386347</v>
+        <v>0.4423995193579108</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.159138703972794</v>
+        <v>3.24217302054436</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.538628319388676</v>
+        <v>-3.248867679516749</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.576214726094604</v>
+        <v>1.692118982043375</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.3040089917386347</v>
+        <v>0.4423995193579108</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.174427873207003</v>
+        <v>3.257462189778569</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914639843069</v>
+        <v>3.729146398430692</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.541098025850482</v>
+        <v>-3.251337385978555</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.482871042832323</v>
+        <v>1.598775298781094</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.3015392852768286</v>
+        <v>0.4399298128961046</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.080590248652361</v>
+        <v>3.163624565223926</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.609468212174492</v>
+        <v>-3.319707572302565</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.374784829788021</v>
+        <v>1.490689085736792</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.3108149843130435</v>
+        <v>0.4492055119323196</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.005417529559391</v>
+        <v>3.088451846130957</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.623256265021539</v>
+        <v>-3.333495625149611</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.359706317281093</v>
+        <v>1.475610573229864</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.3108149843130435</v>
+        <v>0.4492055119323196</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.995854238191282</v>
+        <v>3.078888554762848</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.654249424350244</v>
+        <v>-3.364488784478317</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.172018618589998</v>
+        <v>1.287922874538769</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.3108149843130435</v>
+        <v>0.4492055119323196</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.820563803231669</v>
+        <v>2.903598119803235</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.478775164557775</v>
+        <v>-3.189014524685847</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.246775554498774</v>
+        <v>1.362679810447544</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.3108149843130435</v>
+        <v>0.4492055119323196</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.825131035223457</v>
+        <v>2.908165351795023</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.589711417199023</v>
+        <v>-3.299950777327096</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.178143082203481</v>
+        <v>1.294047338152252</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.3108149843130435</v>
+        <v>0.4492055119323196</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.800873063984664</v>
+        <v>2.88390738055623</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.617515458616743</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.556047871726741</v>
+        <v>-3.266287231854814</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.194739885612299</v>
+        <v>1.31064414156107</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.3444785297853253</v>
+        <v>0.4828690574046014</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.824202576487939</v>
+        <v>2.907236893059504</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.627687845048876</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.496195252523018</v>
+        <v>-3.206434612651091</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.228853319725921</v>
+        <v>1.344757575674692</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.3444785297853253</v>
+        <v>0.4828690574046014</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.834374962920071</v>
+        <v>2.917409279491637</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.622634115622736</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.409951789496641</v>
+        <v>-3.120191149624714</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.258296975510332</v>
+        <v>1.374201231459103</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.3444785297853253</v>
+        <v>0.4828690574046014</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.829321233493931</v>
+        <v>2.912355550065497</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.614409891067262</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.455258608895621</v>
+        <v>-3.165497969023694</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.231950023195266</v>
+        <v>1.347854279144037</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.3036683667760945</v>
+        <v>0.4420588943953706</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.796610911132919</v>
+        <v>2.879645227704484</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.614961764100363</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.484291713597922</v>
+        <v>-3.194531073725995</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.220888654347447</v>
+        <v>1.336792910296218</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.3036683667760945</v>
+        <v>0.4420588943953706</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.79716278416602</v>
+        <v>2.880197100737586</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.544234455991729</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.391481232147063</v>
+        <v>-3.101720592275136</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.187285538819156</v>
+        <v>1.303189794767927</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.3964788482269539</v>
+        <v>0.53486937584623</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.782121764927902</v>
+        <v>2.865156081499467</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.54610793191633</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.435870701476491</v>
+        <v>-3.146110061604563</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.171403227011986</v>
+        <v>1.287307482960757</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.3520893788975262</v>
+        <v>0.4904799065168023</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.757361559254845</v>
+        <v>2.840395875826411</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.541183640428053</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.323199483240241</v>
+        <v>-3.033438843368313</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.211547422818209</v>
+        <v>1.32745167876698</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4647605971337764</v>
+        <v>0.6031511247530525</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.820039998708319</v>
+        <v>2.903074315279884</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.54667493625872</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.210822482057568</v>
+        <v>-2.921061842185641</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.261989519121945</v>
+        <v>1.377893775070716</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4647605971337764</v>
+        <v>0.6031511247530525</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.825531294538986</v>
+        <v>2.908565611110552</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.558172138027259</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.238602879958921</v>
+        <v>-2.948842240086994</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.262374561729943</v>
+        <v>1.378278817678714</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4369801992324234</v>
+        <v>0.5753707268516994</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.820360257566713</v>
+        <v>2.903394574138279</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
         <v>2.396527858027912</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.3216041609842</v>
+        <v>-3.031843521112273</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.067529769320485</v>
+        <v>1.183434025269256</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4184093147052496</v>
+        <v>0.5567998423245257</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.647573446851062</v>
+        <v>2.730607763422628</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.516677518747118</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.430218239427531</v>
+        <v>-3.140457599555604</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.144233798662358</v>
+        <v>1.260138054611129</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4184093147052496</v>
+        <v>0.5567998423245257</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.767723107570268</v>
+        <v>2.850757424141833</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.394809201179388</v>
+        <v>-3.105048561307461</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.172910440063938</v>
+        <v>1.288814696012709</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4184093147052496</v>
+        <v>0.5567998423245257</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.782236133672591</v>
+        <v>2.865270450244156</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
         <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.356425538621237</v>
+        <v>-3.06666489874931</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.185683346429567</v>
+        <v>1.301587602378338</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4567929772634008</v>
+        <v>0.5951835048826769</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.80268577254985</v>
+        <v>2.885720089121416</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.179309208586071</v>
+        <v>-2.889548568714144</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.253258907288936</v>
+        <v>1.369163163237707</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4567929772634008</v>
+        <v>0.5951835048826769</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.799414801395153</v>
+        <v>2.882449117966718</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.224401453419617</v>
+        <v>-2.93464081354769</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.235905401117431</v>
+        <v>1.351809657066202</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.394896934094011</v>
+        <v>0.5332874617132871</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.762960567255432</v>
+        <v>2.845994883826998</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.045026032180849</v>
+        <v>-2.755265392308922</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.301442544919352</v>
+        <v>1.417346800868123</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5516736922647296</v>
+        <v>0.6900642198840058</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.850813597464277</v>
+        <v>2.933847914035843</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.090040245701455</v>
+        <v>-2.800279605829528</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.2642443148427</v>
+        <v>1.38014857079147</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.521324796950125</v>
+        <v>0.6597153245694012</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.813411715607104</v>
+        <v>2.89644603217867</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.357044755973891</v>
+        <v>-3.067284116101963</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.163134073072671</v>
+        <v>1.279038329021442</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3269617589071764</v>
+        <v>0.4653522865264526</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.702485455120281</v>
+        <v>2.785519771691847</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.458242537411063</v>
+        <v>-3.168481897539136</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.121858882394303</v>
+        <v>1.237763138343074</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2585529453618572</v>
+        <v>0.3969434729811334</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.660644088889591</v>
+        <v>2.743678405461156</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.451731570796751</v>
+        <v>-3.161970930924824</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.122063230594345</v>
+        <v>1.237967486543116</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2585529453618572</v>
+        <v>0.3969434729811334</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.658244050443908</v>
+        <v>2.741278367015473</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.432693443089454</v>
+        <v>-3.142932803217526</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.126203200885509</v>
+        <v>1.24210745683428</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2003693340306627</v>
+        <v>0.3387598616499389</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.619858602853436</v>
+        <v>2.702892919425001</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131249</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.463820074240072</v>
+        <v>-3.174059434368144</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.291334417363942</v>
+        <v>1.407238673312713</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2003693340306627</v>
+        <v>0.3387598616499389</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.797440471792116</v>
+        <v>2.880474788363682</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.477686835573989</v>
+        <v>-3.187926195702062</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.286621041816509</v>
+        <v>1.40252529776528</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1625114172968398</v>
+        <v>0.3009019449161159</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.775559050737956</v>
+        <v>2.858593367309522</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
         <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.432882664034059</v>
+        <v>-3.143122024162132</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.310551240829407</v>
+        <v>1.426455496778178</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1625114172968398</v>
+        <v>0.3009019449161159</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.781567581134882</v>
+        <v>2.864601897706448</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.582010952033977</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.285139693799057</v>
+        <v>-2.99537905392713</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.267598650200607</v>
+        <v>1.383502906149378</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3303187745317229</v>
+        <v>0.4687093021509991</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.780202216753011</v>
+        <v>2.863236533324577</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.584804573565458</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.387154376330278</v>
+        <v>-3.097393736458351</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.2295863987196</v>
+        <v>1.345490654668371</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3303187745317229</v>
+        <v>0.4687093021509991</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.782995838284492</v>
+        <v>2.866030154856058</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.585466921957117</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.381001670277493</v>
+        <v>-3.091241030405566</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.232709829532372</v>
+        <v>1.348614085481143</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3364714805845072</v>
+        <v>0.4748620082037834</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.787349810307821</v>
+        <v>2.870384126879387</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.584547398697227</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.397810968427995</v>
+        <v>-3.108050328556068</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.225066587012282</v>
+        <v>1.340970842961053</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3196621824340056</v>
+        <v>0.4580527100532817</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.776344708157631</v>
+        <v>2.859379024729196</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>2.650882952494048</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.335512969651873</v>
+        <v>-3.045752329779946</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.316321340319551</v>
+        <v>1.432225596268322</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3196621824340056</v>
+        <v>0.4580527100532817</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.842680261954452</v>
+        <v>2.925714578526017</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
         <v>2.453174954208175</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.133722771986715</v>
+        <v>-2.843962132114788</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.199329421099742</v>
+        <v>1.315233677048512</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.51768037460316</v>
+        <v>0.6560709022224361</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.763783178970071</v>
+        <v>2.846817495541637</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
         <v>2.52346518653035</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.968909768907868</v>
+        <v>-2.679149129035941</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.335544854653456</v>
+        <v>1.451449110602226</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6824933776820069</v>
+        <v>0.8208839053012831</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.932961213139555</v>
+        <v>3.01599552971112</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
         <v>2.538092922646394</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.066650313532842</v>
+        <v>-2.776889673660915</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.311076372919509</v>
+        <v>1.42698062886828</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6666040995490268</v>
+        <v>0.8049946271683028</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.93805538237581</v>
+        <v>3.021089698947375</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.536628903471065</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.242988073655772</v>
+        <v>-2.953227433783844</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.23907724969501</v>
+        <v>1.35498150564378</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4902663394260973</v>
+        <v>0.6286568670453734</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.830788707126724</v>
+        <v>2.91382302369829</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.535120521510994</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.166566027223845</v>
+        <v>-2.876805387351918</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.268137686307709</v>
+        <v>1.38404194225648</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4902663394260973</v>
+        <v>0.6286568670453734</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.829280325166653</v>
+        <v>2.912314641738218</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
         <v>2.53498338894643</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.122192895585276</v>
+        <v>-2.832432255713349</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.285749806398572</v>
+        <v>1.401654062347343</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5346394710646659</v>
+        <v>0.673029998683942</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.85576707158523</v>
+        <v>2.938801388156795</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.529377183085021</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.999358674698109</v>
+        <v>-2.709598034826182</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.32927728889203</v>
+        <v>1.445181544840801</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5346394710646659</v>
+        <v>0.673029998683942</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.85016086572382</v>
+        <v>2.933195182295386</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190322</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
         <v>2.535758940112825</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.951702944137053</v>
+        <v>-2.661942304265126</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.354721338144257</v>
+        <v>1.470625594093028</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.5822952016257216</v>
+        <v>0.7206857292449976</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.885136061088259</v>
+        <v>2.968170377659824</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569615</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
         <v>2.54065131348755</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.851184785638298</v>
+        <v>-2.561424145766371</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.399820974918484</v>
+        <v>1.515725230867254</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6828133601244761</v>
+        <v>0.8212038877437522</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.950339329562236</v>
+        <v>3.033373646133802</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.82880887755729</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
         <v>2.527405985963422</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.911851376040687</v>
+        <v>-2.62209073616876</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.3623090112334</v>
+        <v>1.478213267182171</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6011150434059425</v>
+        <v>0.7395055710252185</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.888075012006988</v>
+        <v>2.971109328578554</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.531503688574051</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.867012974432289</v>
+        <v>-2.577252334560362</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.384342074487388</v>
+        <v>1.500246330436159</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6056584763508119</v>
+        <v>0.744049003970088</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.894898774384538</v>
+        <v>2.977933090956104</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.81793235491705</v>
       </c>
       <c r="C1982" t="n">
         <v>2.535664628205129</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.967771610189288</v>
+        <v>-2.678010970317361</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.348199559815667</v>
+        <v>1.464103815764437</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5168329076238065</v>
+        <v>0.6552234352430826</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.845764372779413</v>
+        <v>2.928798689350979</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405957</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.541544230732966</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.923568773103387</v>
+        <v>-2.63380813323146</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.371760297177864</v>
+        <v>1.487664553126635</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.561035744709707</v>
+        <v>0.699426272328983</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.87816567755879</v>
+        <v>2.961199994130356</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.539954231202214</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.960547800766831</v>
+        <v>-2.670787160894903</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.355378686581734</v>
+        <v>1.471282942530505</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.5980096465010375</v>
+        <v>0.7364001741203136</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.898760019102836</v>
+        <v>2.981794335674402</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.591201996385253</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.802256383227558</v>
+        <v>-2.512495743355631</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.469943018780483</v>
+        <v>1.585847274729254</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.5980096465010375</v>
+        <v>0.7364001741203136</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.950007784285876</v>
+        <v>3.033042100857442</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321019</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.589642700979506</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.594614379593082</v>
+        <v>-2.304853739721155</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.551440524828526</v>
+        <v>1.667344780777297</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8056516501355137</v>
+        <v>0.9440421777547897</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.073033691060815</v>
+        <v>3.15606800763238</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.584590929217776</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.543582286870554</v>
+        <v>-2.253821646998627</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.566801590155807</v>
+        <v>1.682705846104578</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8566837428580416</v>
+        <v>0.9950742704773177</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.098601174932602</v>
+        <v>3.181635491504167</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84254736040485</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.601778333310481</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.478358105743348</v>
+        <v>-2.188597465871421</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.610078666699395</v>
+        <v>1.725982922648166</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9219079239852472</v>
+        <v>1.060298451604523</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.15492308770163</v>
+        <v>3.237957404273196</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.597739305609762</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.440931085672215</v>
+        <v>-2.151170445800287</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.621010447027129</v>
+        <v>1.7369147029759</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.9271594620144289</v>
+        <v>1.065549989633705</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.154034982818419</v>
+        <v>3.237069299389985</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992657</v>
+        <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
         <v>2.598996097941002</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.461042741706923</v>
+        <v>-2.171282101834996</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.614222576944486</v>
+        <v>1.730126832893256</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.9381868070118481</v>
+        <v>1.076577334631124</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.161908182148111</v>
+        <v>3.244942498719677</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636284</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.759553868962213</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.407297927279718</v>
+        <v>-2.117537287407791</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.796278273736578</v>
+        <v>1.912182529685349</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9482501164523101</v>
+        <v>1.086640644071586</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.328503938833599</v>
+        <v>3.411538255405165</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957623</v>
       </c>
       <c r="C1992" t="n">
         <v>2.87966677818003</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.383506358673576</v>
+        <v>-2.093745718801649</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.925907810396852</v>
+        <v>2.041812066345623</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.9720416850584523</v>
+        <v>1.110432212677729</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.462891789215102</v>
+        <v>3.545926105786668</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998751</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>2.871374754193889</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.357422274409768</v>
+        <v>-2.067661634537841</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.928049420116235</v>
+        <v>2.043953676065005</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.9720416850584523</v>
+        <v>1.110432212677729</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.454599765228961</v>
+        <v>3.537634081800527</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896925</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
         <v>2.869567949777668</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.279291093560821</v>
+        <v>-1.989530453688894</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.957495088039593</v>
+        <v>2.073399343988364</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.046218495942137</v>
+        <v>1.184609023561413</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.497299047342951</v>
+        <v>3.580333363914517</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959854</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.88712235550446</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.270398632167538</v>
+        <v>-1.980637992295611</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.978606478323697</v>
+        <v>2.094510734272468</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.046218495942137</v>
+        <v>1.184609023561413</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.514853453069742</v>
+        <v>3.597887769641308</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>2.878977402909044</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.438874749137416</v>
+        <v>-2.149114109265489</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.90307107894033</v>
+        <v>2.018975334889101</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.018270660225556</v>
+        <v>1.156661187844833</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.489939799044378</v>
+        <v>3.572974115615944</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782705</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
         <v>2.860247100096906</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.741075220275833</v>
+        <v>-1.451314580403905</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.163460587672825</v>
+        <v>2.279364843621596</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.9479226008551453</v>
+        <v>1.086313128474422</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.429000660609993</v>
+        <v>3.512034977181559</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>2.85091112259381</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.71835411659268</v>
+        <v>-1.428593476720753</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.163213051642991</v>
+        <v>2.279117307591762</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.9479226008551453</v>
+        <v>1.086313128474422</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.419664683106898</v>
+        <v>3.502698999678464</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>3.009817248444979</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.716629073302636</v>
+        <v>-1.426868433430709</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.322809194810177</v>
+        <v>2.438713450758948</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9496476441451891</v>
+        <v>1.088038171764466</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.579605834932093</v>
+        <v>3.662640151503659</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>3.779933725644412</v>
       </c>
       <c r="C2000" t="n">
         <v>3.046895070938626</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.871410080080892</v>
+        <v>-1.581649440208964</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.297974614592522</v>
+        <v>2.413878870541293</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9162799700907129</v>
+        <v>1.054670497709989</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.596663052993054</v>
+        <v>3.67969736956462</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>3.043570426928171</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.819974746696232</v>
+        <v>-1.530214106824305</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.315224103935931</v>
+        <v>2.431128359884702</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9677153034753726</v>
+        <v>1.106105831094649</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.624199609013395</v>
+        <v>3.707233925584961</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>3.053576580572912</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.793023522369744</v>
+        <v>-1.503262882497817</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.336010747311267</v>
+        <v>2.451915003260039</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9825956495030918</v>
+        <v>1.120986177122368</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.643133970274768</v>
+        <v>3.726168286846334</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784107</v>
       </c>
       <c r="C2003" t="n">
         <v>3.237679712717872</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.92897653042606</v>
+        <v>-1.639215890554133</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.465732676233701</v>
+        <v>2.581636932182472</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9825956495030918</v>
+        <v>1.120986177122368</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.827237102419728</v>
+        <v>3.910271418991293</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.229796407620865</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.951384648230932</v>
+        <v>-1.661624008359005</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.448886124014745</v>
+        <v>2.564790379963516</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9825956495030918</v>
+        <v>1.120986177122368</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.819353797322721</v>
+        <v>3.902388113894287</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
         <v>3.231850407170503</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.099390415710332</v>
+        <v>-1.809629775838404</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.391737816572623</v>
+        <v>2.507642072521394</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.8958686406395503</v>
+        <v>1.034259168258827</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.769371591554233</v>
+        <v>3.852405908125799</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
         <v>3.28810412489235</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.108831341598862</v>
+        <v>-1.819070701726934</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.444215163939058</v>
+        <v>2.560119419887829</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.018295758182942</v>
+        <v>1.156686285802218</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.899081579802115</v>
+        <v>3.982115896373681</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321632</v>
+        <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
         <v>3.290995219437651</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.107544578059305</v>
+        <v>-1.817783938187377</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.447620963900182</v>
+        <v>2.563525219848953</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.019582521722498</v>
+        <v>1.157973049341775</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.90274473247115</v>
+        <v>3.985779049042716</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
         <v>3.289107032331426</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.109101632048596</v>
+        <v>-1.819340992176669</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.44510995519824</v>
+        <v>2.561014211147011</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.019582521722498</v>
+        <v>1.157973049341775</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.900856545364925</v>
+        <v>3.983890861936491</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.283927261934288</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.116373517572061</v>
+        <v>-1.826612877700134</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.437021430591717</v>
+        <v>2.552925686540488</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.012310636199033</v>
+        <v>1.15070116381831</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.891313643653709</v>
+        <v>3.974347960225274</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
         <v>3.282361272144441</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.11453249851381</v>
+        <v>-1.824771858641882</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.436191848425169</v>
+        <v>2.55209610437394</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.013578862870502</v>
+        <v>1.151969390489778</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.890508589866742</v>
+        <v>3.973542906438308</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647103</v>
+        <v>3.754911907647105</v>
       </c>
       <c r="C2011" t="n">
         <v>3.295434679010359</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.12144120401349</v>
+        <v>-1.831680564141563</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.446501773091216</v>
+        <v>2.562406029039987</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.013578862870502</v>
+        <v>1.151969390489778</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.903581996732661</v>
+        <v>3.986616313304227</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74989685176353</v>
+        <v>3.749896851763531</v>
       </c>
       <c r="C2012" t="n">
         <v>3.295434679010359</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.12300284682835</v>
+        <v>-1.833242206956422</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.445877115965272</v>
+        <v>2.561781371914043</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.013578862870502</v>
+        <v>1.151969390489778</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.903581996732661</v>
+        <v>3.986616313304227</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392113</v>
+        <v>3.715834055392115</v>
       </c>
       <c r="C2013" t="n">
         <v>3.293958720137361</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.150903633937823</v>
+        <v>-1.861142994065895</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.433240842248485</v>
+        <v>2.549145098197256</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.9789819387275672</v>
+        <v>1.117372466346843</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.881347883373902</v>
+        <v>3.964382199945468</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172524</v>
+        <v>3.684909939172526</v>
       </c>
       <c r="C2014" t="n">
         <v>3.29072316411456</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.153936631450497</v>
+        <v>-1.864175991578569</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.428792087220614</v>
+        <v>2.544696343169385</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.9759489412148934</v>
+        <v>1.114339468834169</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.876292528843496</v>
+        <v>3.959326845415062</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971077</v>
+        <v>3.619362241971079</v>
       </c>
       <c r="C2015" t="n">
         <v>3.357429123705064</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.173997952727004</v>
+        <v>-1.884237312855076</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.487473518300515</v>
+        <v>2.603377774249286</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.9558876199383863</v>
+        <v>1.094278147557662</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.930961695668096</v>
+        <v>4.013996012239661</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199804</v>
+        <v>3.640764248199805</v>
       </c>
       <c r="C2016" t="n">
         <v>3.497740842706911</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.430718770721828</v>
+        <v>-2.1409581308499</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.525096910104432</v>
+        <v>2.641001166053203</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.8474730457945715</v>
+        <v>0.9858635734138476</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.006224670183654</v>
+        <v>4.08925898675522</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622235</v>
+        <v>3.668303164622237</v>
       </c>
       <c r="C2017" t="n">
         <v>3.566721111852551</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.584705188497968</v>
+        <v>-2.294944548626041</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.532482612139616</v>
+        <v>2.648386868088387</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.8474730457945715</v>
+        <v>0.9858635734138476</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.075204939329294</v>
+        <v>4.15823925590086</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808527</v>
+        <v>3.619937176808529</v>
       </c>
       <c r="C2018" t="n">
         <v>3.552772313972671</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.534183284670303</v>
+        <v>-2.244422644798375</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.538742575790804</v>
+        <v>2.654646831739574</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.8474730457945715</v>
+        <v>0.9858635734138476</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.061256141449414</v>
+        <v>4.14429045802098</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994892</v>
+        <v>3.656346893994894</v>
       </c>
       <c r="C2019" t="n">
         <v>3.564642803028085</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.786658438678027</v>
+        <v>-2.496897798806099</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.449623003243127</v>
+        <v>2.565527259191899</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.8474730457945715</v>
+        <v>0.9858635734138476</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.073126630504829</v>
+        <v>4.156160947076394</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358296</v>
+        <v>3.674042696358297</v>
       </c>
       <c r="C2020" t="n">
         <v>3.565853337547029</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.056131240599735</v>
+        <v>-2.766370600727807</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.343044416993388</v>
+        <v>2.458948672942159</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.8474730457945715</v>
+        <v>0.9858635734138476</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.074337165023772</v>
+        <v>4.157371481595338</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637084</v>
+        <v>3.663523617637086</v>
       </c>
       <c r="C2021" t="n">
         <v>3.569975079774351</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.213675312329177</v>
+        <v>-2.923914672457248</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.284148530528933</v>
+        <v>2.400052786477704</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.7805712406542971</v>
+        <v>0.9189617682735731</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.03831782416693</v>
+        <v>4.121352140738495</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.482255899460319</v>
+        <v>3.868366238537586</v>
       </c>
       <c r="C2022" t="n">
         <v>3.56505293251054</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.342525863031223</v>
+        <v>-3.052765223159295</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.227686162984304</v>
+        <v>2.343590418933075</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.7395778318035755</v>
+        <v>0.8779683594228516</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.008799631592685</v>
+        <v>4.091833948164251</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240712.xlsx
+++ b/tame_output/ON/bt/strategyON_20240712.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>53.4%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-69.9%</t>
+          <t>-71.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.6%</t>
+          <t>109.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>120.9%</t>
+          <t>122.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.0%</t>
+          <t>-50.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-64.4%</t>
+          <t>-66.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.8%</t>
+          <t>457.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-466.8%</t>
+          <t>-480.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,22 +1102,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,32 +1150,32 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.9%</t>
+          <t>-35.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-141.9%</t>
+          <t>-147.3%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-11.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,16 +1242,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-28.1%</t>
+          <t>-28.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>124.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-130.0%</t>
+          <t>-124.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-136.2%</t>
+          <t>-150.0%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>94.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1471,42 +1471,42 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.2%</t>
+          <t>-25.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.9%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-36.8%</t>
+          <t>-81.7%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2022"/>
+  <dimension ref="A1:G2023"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.076625841947135</v>
+        <v>-7.339982228858227</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2861553937299917</v>
+        <v>0.1808128389655548</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.019894149117834</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.505225665351893</v>
+        <v>2.422191348780327</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.263345550256438</v>
+        <v>-7.526701937167529</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.2074412058718673</v>
+        <v>0.1020986511074309</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.019894149117834</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.501199360817489</v>
+        <v>2.418165044245924</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.646346938999069</v>
+        <v>-7.909703325910161</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.0541385490532309</v>
+        <v>-0.05120400571120598</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.019894149117834</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.501097259495905</v>
+        <v>2.41806294292434</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.828216729984105</v>
+        <v>-8.091573116895196</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.0160378513693531</v>
+        <v>-0.12138040613379</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.201763940102869</v>
+        <v>-1.340154467722146</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.394546900876314</v>
+        <v>2.311512584304749</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.187747052488106</v>
+        <v>-8.451103439399198</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1544996770729039</v>
+        <v>-0.2598422318373403</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.201763940102869</v>
+        <v>-1.340154467722146</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.399897204174365</v>
+        <v>2.316862887602799</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.238096115942328</v>
+        <v>-8.50145250285342</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.166723282497415</v>
+        <v>-0.2720658372618519</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.252113003557092</v>
+        <v>-1.390503531176368</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.377603786059009</v>
+        <v>2.294569469487443</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.335715393363724</v>
+        <v>-8.599071780274816</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2027292428442045</v>
+        <v>-0.3080717976086413</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.349732280978488</v>
+        <v>-1.488122808597764</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.32207397022794</v>
+        <v>2.239039653656374</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.483241481369367</v>
+        <v>-8.746597868280459</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.2588461217248894</v>
+        <v>-0.3641886764893263</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.497258368984132</v>
+        <v>-1.635648896603408</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.236451873746126</v>
+        <v>2.15341755717456</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.687499656699231</v>
+        <v>-8.950856043610322</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3350361947381928</v>
+        <v>-0.4403787495026292</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.624897313598121</v>
+        <v>-1.763287841217397</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.165381704096375</v>
+        <v>2.082347387524809</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.721152495207704</v>
+        <v>-8.984508882118796</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3440147756571461</v>
+        <v>-0.4493573304215825</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.725310681515158</v>
+        <v>-1.863701209134434</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.109616237830588</v>
+        <v>2.026581921259023</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.647682663540255</v>
+        <v>-8.911039050451347</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2992551414967455</v>
+        <v>-0.4045976962611819</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.65184084984771</v>
+        <v>-1.790231377466986</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.169069838324479</v>
+        <v>2.086035521752913</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.822807080926799</v>
+        <v>-9.08616346783789</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3547496877038459</v>
+        <v>-0.4600922424682823</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.826965267234253</v>
+        <v>-1.965355794853529</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.078550408640069</v>
+        <v>1.995516092068503</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.057259174941288</v>
+        <v>-9.32061556185238</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4557496902112379</v>
+        <v>-0.5610922449756743</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.826965267234253</v>
+        <v>-1.965355794853529</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.071331243738473</v>
+        <v>1.988296927166908</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.161633905967735</v>
+        <v>-9.424990292878826</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5041717733957927</v>
+        <v>-0.6095143281602291</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.931339998260699</v>
+        <v>-2.069730525879975</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.00203421434863</v>
+        <v>1.918999897777064</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.214420061568061</v>
+        <v>-9.477776448479153</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5241704457973668</v>
+        <v>-0.6295130005618033</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.027015484843096</v>
+        <v>-2.165406012462372</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.945744712237747</v>
+        <v>1.862710395666182</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.340456854936351</v>
+        <v>-9.603813241847442</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5718914345155679</v>
+        <v>-0.6772339892800043</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.001763862033354</v>
+        <v>-2.14015438965263</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.963589414552708</v>
+        <v>1.880555097981142</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.28338508304042</v>
+        <v>-9.546741469951511</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5450723900707946</v>
+        <v>-0.6504149448352314</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.001763862033354</v>
+        <v>-2.14015438965263</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.967579750239109</v>
+        <v>1.884545433667543</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.42505692476454</v>
+        <v>-9.688413311675632</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6032163536591844</v>
+        <v>-0.7085589084236212</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.001763862033354</v>
+        <v>-2.14015438965263</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.966104523340367</v>
+        <v>1.883070206768801</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.375466080339706</v>
+        <v>-9.638822467250797</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5683266057243785</v>
+        <v>-0.673669160488815</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.95217301760852</v>
+        <v>-2.090563545227796</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.01091244016014</v>
+        <v>1.927878123588574</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.226547745867849</v>
+        <v>-9.489904132778941</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5218104055823187</v>
+        <v>-0.6271529603467556</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.920923426873347</v>
+        <v>-2.059313954492623</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.01661106095456</v>
+        <v>1.933576744382995</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.000702593148439</v>
+        <v>-9.264058980059531</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4218932714583463</v>
+        <v>-0.5272358262227828</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.878996751286183</v>
+        <v>-2.017387278905459</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.051346139343067</v>
+        <v>1.968311822771502</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.876123936810847</v>
+        <v>-9.139480323721939</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3709226643672507</v>
+        <v>-0.4762652191316872</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.878996751286183</v>
+        <v>-2.017387278905459</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.052485283899126</v>
+        <v>1.96945096732756</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.929019224855134</v>
+        <v>-9.192375611766225</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3894470054228574</v>
+        <v>-0.4947895601872943</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.874041405197737</v>
+        <v>-2.012431932817013</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.058092265714301</v>
+        <v>1.975057949142736</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.856886049567253</v>
+        <v>-9.120242436478344</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3548600310690686</v>
+        <v>-0.460202585833505</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.874041405197737</v>
+        <v>-2.012431932817013</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.063825969952938</v>
+        <v>1.980791653381372</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.785519656957606</v>
+        <v>-9.048876043868697</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3360507364190748</v>
+        <v>-0.4413932911835117</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.802675012588089</v>
+        <v>-1.941065540207365</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.096908543124862</v>
+        <v>2.013874226553296</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.692060622972381</v>
+        <v>-8.955417009883472</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3085506041378925</v>
+        <v>-0.4138931589023294</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.802675012588089</v>
+        <v>-1.941065540207365</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.087025061811954</v>
+        <v>2.003990745240388</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.424818822103983</v>
+        <v>-8.688175209015075</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2034884442899072</v>
+        <v>-0.3088309990543441</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.802675012588089</v>
+        <v>-1.941065540207365</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.08519050131258</v>
+        <v>2.002156184741015</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.326911783427493</v>
+        <v>-8.590268170338584</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.164625943792772</v>
+        <v>-0.2699684985572084</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.734689262727533</v>
+        <v>-1.873079790346809</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.125681636255453</v>
+        <v>2.042647319683887</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.302958242451535</v>
+        <v>-8.566314629362626</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.154376021256895</v>
+        <v>-0.2597185760213319</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.710735721751575</v>
+        <v>-1.849126249370851</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.140722266986521</v>
+        <v>2.057687950414956</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.038898304128738</v>
+        <v>-8.302254691039829</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.06201236208952832</v>
+        <v>-0.1673549168539652</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.446675783428779</v>
+        <v>-1.585066311048055</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.285897913818447</v>
+        <v>2.202863597246881</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.3318186806239</v>
+        <v>-7.595175067534991</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2180324536521061</v>
+        <v>0.1126898988876692</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.446675783428779</v>
+        <v>-1.585066311048055</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.283110880158146</v>
+        <v>2.20007656358658</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.291634382257709</v>
+        <v>-7.554990769168801</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2344497968864236</v>
+        <v>0.1291072421219868</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.406491485062588</v>
+        <v>-1.544882012681864</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.307565083065702</v>
+        <v>2.224530766494136</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.128234511318347</v>
+        <v>-7.391590898229438</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2991765664829256</v>
+        <v>0.1938340117184887</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.243091614123226</v>
+        <v>-1.381482141742502</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.404971826850076</v>
+        <v>2.321937510278511</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.894753289088748</v>
+        <v>-7.15810967599984</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4004934842126171</v>
+        <v>0.2951509294481807</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.009610391893627</v>
+        <v>-1.148000919512903</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.552984989025688</v>
+        <v>2.469950672454122</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.745086898081233</v>
+        <v>-7.008443284992325</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4574678303026642</v>
+        <v>0.3521252755382274</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.9167069006510913</v>
+        <v>-1.055097428270367</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.60583487345825</v>
+        <v>2.522800556886684</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.612811424450347</v>
+        <v>-6.876167811361438</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.5057455065020457</v>
+        <v>0.4004029517376089</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.7844314270202046</v>
+        <v>-0.9228219546394807</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.680567644383809</v>
+        <v>2.597533327812243</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.457073091890605</v>
+        <v>-6.720429478801696</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5708559002135791</v>
+        <v>0.4655133454491427</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.6286930944604631</v>
+        <v>-0.7670836220797391</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.776825704607291</v>
+        <v>2.693791388035725</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.208073293207024</v>
+        <v>-6.471429680118115</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6833621609106704</v>
+        <v>0.5780196061462335</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.6286930944604631</v>
+        <v>-0.7670836220797391</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.78973204583095</v>
+        <v>2.706697729259384</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.313663282980128</v>
+        <v>-6.57701966989122</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.5131502354022097</v>
+        <v>0.4078076806377733</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.7342830842335675</v>
+        <v>-0.8726736118528435</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.598402122367868</v>
+        <v>2.515367805796302</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.332398185098725</v>
+        <v>-6.595754572009817</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5542006164318574</v>
+        <v>0.4488580616674209</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.7398790938936988</v>
+        <v>-0.8782696215129748</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.643588858448876</v>
+        <v>2.56055454187731</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.184458143691126</v>
+        <v>-6.447814530602217</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4934977103067295</v>
+        <v>0.3881551555422931</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.7195581779851412</v>
+        <v>-0.8579487056044173</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.535902485305843</v>
+        <v>2.452868168734277</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.131488621437137</v>
+        <v>-6.394845008348229</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.5059715329548466</v>
+        <v>0.4006289781904102</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.6665886557311523</v>
+        <v>-0.8049791833504284</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.558970212404758</v>
+        <v>2.475935895833192</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.087940214666447</v>
+        <v>-6.351296601577539</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.5164302835680297</v>
+        <v>0.4110877288035932</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.6665886557311523</v>
+        <v>-0.8049791833504284</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.552009600309665</v>
+        <v>2.468975283738099</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-5.845791821212589</v>
+        <v>-6.10914820812368</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.627751995330716</v>
+        <v>0.5224094405662796</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.6665886557311523</v>
+        <v>-0.8049791833504284</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.566471954690808</v>
+        <v>2.483437638119242</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.737532684090067</v>
+        <v>-6.000889071001159</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.6655877706389197</v>
+        <v>0.5602452158744833</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.6665886557311523</v>
+        <v>-0.8049791833504284</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.561004075150003</v>
+        <v>2.477969758578437</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.614241549272936</v>
+        <v>-5.877597936184028</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.7124023185763493</v>
+        <v>0.6070597638119124</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.5432975209140218</v>
+        <v>-0.6816880485332979</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.632476850050858</v>
+        <v>2.549442533479292</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.593092350369493</v>
+        <v>-5.856448737280584</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.7285629763750516</v>
+        <v>0.6232204216106152</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.5221483220105785</v>
+        <v>-0.6605388496298545</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.652867347630249</v>
+        <v>2.569833031058684</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.349326908386049</v>
+        <v>-5.61268329529714</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.8218498615154801</v>
+        <v>0.7165073067510432</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.5221483220105785</v>
+        <v>-0.6605388496298545</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.6486480559773</v>
+        <v>2.565613739405734</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.247564088108754</v>
+        <v>-5.510920475019845</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.864679303546414</v>
+        <v>0.7593367487819775</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.5089292536181498</v>
+        <v>-0.6473197812374258</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.658703810932773</v>
+        <v>2.575669494361208</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-4.997713694159679</v>
+        <v>-5.261070081070771</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.9573615361097461</v>
+        <v>0.8520189813453092</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.5089292536181498</v>
+        <v>-0.6473197812374258</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.651445885916475</v>
+        <v>2.56841156934491</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.821821601692246</v>
+        <v>-5.085177988603338</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.031317496617368</v>
+        <v>0.9259749418529313</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.5089292536181498</v>
+        <v>-0.6473197812374258</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.655045009437124</v>
+        <v>2.572010692865558</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.650375138669783</v>
+        <v>-4.913731525580874</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.113223587880907</v>
+        <v>1.00788103311647</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.3374827905956866</v>
+        <v>-0.4758733182149627</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.771240393305156</v>
+        <v>2.68820607673359</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.576085572931444</v>
+        <v>-4.839441959842535</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.14195989179254</v>
+        <v>1.036617337028103</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.2631932248573474</v>
+        <v>-0.4015837524766234</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.814834610364456</v>
+        <v>2.731800293792891</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.512449830697509</v>
+        <v>-4.775806217608601</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.172108989740431</v>
+        <v>1.066766434975994</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.1995574826234128</v>
+        <v>-0.3379480102426889</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.857710856759134</v>
+        <v>2.774676540187568</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.401023071371589</v>
+        <v>-4.664379458282681</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.197873952254594</v>
+        <v>1.092531397490158</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.1995574826234128</v>
+        <v>-0.3379480102426889</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.83890511554293</v>
+        <v>2.755870798971364</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.160592574566729</v>
+        <v>-4.42394896147782</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.295789227601416</v>
+        <v>1.190446672836979</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.04087301418144745</v>
+        <v>-0.09751751343782861</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.984906490250723</v>
+        <v>2.901872173679158</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.088350006395534</v>
+        <v>-4.351706393306626</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.328615568704714</v>
+        <v>1.223273013940277</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.04087301418144745</v>
+        <v>-0.09751751343782861</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.988835804085543</v>
+        <v>2.905801487513978</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.035351684114146</v>
+        <v>-4.298708071025238</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.350493481534609</v>
+        <v>1.245150926770172</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.09620927318338629</v>
+        <v>-0.04218125443588977</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.022716143404047</v>
+        <v>2.939681826832481</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-3.92654679863442</v>
+        <v>-4.062313749578975</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.391013506946493</v>
+        <v>1.336706726568671</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.09620927318338629</v>
+        <v>-0.04218125443588977</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.01971421462404</v>
+        <v>2.936679898052475</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.706526000597409</v>
+        <v>-3.842292951541964</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.480600863171912</v>
+        <v>1.426294082794089</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.2374291182513665</v>
+        <v>0.09903859063209047</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.106025158675442</v>
+        <v>3.022990842103877</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.57365831153413</v>
+        <v>-3.709425262478686</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.549642121599046</v>
+        <v>1.495335341221224</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.2374291182513665</v>
+        <v>0.09903859063209047</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.121919341477266</v>
+        <v>3.0388850249057</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.453485228169631</v>
+        <v>-3.589252179114188</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.598857199385148</v>
+        <v>1.544550419007325</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.3576022016158655</v>
+        <v>0.2192116739965894</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.195169035936267</v>
+        <v>3.112134719364701</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.308813083069894</v>
+        <v>-3.44458003401445</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.666814159986483</v>
+        <v>1.61250737960866</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5022743467156029</v>
+        <v>0.3638838190963268</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.292060425557549</v>
+        <v>3.209026108985984</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.368687910427586</v>
+        <v>-3.504454861372142</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.628901720444832</v>
+        <v>1.574594940067009</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.4423995193579108</v>
+        <v>0.3040089917386347</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.24217302054436</v>
+        <v>3.159138703972794</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.248867679516749</v>
+        <v>-3.384634630461305</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.692118982043375</v>
+        <v>1.637812201665553</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.4423995193579108</v>
+        <v>0.3040089917386347</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.257462189778569</v>
+        <v>3.174427873207003</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.251337385978555</v>
+        <v>-3.387104336923111</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.598775298781094</v>
+        <v>1.544468518403272</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.4399298128961046</v>
+        <v>0.3015392852768286</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.163624565223926</v>
+        <v>3.080590248652361</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.319707572302565</v>
+        <v>-3.455474523247121</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.490689085736792</v>
+        <v>1.436382305358969</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.4492055119323196</v>
+        <v>0.3108149843130435</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.088451846130957</v>
+        <v>3.005417529559391</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.333495625149611</v>
+        <v>-3.469262576094168</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.475610573229864</v>
+        <v>1.421303792852042</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.4492055119323196</v>
+        <v>0.3108149843130435</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.078888554762848</v>
+        <v>2.995854238191282</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.364488784478317</v>
+        <v>-3.500255735422873</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.287922874538769</v>
+        <v>1.233616094160946</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.4492055119323196</v>
+        <v>0.3108149843130435</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.903598119803235</v>
+        <v>2.820563803231669</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.189014524685847</v>
+        <v>-3.324781475630404</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.362679810447544</v>
+        <v>1.308373030069722</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.4492055119323196</v>
+        <v>0.3108149843130435</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.908165351795023</v>
+        <v>2.825131035223457</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.299950777327096</v>
+        <v>-3.435717728271652</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.294047338152252</v>
+        <v>1.23974055777443</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.4492055119323196</v>
+        <v>0.3108149843130435</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.88390738055623</v>
+        <v>2.800873063984664</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.617515458616743</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.266287231854814</v>
+        <v>-3.40205418279937</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.31064414156107</v>
+        <v>1.256337361183248</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.4828690574046014</v>
+        <v>0.3444785297853253</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.907236893059504</v>
+        <v>2.824202576487939</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.627687845048876</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.206434612651091</v>
+        <v>-3.342201563595647</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.344757575674692</v>
+        <v>1.29045079529687</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.4828690574046014</v>
+        <v>0.3444785297853253</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.917409279491637</v>
+        <v>2.834374962920071</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.622634115622736</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.120191149624714</v>
+        <v>-3.25595810056927</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.374201231459103</v>
+        <v>1.319894451081281</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.4828690574046014</v>
+        <v>0.3444785297853253</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.912355550065497</v>
+        <v>2.829321233493931</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.614409891067262</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.165497969023694</v>
+        <v>-3.30126491996825</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.347854279144037</v>
+        <v>1.293547498766214</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.4420588943953706</v>
+        <v>0.3036683667760945</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.879645227704484</v>
+        <v>2.796610911132919</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.614961764100363</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.194531073725995</v>
+        <v>-3.330298024670551</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.336792910296218</v>
+        <v>1.282486129918395</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.4420588943953706</v>
+        <v>0.3036683667760945</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.880197100737586</v>
+        <v>2.79716278416602</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.544234455991729</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.101720592275136</v>
+        <v>-3.237487543219692</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.303189794767927</v>
+        <v>1.248883014390105</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.53486937584623</v>
+        <v>0.3964788482269539</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.865156081499467</v>
+        <v>2.782121764927902</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.54610793191633</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.146110061604563</v>
+        <v>-3.28187701254912</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.287307482960757</v>
+        <v>1.233000702582934</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.4904799065168023</v>
+        <v>0.3520893788975262</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.840395875826411</v>
+        <v>2.757361559254845</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.541183640428053</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.033438843368313</v>
+        <v>-3.16920579431287</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.32745167876698</v>
+        <v>1.273144898389158</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6031511247530525</v>
+        <v>0.4647605971337764</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.903074315279884</v>
+        <v>2.820039998708319</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.54667493625872</v>
       </c>
       <c r="D1949" t="n">
-        <v>-2.921061842185641</v>
+        <v>-3.056828793130197</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.377893775070716</v>
+        <v>1.323586994692894</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6031511247530525</v>
+        <v>0.4647605971337764</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.908565611110552</v>
+        <v>2.825531294538986</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.558172138027259</v>
       </c>
       <c r="D1950" t="n">
-        <v>-2.948842240086994</v>
+        <v>-3.08460919103155</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.378278817678714</v>
+        <v>1.323972037300892</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.5753707268516994</v>
+        <v>0.4369801992324234</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.903394574138279</v>
+        <v>2.820360257566713</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.396527858027912</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.031843521112273</v>
+        <v>-3.167610472056829</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.183434025269256</v>
+        <v>1.129127244891433</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5567998423245257</v>
+        <v>0.4184093147052496</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.730607763422628</v>
+        <v>2.647573446851062</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.516677518747118</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.140457599555604</v>
+        <v>-3.27622455050016</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.260138054611129</v>
+        <v>1.205831274233306</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5567998423245257</v>
+        <v>0.4184093147052496</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.850757424141833</v>
+        <v>2.767723107570268</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.105048561307461</v>
+        <v>-3.240815512252017</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.288814696012709</v>
+        <v>1.234507915634887</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5567998423245257</v>
+        <v>0.4184093147052496</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.865270450244156</v>
+        <v>2.782236133672591</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.06666489874931</v>
+        <v>-3.202431849693866</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.301587602378338</v>
+        <v>1.247280822000516</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.5951835048826769</v>
+        <v>0.4567929772634008</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.885720089121416</v>
+        <v>2.80268577254985</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-2.889548568714144</v>
+        <v>-3.0253155196587</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.369163163237707</v>
+        <v>1.314856382859884</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.5951835048826769</v>
+        <v>0.4567929772634008</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.882449117966718</v>
+        <v>2.799414801395153</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-2.93464081354769</v>
+        <v>-3.070407764492246</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.351809657066202</v>
+        <v>1.297502876688379</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5332874617132871</v>
+        <v>0.394896934094011</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.845994883826998</v>
+        <v>2.762960567255432</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-2.755265392308922</v>
+        <v>-2.891032343253478</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.417346800868123</v>
+        <v>1.363040020490301</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6900642198840058</v>
+        <v>0.5516736922647296</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.933847914035843</v>
+        <v>2.850813597464277</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-2.800279605829528</v>
+        <v>-2.936046556774084</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.38014857079147</v>
+        <v>1.325841790413648</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6597153245694012</v>
+        <v>0.521324796950125</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.89644603217867</v>
+        <v>2.813411715607104</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.067284116101963</v>
+        <v>-3.20305106704652</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.279038329021442</v>
+        <v>1.22473154864362</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4653522865264526</v>
+        <v>0.3269617589071764</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.785519771691847</v>
+        <v>2.702485455120281</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.168481897539136</v>
+        <v>-3.304248848483692</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.237763138343074</v>
+        <v>1.183456357965252</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3969434729811334</v>
+        <v>0.2585529453618572</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.743678405461156</v>
+        <v>2.660644088889591</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.161970930924824</v>
+        <v>-3.29773788186938</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.237967486543116</v>
+        <v>1.183660706165294</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3969434729811334</v>
+        <v>0.2585529453618572</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.741278367015473</v>
+        <v>2.658244050443908</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.142932803217526</v>
+        <v>-3.278699754162083</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.24210745683428</v>
+        <v>1.187800676456457</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3387598616499389</v>
+        <v>0.2003693340306627</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.702892919425001</v>
+        <v>2.619858602853436</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.174059434368144</v>
+        <v>-3.309826385312701</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.407238673312713</v>
+        <v>1.352931892934891</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3387598616499389</v>
+        <v>0.2003693340306627</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.880474788363682</v>
+        <v>2.797440471792116</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.187926195702062</v>
+        <v>-3.323693146646618</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.40252529776528</v>
+        <v>1.348218517387457</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3009019449161159</v>
+        <v>0.1625114172968398</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.858593367309522</v>
+        <v>2.775559050737956</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.143122024162132</v>
+        <v>-3.278888975106688</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.426455496778178</v>
+        <v>1.372148716400355</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3009019449161159</v>
+        <v>0.1625114172968398</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.864601897706448</v>
+        <v>2.781567581134882</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.582010952033977</v>
       </c>
       <c r="D1966" t="n">
-        <v>-2.99537905392713</v>
+        <v>-3.131146004871686</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.383502906149378</v>
+        <v>1.329196125771556</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4687093021509991</v>
+        <v>0.3303187745317229</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.863236533324577</v>
+        <v>2.780202216753011</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.584804573565458</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.097393736458351</v>
+        <v>-3.233160687402907</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.345490654668371</v>
+        <v>1.291183874290548</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4687093021509991</v>
+        <v>0.3303187745317229</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.866030154856058</v>
+        <v>2.782995838284492</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.585466921957117</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.091241030405566</v>
+        <v>-3.227007981350122</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.348614085481143</v>
+        <v>1.29430730510332</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4748620082037834</v>
+        <v>0.3364714805845072</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.870384126879387</v>
+        <v>2.787349810307821</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.584547398697227</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.108050328556068</v>
+        <v>-3.243817279500624</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.340970842961053</v>
+        <v>1.28666406258323</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4580527100532817</v>
+        <v>0.3196621824340056</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.859379024729196</v>
+        <v>2.776344708157631</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.650882952494048</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.045752329779946</v>
+        <v>-3.181519280724502</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.432225596268322</v>
+        <v>1.3779188158905</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4580527100532817</v>
+        <v>0.3196621824340056</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.925714578526017</v>
+        <v>2.842680261954452</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.453174954208175</v>
       </c>
       <c r="D1971" t="n">
-        <v>-2.843962132114788</v>
+        <v>-2.979729083059344</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.315233677048512</v>
+        <v>1.26092689667069</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6560709022224361</v>
+        <v>0.51768037460316</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.846817495541637</v>
+        <v>2.763783178970071</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.52346518653035</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.679149129035941</v>
+        <v>-2.814916079980497</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.451449110602226</v>
+        <v>1.397142330224404</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.8208839053012831</v>
+        <v>0.6824933776820069</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.01599552971112</v>
+        <v>2.932961213139555</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.538092922646394</v>
       </c>
       <c r="D1973" t="n">
-        <v>-2.776889673660915</v>
+        <v>-2.912656624605471</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.42698062886828</v>
+        <v>1.372673848490458</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8049946271683028</v>
+        <v>0.6666040995490268</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.021089698947375</v>
+        <v>2.93805538237581</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.536628903471065</v>
       </c>
       <c r="D1974" t="n">
-        <v>-2.953227433783844</v>
+        <v>-3.088994384728401</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.35498150564378</v>
+        <v>1.300674725265958</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6286568670453734</v>
+        <v>0.4902663394260973</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.91382302369829</v>
+        <v>2.830788707126724</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.535120521510994</v>
       </c>
       <c r="D1975" t="n">
-        <v>-2.876805387351918</v>
+        <v>-3.012572338296474</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.38404194225648</v>
+        <v>1.329735161878657</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6286568670453734</v>
+        <v>0.4902663394260973</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.912314641738218</v>
+        <v>2.829280325166653</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.53498338894643</v>
       </c>
       <c r="D1976" t="n">
-        <v>-2.832432255713349</v>
+        <v>-2.968199206657905</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.401654062347343</v>
+        <v>1.347347281969521</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.673029998683942</v>
+        <v>0.5346394710646659</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.938801388156795</v>
+        <v>2.85576707158523</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.529377183085021</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.709598034826182</v>
+        <v>-2.845364985770738</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.445181544840801</v>
+        <v>1.390874764462978</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.673029998683942</v>
+        <v>0.5346394710646659</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.933195182295386</v>
+        <v>2.85016086572382</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.535758940112825</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.661942304265126</v>
+        <v>-2.797709255209682</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.470625594093028</v>
+        <v>1.416318813715205</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.7206857292449976</v>
+        <v>0.5822952016257216</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.968170377659824</v>
+        <v>2.885136061088259</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.54065131348755</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.561424145766371</v>
+        <v>-2.697191096710927</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.515725230867254</v>
+        <v>1.461418450489432</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8212038877437522</v>
+        <v>0.6828133601244761</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.033373646133802</v>
+        <v>2.950339329562236</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.527405985963422</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.62209073616876</v>
+        <v>-2.757857687113316</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.478213267182171</v>
+        <v>1.423906486804349</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7395055710252185</v>
+        <v>0.6011150434059425</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.971109328578554</v>
+        <v>2.888075012006988</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.531503688574051</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.577252334560362</v>
+        <v>-2.713019285504918</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.500246330436159</v>
+        <v>1.445939550058336</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.744049003970088</v>
+        <v>0.6056584763508119</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.977933090956104</v>
+        <v>2.894898774384538</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.535664628205129</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.678010970317361</v>
+        <v>-2.813777921261917</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.464103815764437</v>
+        <v>1.409797035386615</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6552234352430826</v>
+        <v>0.5168329076238065</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.928798689350979</v>
+        <v>2.845764372779413</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.541544230732966</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.63380813323146</v>
+        <v>-2.769575084176016</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.487664553126635</v>
+        <v>1.433357772748812</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.699426272328983</v>
+        <v>0.561035744709707</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.961199994130356</v>
+        <v>2.87816567755879</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.539954231202214</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.670787160894903</v>
+        <v>-2.80655411183946</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.471282942530505</v>
+        <v>1.416976162152683</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7364001741203136</v>
+        <v>0.5980096465010375</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.981794335674402</v>
+        <v>2.898760019102836</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.591201996385253</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.512495743355631</v>
+        <v>-2.648262694300187</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.585847274729254</v>
+        <v>1.531540494351431</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7364001741203136</v>
+        <v>0.5980096465010375</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.033042100857442</v>
+        <v>2.950007784285876</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.589642700979506</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.304853739721155</v>
+        <v>-2.440620690665711</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.667344780777297</v>
+        <v>1.613038000399475</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9440421777547897</v>
+        <v>0.8056516501355137</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.15606800763238</v>
+        <v>3.073033691060815</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.584590929217776</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.253821646998627</v>
+        <v>-2.389588597943183</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.682705846104578</v>
+        <v>1.628399065726756</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9950742704773177</v>
+        <v>0.8566837428580416</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.181635491504167</v>
+        <v>3.098601174932602</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.601778333310481</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.188597465871421</v>
+        <v>-2.324364416815977</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.725982922648166</v>
+        <v>1.671676142270343</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.060298451604523</v>
+        <v>0.9219079239852472</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.237957404273196</v>
+        <v>3.15492308770163</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.597739305609762</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.151170445800287</v>
+        <v>-2.286937396744844</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.7369147029759</v>
+        <v>1.682607922598077</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.065549989633705</v>
+        <v>0.9271594620144289</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.237069299389985</v>
+        <v>3.154034982818419</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.598996097941002</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.171282101834996</v>
+        <v>-2.307049052779552</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.730126832893256</v>
+        <v>1.675820052515434</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.076577334631124</v>
+        <v>0.9381868070118481</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.244942498719677</v>
+        <v>3.161908182148111</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.759553868962213</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.117537287407791</v>
+        <v>-2.253304238352347</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.912182529685349</v>
+        <v>1.857875749307527</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.086640644071586</v>
+        <v>0.9482501164523101</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.411538255405165</v>
+        <v>3.328503938833599</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.87966677818003</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.093745718801649</v>
+        <v>-2.229512669746205</v>
       </c>
       <c r="E1992" t="n">
-        <v>2.041812066345623</v>
+        <v>1.987505285967801</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.110432212677729</v>
+        <v>0.9720416850584523</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.545926105786668</v>
+        <v>3.462891789215102</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.871374754193889</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.067661634537841</v>
+        <v>-2.203428585482397</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.043953676065005</v>
+        <v>1.989646895687183</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.110432212677729</v>
+        <v>0.9720416850584523</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.537634081800527</v>
+        <v>3.454599765228961</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.869567949777668</v>
       </c>
       <c r="D1994" t="n">
-        <v>-1.989530453688894</v>
+        <v>-2.12529740463345</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.073399343988364</v>
+        <v>2.019092563610541</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.184609023561413</v>
+        <v>1.046218495942137</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.580333363914517</v>
+        <v>3.497299047342951</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.88712235550446</v>
       </c>
       <c r="D1995" t="n">
-        <v>-1.980637992295611</v>
+        <v>-2.116404943240167</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.094510734272468</v>
+        <v>2.040203953894646</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.184609023561413</v>
+        <v>1.046218495942137</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.597887769641308</v>
+        <v>3.514853453069742</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.878977402909044</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.149114109265489</v>
+        <v>-2.284881060210045</v>
       </c>
       <c r="E1996" t="n">
-        <v>2.018975334889101</v>
+        <v>1.964668554511279</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.156661187844833</v>
+        <v>1.018270660225556</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.572974115615944</v>
+        <v>3.489939799044378</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.860247100096906</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.451314580403905</v>
+        <v>-1.587081531348462</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.279364843621596</v>
+        <v>2.225058063243774</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.086313128474422</v>
+        <v>0.9479226008551453</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.512034977181559</v>
+        <v>3.429000660609993</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.85091112259381</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.428593476720753</v>
+        <v>-1.564360427665309</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.279117307591762</v>
+        <v>2.224810527213939</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.086313128474422</v>
+        <v>0.9479226008551453</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.502698999678464</v>
+        <v>3.419664683106898</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.009817248444979</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.426868433430709</v>
+        <v>-1.562635384375265</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.438713450758948</v>
+        <v>2.384406670381126</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.088038171764466</v>
+        <v>0.9496476441451891</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.662640151503659</v>
+        <v>3.579605834932093</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.046895070938626</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.581649440208964</v>
+        <v>-1.717416391153521</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.413878870541293</v>
+        <v>2.35957209016347</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.054670497709989</v>
+        <v>0.9162799700907129</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.67969736956462</v>
+        <v>3.596663052993054</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.043570426928171</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.530214106824305</v>
+        <v>-1.665981057768861</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.431128359884702</v>
+        <v>2.376821579506879</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.106105831094649</v>
+        <v>0.9677153034753726</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.707233925584961</v>
+        <v>3.624199609013395</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.053576580572912</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.503262882497817</v>
+        <v>-1.639029833442373</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.451915003260039</v>
+        <v>2.397608222882216</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.120986177122368</v>
+        <v>0.9825956495030918</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.726168286846334</v>
+        <v>3.643133970274768</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.237679712717872</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.639215890554133</v>
+        <v>-1.774982841498689</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.581636932182472</v>
+        <v>2.527330151804649</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.120986177122368</v>
+        <v>0.9825956495030918</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.910271418991293</v>
+        <v>3.827237102419728</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.229796407620865</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.661624008359005</v>
+        <v>-1.797390959303561</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.564790379963516</v>
+        <v>2.510483599585694</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.120986177122368</v>
+        <v>0.9825956495030918</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.902388113894287</v>
+        <v>3.819353797322721</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.231850407170503</v>
       </c>
       <c r="D2005" t="n">
-        <v>-1.809629775838404</v>
+        <v>-1.945396726782961</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.507642072521394</v>
+        <v>2.453335292143571</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.034259168258827</v>
+        <v>0.8958686406395503</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.852405908125799</v>
+        <v>3.769371591554233</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.28810412489235</v>
       </c>
       <c r="D2006" t="n">
-        <v>-1.819070701726934</v>
+        <v>-1.95483765267149</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.560119419887829</v>
+        <v>2.505812639510006</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.156686285802218</v>
+        <v>1.018295758182942</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.982115896373681</v>
+        <v>3.899081579802115</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.290995219437651</v>
       </c>
       <c r="D2007" t="n">
-        <v>-1.817783938187377</v>
+        <v>-1.953550889131934</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.563525219848953</v>
+        <v>2.50921843947113</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.157973049341775</v>
+        <v>1.019582521722498</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.985779049042716</v>
+        <v>3.90274473247115</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.289107032331426</v>
       </c>
       <c r="D2008" t="n">
-        <v>-1.819340992176669</v>
+        <v>-1.955107943121225</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.561014211147011</v>
+        <v>2.506707430769189</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.157973049341775</v>
+        <v>1.019582521722498</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.983890861936491</v>
+        <v>3.900856545364925</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.283927261934288</v>
       </c>
       <c r="D2009" t="n">
-        <v>-1.826612877700134</v>
+        <v>-1.96237982864469</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.552925686540488</v>
+        <v>2.498618906162665</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.15070116381831</v>
+        <v>1.012310636199033</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.974347960225274</v>
+        <v>3.891313643653709</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.282361272144441</v>
       </c>
       <c r="D2010" t="n">
-        <v>-1.824771858641882</v>
+        <v>-1.960538809586438</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.55209610437394</v>
+        <v>2.497789323996118</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.151969390489778</v>
+        <v>1.013578862870502</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.973542906438308</v>
+        <v>3.890508589866742</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.295434679010359</v>
       </c>
       <c r="D2011" t="n">
-        <v>-1.831680564141563</v>
+        <v>-1.967447515086119</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.562406029039987</v>
+        <v>2.508099248662164</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.151969390489778</v>
+        <v>1.013578862870502</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.986616313304227</v>
+        <v>3.903581996732661</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.295434679010359</v>
       </c>
       <c r="D2012" t="n">
-        <v>-1.833242206956422</v>
+        <v>-1.969009157900979</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.561781371914043</v>
+        <v>2.507474591536221</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.151969390489778</v>
+        <v>1.013578862870502</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.986616313304227</v>
+        <v>3.903581996732661</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.293958720137361</v>
       </c>
       <c r="D2013" t="n">
-        <v>-1.861142994065895</v>
+        <v>-1.996909945010452</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.549145098197256</v>
+        <v>2.494838317819434</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.117372466346843</v>
+        <v>0.9789819387275672</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.964382199945468</v>
+        <v>3.881347883373902</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.29072316411456</v>
       </c>
       <c r="D2014" t="n">
-        <v>-1.864175991578569</v>
+        <v>-1.999942942523126</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.544696343169385</v>
+        <v>2.490389562791563</v>
       </c>
       <c r="F2014" t="n">
-        <v>1.114339468834169</v>
+        <v>0.9759489412148934</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.959326845415062</v>
+        <v>3.876292528843496</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.357429123705064</v>
       </c>
       <c r="D2015" t="n">
-        <v>-1.884237312855076</v>
+        <v>-2.020004263799632</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.603377774249286</v>
+        <v>2.549070993871464</v>
       </c>
       <c r="F2015" t="n">
-        <v>1.094278147557662</v>
+        <v>0.9558876199383863</v>
       </c>
       <c r="G2015" t="n">
-        <v>4.013996012239661</v>
+        <v>3.930961695668096</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.497740842706911</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.1409581308499</v>
+        <v>-2.276725081794456</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.641001166053203</v>
+        <v>2.586694385675381</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.9858635734138476</v>
+        <v>0.8474730457945715</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.08925898675522</v>
+        <v>4.006224670183654</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.566721111852551</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.294944548626041</v>
+        <v>-2.430711499570597</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.648386868088387</v>
+        <v>2.594080087710565</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.9858635734138476</v>
+        <v>0.8474730457945715</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.15823925590086</v>
+        <v>4.075204939329294</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.552772313972671</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.244422644798375</v>
+        <v>-2.380189595742931</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.654646831739574</v>
+        <v>2.600340051361752</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.9858635734138476</v>
+        <v>0.8474730457945715</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.14429045802098</v>
+        <v>4.061256141449414</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.564642803028085</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.496897798806099</v>
+        <v>-2.632664749750655</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.565527259191899</v>
+        <v>2.511220478814076</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.9858635734138476</v>
+        <v>0.8474730457945715</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.156160947076394</v>
+        <v>4.073126630504829</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.565853337547029</v>
       </c>
       <c r="D2020" t="n">
-        <v>-2.766370600727807</v>
+        <v>-2.902137551672364</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.458948672942159</v>
+        <v>2.404641892564336</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.9858635734138476</v>
+        <v>0.8474730457945715</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.157371481595338</v>
+        <v>4.074337165023772</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.569975079774351</v>
       </c>
       <c r="D2021" t="n">
-        <v>-2.923914672457248</v>
+        <v>-3.059681623401805</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.400052786477704</v>
+        <v>2.345746006099882</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.9189617682735731</v>
+        <v>0.7805712406542971</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.121352140738495</v>
+        <v>4.03831782416693</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,45 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.868366238537586</v>
+        <v>3.652163313301343</v>
       </c>
       <c r="C2022" t="n">
         <v>3.56505293251054</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.052765223159295</v>
+        <v>-3.188532174103851</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.343590418933075</v>
+        <v>2.289283638555252</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.8779683594228516</v>
+        <v>0.7395778318035755</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.091833948164251</v>
+        <v>4.008799631592685</v>
+      </c>
+    </row>
+    <row r="2023">
+      <c r="A2023" s="2" t="n">
+        <v>45485</v>
+      </c>
+      <c r="B2023" t="n">
+        <v>3.829799540304149</v>
+      </c>
+      <c r="C2023" t="n">
+        <v>3.650436263048445</v>
+      </c>
+      <c r="D2023" t="n">
+        <v>-3.188532174103851</v>
+      </c>
+      <c r="E2023" t="n">
+        <v>2.289283638555252</v>
+      </c>
+      <c r="F2023" t="n">
+        <v>0.7395778318035755</v>
+      </c>
+      <c r="G2023" t="n">
+        <v>3.643500060034813</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240712.xlsx
+++ b/tame_output/ON/bt/strategyON_20240712.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.7%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>76.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,32 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>43.9%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.0%</t>
+          <t>-71.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.6%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.0%</t>
+          <t>-66.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.9%</t>
+          <t>457.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-480.4%</t>
+          <t>-493.2%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-17.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-147.3%</t>
+          <t>-161.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-23.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-18.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-81.7%</t>
+          <t>-91.2%</t>
         </is>
       </c>
     </row>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.79769488424229</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502336</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.062313749578975</v>
+        <v>-4.189903185545511</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.336706726568671</v>
+        <v>1.285670952182057</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.04218125443588977</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.842292951541964</v>
+        <v>-3.9698823875085</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.426294082794089</v>
+        <v>1.375258308407475</v>
       </c>
       <c r="F1929" t="n">
         <v>0.09903859063209047</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.709425262478686</v>
+        <v>-3.837014698445222</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.495335341221224</v>
+        <v>1.44429956683461</v>
       </c>
       <c r="F1930" t="n">
         <v>0.09903859063209047</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.589252179114188</v>
+        <v>-3.716841615080723</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.544550419007325</v>
+        <v>1.493514644620711</v>
       </c>
       <c r="F1931" t="n">
         <v>0.2192116739965894</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.44458003401445</v>
+        <v>-3.572169469980985</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.61250737960866</v>
+        <v>1.561471605222046</v>
       </c>
       <c r="F1932" t="n">
         <v>0.3638838190963268</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942101</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.504454861372142</v>
+        <v>-3.632044297338678</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.574594940067009</v>
+        <v>1.523559165680395</v>
       </c>
       <c r="F1933" t="n">
         <v>0.3040089917386347</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.384634630461305</v>
+        <v>-3.51222406642784</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.637812201665553</v>
+        <v>1.586776427278938</v>
       </c>
       <c r="F1934" t="n">
         <v>0.3040089917386347</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430692</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.387104336923111</v>
+        <v>-3.514693772889646</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.544468518403272</v>
+        <v>1.493432744016657</v>
       </c>
       <c r="F1935" t="n">
         <v>0.3015392852768286</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.455474523247121</v>
+        <v>-3.583063959213656</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.436382305358969</v>
+        <v>1.385346530972355</v>
       </c>
       <c r="F1936" t="n">
         <v>0.3108149843130435</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.469262576094168</v>
+        <v>-3.596852012060703</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.421303792852042</v>
+        <v>1.370268018465428</v>
       </c>
       <c r="F1937" t="n">
         <v>0.3108149843130435</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.500255735422873</v>
+        <v>-3.627845171389408</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.233616094160946</v>
+        <v>1.182580319774332</v>
       </c>
       <c r="F1938" t="n">
         <v>0.3108149843130435</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.324781475630404</v>
+        <v>-3.452370911596939</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.308373030069722</v>
+        <v>1.257337255683108</v>
       </c>
       <c r="F1939" t="n">
         <v>0.3108149843130435</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.435717728271652</v>
+        <v>-3.563307164238187</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.23974055777443</v>
+        <v>1.188704783387815</v>
       </c>
       <c r="F1940" t="n">
         <v>0.3108149843130435</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.617515458616743</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.40205418279937</v>
+        <v>-3.529643618765906</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.256337361183248</v>
+        <v>1.205301586796634</v>
       </c>
       <c r="F1941" t="n">
         <v>0.3444785297853253</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.627687845048876</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.342201563595647</v>
+        <v>-3.469790999562183</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.29045079529687</v>
+        <v>1.239415020910255</v>
       </c>
       <c r="F1942" t="n">
         <v>0.3444785297853253</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.622634115622736</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.25595810056927</v>
+        <v>-3.383547536535805</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.319894451081281</v>
+        <v>1.268858676694667</v>
       </c>
       <c r="F1943" t="n">
         <v>0.3444785297853253</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.614409891067262</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.30126491996825</v>
+        <v>-3.428854355934785</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.293547498766214</v>
+        <v>1.2425117243796</v>
       </c>
       <c r="F1944" t="n">
         <v>0.3036683667760945</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.614961764100363</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.330298024670551</v>
+        <v>-3.457887460637087</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.282486129918395</v>
+        <v>1.231450355531781</v>
       </c>
       <c r="F1945" t="n">
         <v>0.3036683667760945</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.544234455991729</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.237487543219692</v>
+        <v>-3.365076979186227</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.248883014390105</v>
+        <v>1.197847240003491</v>
       </c>
       <c r="F1946" t="n">
         <v>0.3964788482269539</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.54610793191633</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.28187701254912</v>
+        <v>-3.409466448515655</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.233000702582934</v>
+        <v>1.18196492819632</v>
       </c>
       <c r="F1947" t="n">
         <v>0.3520893788975262</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.541183640428053</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.16920579431287</v>
+        <v>-3.296795230279405</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.273144898389158</v>
+        <v>1.222109124002543</v>
       </c>
       <c r="F1948" t="n">
         <v>0.4647605971337764</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.54667493625872</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.056828793130197</v>
+        <v>-3.184418229096732</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.323586994692894</v>
+        <v>1.27255122030628</v>
       </c>
       <c r="F1949" t="n">
         <v>0.4647605971337764</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.558172138027259</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.08460919103155</v>
+        <v>-3.212198626998085</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.323972037300892</v>
+        <v>1.272936262914278</v>
       </c>
       <c r="F1950" t="n">
         <v>0.4369801992324234</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.396527858027912</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.167610472056829</v>
+        <v>-3.295199908023364</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.129127244891433</v>
+        <v>1.078091470504819</v>
       </c>
       <c r="F1951" t="n">
         <v>0.4184093147052496</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.516677518747118</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.27622455050016</v>
+        <v>-3.403813986466695</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.205831274233306</v>
+        <v>1.154795499846692</v>
       </c>
       <c r="F1952" t="n">
         <v>0.4184093147052496</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.240815512252017</v>
+        <v>-3.368404948218553</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.234507915634887</v>
+        <v>1.183472141248272</v>
       </c>
       <c r="F1953" t="n">
         <v>0.4184093147052496</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913426</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.202431849693866</v>
+        <v>-3.330021285660401</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.247280822000516</v>
+        <v>1.196245047613901</v>
       </c>
       <c r="F1954" t="n">
         <v>0.4567929772634008</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.0253155196587</v>
+        <v>-3.152904955625235</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.314856382859884</v>
+        <v>1.26382060847327</v>
       </c>
       <c r="F1955" t="n">
         <v>0.4567929772634008</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.070407764492246</v>
+        <v>-3.197997200458781</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.297502876688379</v>
+        <v>1.246467102301765</v>
       </c>
       <c r="F1956" t="n">
         <v>0.394896934094011</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-2.891032343253478</v>
+        <v>-3.018621779220013</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.363040020490301</v>
+        <v>1.312004246103687</v>
       </c>
       <c r="F1957" t="n">
         <v>0.5516736922647296</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-2.936046556774084</v>
+        <v>-3.06363599274062</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.325841790413648</v>
+        <v>1.274806016027034</v>
       </c>
       <c r="F1958" t="n">
         <v>0.521324796950125</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.20305106704652</v>
+        <v>-3.330640503013055</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.22473154864362</v>
+        <v>1.173695774257006</v>
       </c>
       <c r="F1959" t="n">
         <v>0.3269617589071764</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.304248848483692</v>
+        <v>-3.431838284450228</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.183456357965252</v>
+        <v>1.132420583578638</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2585529453618572</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.29773788186938</v>
+        <v>-3.425327317835915</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.183660706165294</v>
+        <v>1.13262493177868</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2585529453618572</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.278699754162083</v>
+        <v>-3.406289190128618</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.187800676456457</v>
+        <v>1.136764902069843</v>
       </c>
       <c r="F1962" t="n">
         <v>0.2003693340306627</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131249</v>
       </c>
       <c r="C1963" t="n">
         <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.309826385312701</v>
+        <v>-3.437415821279236</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.352931892934891</v>
+        <v>1.301896118548277</v>
       </c>
       <c r="F1963" t="n">
         <v>0.2003693340306627</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.323693146646618</v>
+        <v>-3.451282582613153</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.348218517387457</v>
+        <v>1.297182743000843</v>
       </c>
       <c r="F1964" t="n">
         <v>0.1625114172968398</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.278888975106688</v>
+        <v>-3.406478411073223</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.372148716400355</v>
+        <v>1.321112942013741</v>
       </c>
       <c r="F1965" t="n">
         <v>0.1625114172968398</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.582010952033977</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.131146004871686</v>
+        <v>-3.258735440838221</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.329196125771556</v>
+        <v>1.278160351384942</v>
       </c>
       <c r="F1966" t="n">
         <v>0.3303187745317229</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.584804573565458</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.233160687402907</v>
+        <v>-3.360750123369442</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.291183874290548</v>
+        <v>1.240148099903934</v>
       </c>
       <c r="F1967" t="n">
         <v>0.3303187745317229</v>
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.585466921957117</v>
+        <v>2.490330741537004</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.227007981350122</v>
+        <v>-3.354597417316658</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.29430730510332</v>
+        <v>1.148135350296594</v>
       </c>
       <c r="F1968" t="n">
         <v>0.3364714805845072</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.787349810307821</v>
+        <v>2.692213629887708</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.584547398697227</v>
+        <v>2.489411218277114</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.243817279500624</v>
+        <v>-3.371406715467159</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.28666406258323</v>
+        <v>1.140492107776503</v>
       </c>
       <c r="F1969" t="n">
         <v>0.3196621824340056</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.776344708157631</v>
+        <v>2.681208527737518</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.650882952494048</v>
+        <v>2.555746772073935</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.181519280724502</v>
+        <v>-3.309108716691037</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.3779188158905</v>
+        <v>1.231746861083773</v>
       </c>
       <c r="F1970" t="n">
         <v>0.3196621824340056</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.842680261954452</v>
+        <v>2.747544081534339</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.453174954208175</v>
+        <v>2.358038773788062</v>
       </c>
       <c r="D1971" t="n">
-        <v>-2.979729083059344</v>
+        <v>-3.107318519025879</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.26092689667069</v>
+        <v>1.114754941863963</v>
       </c>
       <c r="F1971" t="n">
         <v>0.51768037460316</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.763783178970071</v>
+        <v>2.668646998549959</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.52346518653035</v>
+        <v>2.428329006110237</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.814916079980497</v>
+        <v>-2.942505515947032</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.397142330224404</v>
+        <v>1.250970375417677</v>
       </c>
       <c r="F1972" t="n">
         <v>0.6824933776820069</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.932961213139555</v>
+        <v>2.837825032719442</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.538092922646394</v>
+        <v>2.442956742226281</v>
       </c>
       <c r="D1973" t="n">
-        <v>-2.912656624605471</v>
+        <v>-3.040246060572007</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.372673848490458</v>
+        <v>1.226501893683731</v>
       </c>
       <c r="F1973" t="n">
         <v>0.6666040995490268</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.93805538237581</v>
+        <v>2.842919201955697</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.536628903471065</v>
+        <v>2.441492723050953</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.088994384728401</v>
+        <v>-3.216583820694936</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.300674725265958</v>
+        <v>1.154502770459231</v>
       </c>
       <c r="F1974" t="n">
         <v>0.4902663394260973</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.830788707126724</v>
+        <v>2.735652526706611</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.535120521510994</v>
+        <v>2.439984341090881</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.012572338296474</v>
+        <v>-3.140161774263009</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.329735161878657</v>
+        <v>1.18356320707193</v>
       </c>
       <c r="F1975" t="n">
         <v>0.4902663394260973</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.829280325166653</v>
+        <v>2.73414414474654</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.53498338894643</v>
+        <v>2.439847208526317</v>
       </c>
       <c r="D1976" t="n">
-        <v>-2.968199206657905</v>
+        <v>-3.095788642624441</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.347347281969521</v>
+        <v>1.201175327162794</v>
       </c>
       <c r="F1976" t="n">
         <v>0.5346394710646659</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.85576707158523</v>
+        <v>2.760630891165117</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.529377183085021</v>
+        <v>2.434241002664908</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.845364985770738</v>
+        <v>-2.972954421737273</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.390874764462978</v>
+        <v>1.244702809656251</v>
       </c>
       <c r="F1977" t="n">
         <v>0.5346394710646659</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.85016086572382</v>
+        <v>2.755024685303708</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.535758940112825</v>
+        <v>2.440622759692713</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.797709255209682</v>
+        <v>-2.925298691176217</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.416318813715205</v>
+        <v>1.270146858908478</v>
       </c>
       <c r="F1978" t="n">
         <v>0.5822952016257216</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.885136061088259</v>
+        <v>2.789999880668146</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.54065131348755</v>
+        <v>2.445515133067437</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.697191096710927</v>
+        <v>-2.824780532677463</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.461418450489432</v>
+        <v>1.315246495682705</v>
       </c>
       <c r="F1979" t="n">
         <v>0.6828133601244761</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.950339329562236</v>
+        <v>2.855203149142123</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.82880887755729</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.527405985963422</v>
+        <v>2.43226980554331</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.757857687113316</v>
+        <v>-2.885447123079852</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.423906486804349</v>
+        <v>1.277734531997622</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6011150434059425</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.888075012006988</v>
+        <v>2.792938831586875</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.531503688574051</v>
+        <v>2.436367508153938</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.713019285504918</v>
+        <v>-2.840608721471454</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.445939550058336</v>
+        <v>1.299767595251609</v>
       </c>
       <c r="F1981" t="n">
         <v>0.6056584763508119</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.894898774384538</v>
+        <v>2.799762593964426</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.81793235491705</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.535664628205129</v>
+        <v>2.440528447785016</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.813777921261917</v>
+        <v>-2.941367357228452</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.409797035386615</v>
+        <v>1.263625080579888</v>
       </c>
       <c r="F1982" t="n">
         <v>0.5168329076238065</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.845764372779413</v>
+        <v>2.7506281923593</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405957</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.541544230732966</v>
+        <v>2.446408050312853</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.769575084176016</v>
+        <v>-2.897164520142552</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.433357772748812</v>
+        <v>1.287185817942085</v>
       </c>
       <c r="F1983" t="n">
         <v>0.561035744709707</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.87816567755879</v>
+        <v>2.783029497138678</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.539954231202214</v>
+        <v>2.444818050782101</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.80655411183946</v>
+        <v>-2.934143547805995</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.416976162152683</v>
+        <v>1.270804207345956</v>
       </c>
       <c r="F1984" t="n">
         <v>0.5980096465010375</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.898760019102836</v>
+        <v>2.803623838682724</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.591201996385253</v>
+        <v>2.496065815965141</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.648262694300187</v>
+        <v>-2.775852130266723</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.531540494351431</v>
+        <v>1.385368539544704</v>
       </c>
       <c r="F1985" t="n">
         <v>0.5980096465010375</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.950007784285876</v>
+        <v>2.854871603865763</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.589642700979506</v>
+        <v>2.494506520559394</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.440620690665711</v>
+        <v>-2.568210126632247</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.613038000399475</v>
+        <v>1.466866045592748</v>
       </c>
       <c r="F1986" t="n">
         <v>0.8056516501355137</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.073033691060815</v>
+        <v>2.977897510640702</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.584590929217776</v>
+        <v>2.489454748797664</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.389588597943183</v>
+        <v>-2.517178033909719</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.628399065726756</v>
+        <v>1.482227110920029</v>
       </c>
       <c r="F1987" t="n">
         <v>0.8566837428580416</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.098601174932602</v>
+        <v>3.003464994512489</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.84254736040485</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.601778333310481</v>
+        <v>2.506642152890369</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.324364416815977</v>
+        <v>-2.451953852782513</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.671676142270343</v>
+        <v>1.525504187463616</v>
       </c>
       <c r="F1988" t="n">
         <v>0.9219079239852472</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.15492308770163</v>
+        <v>3.059786907281517</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882553</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.597739305609762</v>
+        <v>2.502603125189649</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.286937396744844</v>
+        <v>-2.414526832711379</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.682607922598077</v>
+        <v>1.53643596779135</v>
       </c>
       <c r="F1989" t="n">
         <v>0.9271594620144289</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.154034982818419</v>
+        <v>3.058898802398307</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992659</v>
+        <v>3.845169808992656</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.598996097941002</v>
+        <v>2.503859917520889</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.307049052779552</v>
+        <v>-2.434638488746087</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.675820052515434</v>
+        <v>1.529648097708707</v>
       </c>
       <c r="F1990" t="n">
         <v>0.9381868070118481</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.161908182148111</v>
+        <v>3.066772001727998</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636283</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.759553868962213</v>
+        <v>2.6644176885421</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.253304238352347</v>
+        <v>-2.380893674318882</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.857875749307527</v>
+        <v>1.7117037945008</v>
       </c>
       <c r="F1991" t="n">
         <v>0.9482501164523101</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.328503938833599</v>
+        <v>3.233367758413486</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957623</v>
+        <v>3.813222820957621</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.87966677818003</v>
+        <v>2.784530597759917</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.229512669746205</v>
+        <v>-2.35710210571274</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.987505285967801</v>
+        <v>1.841333331161074</v>
       </c>
       <c r="F1992" t="n">
         <v>0.9720416850584523</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.462891789215102</v>
+        <v>3.367755608794989</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.871374754193889</v>
+        <v>2.776238573773776</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.203428585482397</v>
+        <v>-2.331018021448932</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.989646895687183</v>
+        <v>1.843474940880456</v>
       </c>
       <c r="F1993" t="n">
         <v>0.9720416850584523</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.454599765228961</v>
+        <v>3.359463584808848</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896925</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.869567949777668</v>
+        <v>2.774431769357556</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.12529740463345</v>
+        <v>-2.252886840599985</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.019092563610541</v>
+        <v>1.872920608803814</v>
       </c>
       <c r="F1994" t="n">
         <v>1.046218495942137</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.497299047342951</v>
+        <v>3.402162866922838</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959854</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.88712235550446</v>
+        <v>2.791986175084347</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.116404943240167</v>
+        <v>-2.243994379206702</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.040203953894646</v>
+        <v>1.894031999087919</v>
       </c>
       <c r="F1995" t="n">
         <v>1.046218495942137</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.514853453069742</v>
+        <v>3.419717272649629</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.878977402909044</v>
+        <v>2.783841222488931</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.284881060210045</v>
+        <v>-2.41247049617658</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.964668554511279</v>
+        <v>1.818496599704552</v>
       </c>
       <c r="F1996" t="n">
         <v>1.018270660225556</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.489939799044378</v>
+        <v>3.394803618624265</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782705</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.860247100096906</v>
+        <v>2.765110919676793</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.587081531348462</v>
+        <v>-1.714670967314997</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.225058063243774</v>
+        <v>2.078886108437047</v>
       </c>
       <c r="F1997" t="n">
         <v>0.9479226008551453</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.429000660609993</v>
+        <v>3.33386448018988</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.85091112259381</v>
+        <v>2.755774942173697</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.564360427665309</v>
+        <v>-1.691949863631844</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.224810527213939</v>
+        <v>2.078638572407213</v>
       </c>
       <c r="F1998" t="n">
         <v>0.9479226008551453</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.419664683106898</v>
+        <v>3.324528502686785</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.78320569677767</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.009817248444979</v>
+        <v>2.914681068024866</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.562635384375265</v>
+        <v>-1.690224820341801</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.384406670381126</v>
+        <v>2.238234715574399</v>
       </c>
       <c r="F1999" t="n">
         <v>0.9496476441451891</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.579605834932093</v>
+        <v>3.48446965451198</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644412</v>
+        <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.046895070938626</v>
+        <v>2.951758890518513</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.717416391153521</v>
+        <v>-1.845005827120056</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.35957209016347</v>
+        <v>2.213400135356744</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9162799700907129</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.596663052993054</v>
+        <v>3.501526872572941</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.043570426928171</v>
+        <v>2.948434246508058</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.665981057768861</v>
+        <v>-1.793570493735396</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.376821579506879</v>
+        <v>2.230649624700153</v>
       </c>
       <c r="F2001" t="n">
         <v>0.9677153034753726</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.624199609013395</v>
+        <v>3.529063428593282</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.053576580572912</v>
+        <v>2.9584404001528</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.639029833442373</v>
+        <v>-1.766619269408908</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.397608222882216</v>
+        <v>2.251436268075489</v>
       </c>
       <c r="F2002" t="n">
         <v>0.9825956495030918</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.643133970274768</v>
+        <v>3.547997789854655</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784107</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.237679712717872</v>
+        <v>3.14254353229776</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.774982841498689</v>
+        <v>-1.902572277465225</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.527330151804649</v>
+        <v>2.381158196997923</v>
       </c>
       <c r="F2003" t="n">
         <v>0.9825956495030918</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.827237102419728</v>
+        <v>3.732100921999615</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714422</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.229796407620865</v>
+        <v>3.134660227200753</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.797390959303561</v>
+        <v>-1.924980395270097</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.510483599585694</v>
+        <v>2.364311644778967</v>
       </c>
       <c r="F2004" t="n">
         <v>0.9825956495030918</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.819353797322721</v>
+        <v>3.724217616902608</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155033</v>
+        <v>3.719118627155029</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.231850407170503</v>
+        <v>3.13671422675039</v>
       </c>
       <c r="D2005" t="n">
-        <v>-1.945396726782961</v>
+        <v>-2.072986162749496</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.453335292143571</v>
+        <v>2.307163337336844</v>
       </c>
       <c r="F2005" t="n">
         <v>0.8958686406395503</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.769371591554233</v>
+        <v>3.67423541113412</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161978</v>
+        <v>3.729452285161974</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.28810412489235</v>
+        <v>3.192967944472237</v>
       </c>
       <c r="D2006" t="n">
-        <v>-1.95483765267149</v>
+        <v>-2.082427088638026</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.505812639510006</v>
+        <v>2.35964068470328</v>
       </c>
       <c r="F2006" t="n">
         <v>1.018295758182942</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.899081579802115</v>
+        <v>3.803945399382003</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321634</v>
+        <v>3.71494119332163</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.290995219437651</v>
+        <v>3.195859039017538</v>
       </c>
       <c r="D2007" t="n">
-        <v>-1.953550889131934</v>
+        <v>-2.081140325098469</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.50921843947113</v>
+        <v>2.363046484664403</v>
       </c>
       <c r="F2007" t="n">
         <v>1.019582521722498</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.90274473247115</v>
+        <v>3.807608552051037</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347702</v>
+        <v>3.727898186347699</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.289107032331426</v>
+        <v>3.193970851911313</v>
       </c>
       <c r="D2008" t="n">
-        <v>-1.955107943121225</v>
+        <v>-2.082697379087761</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.506707430769189</v>
+        <v>2.360535475962462</v>
       </c>
       <c r="F2008" t="n">
         <v>1.019582521722498</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.900856545364925</v>
+        <v>3.805720364944813</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887743</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.283927261934288</v>
+        <v>3.188791081514176</v>
       </c>
       <c r="D2009" t="n">
-        <v>-1.96237982864469</v>
+        <v>-2.089969264611225</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.498618906162665</v>
+        <v>2.352446951355938</v>
       </c>
       <c r="F2009" t="n">
         <v>1.012310636199033</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.891313643653709</v>
+        <v>3.796177463233596</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.282361272144441</v>
+        <v>3.187225091724328</v>
       </c>
       <c r="D2010" t="n">
-        <v>-1.960538809586438</v>
+        <v>-2.088128245552974</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.497789323996118</v>
+        <v>2.351617369189391</v>
       </c>
       <c r="F2010" t="n">
         <v>1.013578862870502</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.890508589866742</v>
+        <v>3.795372409446629</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647105</v>
+        <v>3.754911907647101</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.295434679010359</v>
+        <v>3.200298498590247</v>
       </c>
       <c r="D2011" t="n">
-        <v>-1.967447515086119</v>
+        <v>-2.095036951052655</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.508099248662164</v>
+        <v>2.361927293855437</v>
       </c>
       <c r="F2011" t="n">
         <v>1.013578862870502</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.903581996732661</v>
+        <v>3.808445816312548</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763531</v>
+        <v>3.749896851763529</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.295434679010359</v>
+        <v>3.200298498590247</v>
       </c>
       <c r="D2012" t="n">
-        <v>-1.969009157900979</v>
+        <v>-2.096598593867514</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.507474591536221</v>
+        <v>2.361302636729493</v>
       </c>
       <c r="F2012" t="n">
         <v>1.013578862870502</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.903581996732661</v>
+        <v>3.808445816312548</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392115</v>
+        <v>3.715834055392111</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.293958720137361</v>
+        <v>3.198822539717249</v>
       </c>
       <c r="D2013" t="n">
-        <v>-1.996909945010452</v>
+        <v>-2.124499380976987</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.494838317819434</v>
+        <v>2.348666363012706</v>
       </c>
       <c r="F2013" t="n">
         <v>0.9789819387275672</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.881347883373902</v>
+        <v>3.786211702953789</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172526</v>
+        <v>3.684909939172523</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.29072316411456</v>
+        <v>3.195586983694447</v>
       </c>
       <c r="D2014" t="n">
-        <v>-1.999942942523126</v>
+        <v>-2.127532378489661</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.490389562791563</v>
+        <v>2.344217607984835</v>
       </c>
       <c r="F2014" t="n">
         <v>0.9759489412148934</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.876292528843496</v>
+        <v>3.781156348423384</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971079</v>
+        <v>3.619362241971075</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.357429123705064</v>
+        <v>3.262292943284951</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.020004263799632</v>
+        <v>-2.147593699766168</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.549070993871464</v>
+        <v>2.402899039064736</v>
       </c>
       <c r="F2015" t="n">
         <v>0.9558876199383863</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.930961695668096</v>
+        <v>3.835825515247983</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199805</v>
+        <v>3.640764248199802</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.497740842706911</v>
+        <v>3.402604662286798</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.276725081794456</v>
+        <v>-2.404314517760992</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.586694385675381</v>
+        <v>2.440522430868654</v>
       </c>
       <c r="F2016" t="n">
         <v>0.8474730457945715</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.006224670183654</v>
+        <v>3.911088489763541</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622237</v>
+        <v>3.668303164622233</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.566721111852551</v>
+        <v>3.471584931432438</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.430711499570597</v>
+        <v>-2.558300935537133</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.594080087710565</v>
+        <v>2.447908132903837</v>
       </c>
       <c r="F2017" t="n">
         <v>0.8474730457945715</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.075204939329294</v>
+        <v>3.980068758909181</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808529</v>
+        <v>3.619937176808525</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.552772313972671</v>
+        <v>3.457636133552559</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.380189595742931</v>
+        <v>-2.507779031709467</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.600340051361752</v>
+        <v>2.454168096555025</v>
       </c>
       <c r="F2018" t="n">
         <v>0.8474730457945715</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.061256141449414</v>
+        <v>3.966119961029301</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994894</v>
+        <v>3.65634689399489</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.564642803028085</v>
+        <v>3.469506622607973</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.632664749750655</v>
+        <v>-2.760254185717192</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.511220478814076</v>
+        <v>2.365048524007349</v>
       </c>
       <c r="F2019" t="n">
         <v>0.8474730457945715</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.073126630504829</v>
+        <v>3.977990450084716</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358297</v>
+        <v>3.674042696358294</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.565853337547029</v>
+        <v>3.470717157126916</v>
       </c>
       <c r="D2020" t="n">
-        <v>-2.902137551672364</v>
+        <v>-3.0297269876389</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.404641892564336</v>
+        <v>2.258469937757609</v>
       </c>
       <c r="F2020" t="n">
         <v>0.8474730457945715</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.074337165023772</v>
+        <v>3.97920098460366</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637086</v>
+        <v>3.663523617637082</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.569975079774351</v>
+        <v>3.474838899354238</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.059681623401805</v>
+        <v>-3.187271059368341</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.345746006099882</v>
+        <v>2.199574051293154</v>
       </c>
       <c r="F2021" t="n">
         <v>0.7805712406542971</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.03831782416693</v>
+        <v>3.943181643746817</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301343</v>
+        <v>3.652163313301339</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.56505293251054</v>
+        <v>3.469916752090427</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.188532174103851</v>
+        <v>-3.316121610070387</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.289283638555252</v>
+        <v>2.143111683748525</v>
       </c>
       <c r="F2022" t="n">
         <v>0.7395778318035755</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.008799631592685</v>
+        <v>3.913663451172573</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.829799540304149</v>
+        <v>3.827608339930108</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.650436263048445</v>
+        <v>3.555054617469487</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.188532174103851</v>
+        <v>-3.316121610070387</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.289283638555252</v>
+        <v>2.143111683748525</v>
       </c>
       <c r="F2023" t="n">
         <v>0.7395778318035755</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.643500060034813</v>
+        <v>3.548118414455855</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240712.xlsx
+++ b/tame_output/ON/bt/strategyON_20240712.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>56.6%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>82.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,32 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>61.7%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.6%</t>
+          <t>-70.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>109.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.6%</t>
+          <t>-65.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.6%</t>
+          <t>457.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-493.2%</t>
+          <t>-477.6%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-161.9%</t>
+          <t>-146.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.2%</t>
+          <t>-10.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>124.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-124.6%</t>
+          <t>-123.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-150.0%</t>
+          <t>-142.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>-24.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-91.2%</t>
+          <t>-73.4%</t>
         </is>
       </c>
     </row>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297399</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919906</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279183</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074779</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769488424229</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502334</v>
+        <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942101</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430692</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.634074812643843</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.638642044635631</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502432322544</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.614384073396838</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.617515458616743</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.627687845048876</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.622634115622736</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.614409891067262</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.614961764100363</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.544234455991729</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.54610793191633</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.541183640428053</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.54667493625872</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.558172138027259</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
         <v>2.396527858027912</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.516677518747118</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.531190544849441</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
         <v>2.528609986191809</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.525339015037112</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.526022406799025</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.519809382105439</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.500616837437029</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509537</v>
       </c>
       <c r="C1959" t="n">
         <v>2.506308399775975</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760813</v>
       </c>
       <c r="C1960" t="n">
         <v>2.505512321672476</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.503112283226793</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.499637002435038</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131249</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.677218871373718</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.678052200359852</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
         <v>2.684060730756778</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.582010952033977</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.584804573565458</v>
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.490330741537004</v>
+        <v>2.585466921957117</v>
       </c>
       <c r="D1968" t="n">
         <v>-3.354597417316658</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.148135350296594</v>
+        <v>1.243271530716706</v>
       </c>
       <c r="F1968" t="n">
         <v>0.3364714805845072</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.692213629887708</v>
+        <v>2.787349810307821</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.489411218277114</v>
+        <v>2.584547398697227</v>
       </c>
       <c r="D1969" t="n">
         <v>-3.371406715467159</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.140492107776503</v>
+        <v>1.235628288196616</v>
       </c>
       <c r="F1969" t="n">
         <v>0.3196621824340056</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.681208527737518</v>
+        <v>2.776344708157631</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.555746772073935</v>
+        <v>2.650882952494048</v>
       </c>
       <c r="D1970" t="n">
         <v>-3.309108716691037</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.231746861083773</v>
+        <v>1.326883041503886</v>
       </c>
       <c r="F1970" t="n">
         <v>0.3196621824340056</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.747544081534339</v>
+        <v>2.842680261954452</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.358038773788062</v>
+        <v>2.453174954208175</v>
       </c>
       <c r="D1971" t="n">
         <v>-3.107318519025879</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.114754941863963</v>
+        <v>1.209891122284076</v>
       </c>
       <c r="F1971" t="n">
         <v>0.51768037460316</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.668646998549959</v>
+        <v>2.763783178970071</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.428329006110237</v>
+        <v>2.52346518653035</v>
       </c>
       <c r="D1972" t="n">
         <v>-2.942505515947032</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.250970375417677</v>
+        <v>1.34610655583779</v>
       </c>
       <c r="F1972" t="n">
         <v>0.6824933776820069</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.837825032719442</v>
+        <v>2.932961213139555</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.442956742226281</v>
+        <v>2.538092922646394</v>
       </c>
       <c r="D1973" t="n">
         <v>-3.040246060572007</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.226501893683731</v>
+        <v>1.321638074103844</v>
       </c>
       <c r="F1973" t="n">
         <v>0.6666040995490268</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.842919201955697</v>
+        <v>2.93805538237581</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489382</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.441492723050953</v>
+        <v>2.536628903471065</v>
       </c>
       <c r="D1974" t="n">
         <v>-3.216583820694936</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.154502770459231</v>
+        <v>1.249638950879344</v>
       </c>
       <c r="F1974" t="n">
         <v>0.4902663394260973</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.735652526706611</v>
+        <v>2.830788707126724</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397792</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.439984341090881</v>
+        <v>2.535120521510994</v>
       </c>
       <c r="D1975" t="n">
         <v>-3.140161774263009</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.18356320707193</v>
+        <v>1.278699387492043</v>
       </c>
       <c r="F1975" t="n">
         <v>0.4902663394260973</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.73414414474654</v>
+        <v>2.829280325166653</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.439847208526317</v>
+        <v>2.53498338894643</v>
       </c>
       <c r="D1976" t="n">
         <v>-3.095788642624441</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.201175327162794</v>
+        <v>1.296311507582907</v>
       </c>
       <c r="F1976" t="n">
         <v>0.5346394710646659</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.760630891165117</v>
+        <v>2.85576707158523</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.434241002664908</v>
+        <v>2.529377183085021</v>
       </c>
       <c r="D1977" t="n">
         <v>-2.972954421737273</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.244702809656251</v>
+        <v>1.339838990076364</v>
       </c>
       <c r="F1977" t="n">
         <v>0.5346394710646659</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.755024685303708</v>
+        <v>2.85016086572382</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190322</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.440622759692713</v>
+        <v>2.535758940112825</v>
       </c>
       <c r="D1978" t="n">
         <v>-2.925298691176217</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.270146858908478</v>
+        <v>1.365283039328591</v>
       </c>
       <c r="F1978" t="n">
         <v>0.5822952016257216</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.789999880668146</v>
+        <v>2.885136061088259</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569615</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.445515133067437</v>
+        <v>2.54065131348755</v>
       </c>
       <c r="D1979" t="n">
         <v>-2.824780532677463</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.315246495682705</v>
+        <v>1.410382676102818</v>
       </c>
       <c r="F1979" t="n">
         <v>0.6828133601244761</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.855203149142123</v>
+        <v>2.950339329562236</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.82880887755729</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.43226980554331</v>
+        <v>2.527405985963422</v>
       </c>
       <c r="D1980" t="n">
         <v>-2.885447123079852</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.277734531997622</v>
+        <v>1.372870712417734</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6011150434059425</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.792938831586875</v>
+        <v>2.888075012006988</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.436367508153938</v>
+        <v>2.531503688574051</v>
       </c>
       <c r="D1981" t="n">
         <v>-2.840608721471454</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.299767595251609</v>
+        <v>1.394903775671722</v>
       </c>
       <c r="F1981" t="n">
         <v>0.6056584763508119</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.799762593964426</v>
+        <v>2.894898774384538</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.81793235491705</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.440528447785016</v>
+        <v>2.535664628205129</v>
       </c>
       <c r="D1982" t="n">
         <v>-2.941367357228452</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.263625080579888</v>
+        <v>1.358761261000001</v>
       </c>
       <c r="F1982" t="n">
         <v>0.5168329076238065</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.7506281923593</v>
+        <v>2.845764372779413</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405957</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.446408050312853</v>
+        <v>2.541544230732966</v>
       </c>
       <c r="D1983" t="n">
         <v>-2.897164520142552</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.287185817942085</v>
+        <v>1.382321998362198</v>
       </c>
       <c r="F1983" t="n">
         <v>0.561035744709707</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.783029497138678</v>
+        <v>2.87816567755879</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.444818050782101</v>
+        <v>2.539954231202214</v>
       </c>
       <c r="D1984" t="n">
         <v>-2.934143547805995</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.270804207345956</v>
+        <v>1.365940387766069</v>
       </c>
       <c r="F1984" t="n">
         <v>0.5980096465010375</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.803623838682724</v>
+        <v>2.898760019102836</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.496065815965141</v>
+        <v>2.591201996385253</v>
       </c>
       <c r="D1985" t="n">
         <v>-2.775852130266723</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.385368539544704</v>
+        <v>1.480504719964817</v>
       </c>
       <c r="F1985" t="n">
         <v>0.5980096465010375</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.854871603865763</v>
+        <v>2.950007784285876</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321019</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.494506520559394</v>
+        <v>2.589642700979506</v>
       </c>
       <c r="D1986" t="n">
         <v>-2.568210126632247</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.466866045592748</v>
+        <v>1.562002226012861</v>
       </c>
       <c r="F1986" t="n">
         <v>0.8056516501355137</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.977897510640702</v>
+        <v>3.073033691060815</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.489454748797664</v>
+        <v>2.584590929217776</v>
       </c>
       <c r="D1987" t="n">
         <v>-2.517178033909719</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.482227110920029</v>
+        <v>1.577363291340142</v>
       </c>
       <c r="F1987" t="n">
         <v>0.8566837428580416</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.003464994512489</v>
+        <v>3.098601174932602</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84254736040485</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.506642152890369</v>
+        <v>2.601778333310481</v>
       </c>
       <c r="D1988" t="n">
         <v>-2.451953852782513</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.525504187463616</v>
+        <v>1.620640367883729</v>
       </c>
       <c r="F1988" t="n">
         <v>0.9219079239852472</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.059786907281517</v>
+        <v>3.15492308770163</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882553</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.502603125189649</v>
+        <v>2.597739305609762</v>
       </c>
       <c r="D1989" t="n">
         <v>-2.414526832711379</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.53643596779135</v>
+        <v>1.631572148211463</v>
       </c>
       <c r="F1989" t="n">
         <v>0.9271594620144289</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.058898802398307</v>
+        <v>3.154034982818419</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992656</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.503859917520889</v>
+        <v>2.598996097941002</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.434638488746087</v>
+        <v>-2.278711040780695</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.529648097708707</v>
+        <v>1.687155257314977</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.9381868070118481</v>
+        <v>1.01433581429035</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.066772001727998</v>
+        <v>3.207597586515212</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636283</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.6644176885421</v>
+        <v>2.759553868962213</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.380893674318882</v>
+        <v>-2.22496622635349</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.7117037945008</v>
+        <v>1.86921095410707</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9482501164523101</v>
+        <v>1.024399123730812</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.233367758413486</v>
+        <v>3.3741933432007</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957621</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.784530597759917</v>
+        <v>2.87966677818003</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.35710210571274</v>
+        <v>-2.201174657747348</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.841333331161074</v>
+        <v>1.998840490767344</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.9720416850584523</v>
+        <v>1.048190692336954</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.367755608794989</v>
+        <v>3.508581193582203</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998751</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.776238573773776</v>
+        <v>2.871374754193889</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.331018021448932</v>
+        <v>-2.17509057348354</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.843474940880456</v>
+        <v>2.000982100486726</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.9720416850584523</v>
+        <v>1.048190692336954</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.359463584808848</v>
+        <v>3.500289169596062</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896925</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.774431769357556</v>
+        <v>2.869567949777668</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.252886840599985</v>
+        <v>-2.096959392634593</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.872920608803814</v>
+        <v>2.030427768410084</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.046218495942137</v>
+        <v>1.122367503220639</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.402162866922838</v>
+        <v>3.542988451710052</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959854</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.791986175084347</v>
+        <v>2.88712235550446</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.243994379206702</v>
+        <v>-2.08806693124131</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.894031999087919</v>
+        <v>2.051539158694188</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.046218495942137</v>
+        <v>1.122367503220639</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.419717272649629</v>
+        <v>3.560542857436843</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.783841222488931</v>
+        <v>2.878977402909044</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.41247049617658</v>
+        <v>-2.256543048211188</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.818496599704552</v>
+        <v>1.976003759310821</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.018270660225556</v>
+        <v>1.094419667504058</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.394803618624265</v>
+        <v>3.535629203411479</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782705</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.765110919676793</v>
+        <v>2.860247100096906</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.714670967314997</v>
+        <v>-1.558743519349605</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.078886108437047</v>
+        <v>2.236393268043317</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.9479226008551453</v>
+        <v>1.024071608133647</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.33386448018988</v>
+        <v>3.474690064977094</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632636</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.755774942173697</v>
+        <v>2.85091112259381</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.691949863631844</v>
+        <v>-1.536022415666452</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.078638572407213</v>
+        <v>2.236145732013482</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.9479226008551453</v>
+        <v>1.024071608133647</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.324528502686785</v>
+        <v>3.465354087473999</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.78320569677767</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
-        <v>2.914681068024866</v>
+        <v>3.009817248444979</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.690224820341801</v>
+        <v>-1.534297372376409</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.238234715574399</v>
+        <v>2.395741875180669</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9496476441451891</v>
+        <v>1.025796651423691</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.48446965451198</v>
+        <v>3.625295239299194</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644408</v>
+        <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
-        <v>2.951758890518513</v>
+        <v>3.046895070938626</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.845005827120056</v>
+        <v>-1.689078379154664</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.213400135356744</v>
+        <v>2.370907294963013</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9162799700907129</v>
+        <v>0.9924289773692148</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.501526872572941</v>
+        <v>3.642352457360155</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799964</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.948434246508058</v>
+        <v>3.043570426928171</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.793570493735396</v>
+        <v>-1.637643045770004</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.230649624700153</v>
+        <v>2.388156784306422</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9677153034753726</v>
+        <v>1.043864310753874</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.529063428593282</v>
+        <v>3.669889013380496</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.9584404001528</v>
+        <v>3.053576580572912</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.766619269408908</v>
+        <v>-1.610691821443516</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.251436268075489</v>
+        <v>2.408943427681759</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9825956495030918</v>
+        <v>1.058744656781593</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.547997789854655</v>
+        <v>3.688823374641869</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.14254353229776</v>
+        <v>3.237679712717872</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.902572277465225</v>
+        <v>-1.746644829499832</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.381158196997923</v>
+        <v>2.538665356604192</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9825956495030918</v>
+        <v>1.058744656781593</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.732100921999615</v>
+        <v>3.872926506786829</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714422</v>
+        <v>3.743925505714426</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.134660227200753</v>
+        <v>3.229796407620865</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.924980395270097</v>
+        <v>-1.769052947304705</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.364311644778967</v>
+        <v>2.521818804385236</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9825956495030918</v>
+        <v>1.058744656781593</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.724217616902608</v>
+        <v>3.865043201689822</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155029</v>
+        <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.13671422675039</v>
+        <v>3.231850407170503</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.072986162749496</v>
+        <v>-1.917058714784104</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.307163337336844</v>
+        <v>2.464670496943114</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.8958686406395503</v>
+        <v>0.972017647918052</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.67423541113412</v>
+        <v>3.815060995921334</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161974</v>
+        <v>3.729452285161979</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.192967944472237</v>
+        <v>3.28810412489235</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.082427088638026</v>
+        <v>-1.926499640672634</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.35964068470328</v>
+        <v>2.517147844309549</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.018295758182942</v>
+        <v>1.094444765461443</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.803945399382003</v>
+        <v>3.944770984169216</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.71494119332163</v>
+        <v>3.714941193321636</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.195859039017538</v>
+        <v>3.290995219437651</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.081140325098469</v>
+        <v>-1.925212877133077</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.363046484664403</v>
+        <v>2.520553644270673</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.019582521722498</v>
+        <v>1.095731529001</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.807608552051037</v>
+        <v>3.948434136838251</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347699</v>
+        <v>3.727898186347704</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.193970851911313</v>
+        <v>3.289107032331426</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.082697379087761</v>
+        <v>-1.926769931122368</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.360535475962462</v>
+        <v>2.518042635568731</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.019582521722498</v>
+        <v>1.095731529001</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.805720364944813</v>
+        <v>3.946545949732026</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887743</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.188791081514176</v>
+        <v>3.283927261934288</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.089969264611225</v>
+        <v>-1.934041816645833</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.352446951355938</v>
+        <v>2.509954110962208</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.012310636199033</v>
+        <v>1.088459643477535</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.796177463233596</v>
+        <v>3.937003048020809</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343066</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.187225091724328</v>
+        <v>3.282361272144441</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.088128245552974</v>
+        <v>-1.932200797587582</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.351617369189391</v>
+        <v>2.509124528795661</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.013578862870502</v>
+        <v>1.089727870149003</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.795372409446629</v>
+        <v>3.936197994233843</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647101</v>
+        <v>3.754911907647107</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.200298498590247</v>
+        <v>3.295434679010359</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.095036951052655</v>
+        <v>-1.939109503087262</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.361927293855437</v>
+        <v>2.519434453461707</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.013578862870502</v>
+        <v>1.089727870149003</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.808445816312548</v>
+        <v>3.949271401099762</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763529</v>
+        <v>3.749896851763533</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.200298498590247</v>
+        <v>3.295434679010359</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.096598593867514</v>
+        <v>-1.940671145902122</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.361302636729493</v>
+        <v>2.518809796335763</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.013578862870502</v>
+        <v>1.089727870149003</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.808445816312548</v>
+        <v>3.949271401099762</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392111</v>
+        <v>3.715834055392117</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.198822539717249</v>
+        <v>3.293958720137361</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.124499380976987</v>
+        <v>-1.968571933011595</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.348666363012706</v>
+        <v>2.506173522618976</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.9789819387275672</v>
+        <v>1.055130946006069</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.786211702953789</v>
+        <v>3.927037287741003</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172523</v>
+        <v>3.684909939172528</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.195586983694447</v>
+        <v>3.29072316411456</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.127532378489661</v>
+        <v>-1.971604930524269</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.344217607984835</v>
+        <v>2.501724767591105</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.9759489412148934</v>
+        <v>1.052097948493395</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.781156348423384</v>
+        <v>3.921981933210597</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971075</v>
+        <v>3.619362241971081</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.262292943284951</v>
+        <v>3.357429123705064</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.147593699766168</v>
+        <v>-1.991666251800776</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.402899039064736</v>
+        <v>2.560406198671006</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.9558876199383863</v>
+        <v>1.032036627216888</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.835825515247983</v>
+        <v>3.976651100035197</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199802</v>
+        <v>3.640764248199807</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.402604662286798</v>
+        <v>3.497740842706911</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.404314517760992</v>
+        <v>-2.2483870697956</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.440522430868654</v>
+        <v>2.598029590474924</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.8474730457945715</v>
+        <v>0.9236220530730729</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.911088489763541</v>
+        <v>4.051914074550755</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622233</v>
+        <v>3.668303164622238</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.471584931432438</v>
+        <v>3.566721111852551</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.558300935537133</v>
+        <v>-2.40237348757174</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.447908132903837</v>
+        <v>2.605415292510108</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.8474730457945715</v>
+        <v>0.9236220530730729</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.980068758909181</v>
+        <v>4.120894343696395</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808525</v>
+        <v>3.619937176808531</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.457636133552559</v>
+        <v>3.552772313972671</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.507779031709467</v>
+        <v>-2.351851583744074</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.454168096555025</v>
+        <v>2.611675256161294</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.8474730457945715</v>
+        <v>0.9236220530730729</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.966119961029301</v>
+        <v>4.106945545816515</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.65634689399489</v>
+        <v>3.656346893994896</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.469506622607973</v>
+        <v>3.564642803028085</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.760254185717192</v>
+        <v>-2.604326737751799</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.365048524007349</v>
+        <v>2.522555683613619</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.8474730457945715</v>
+        <v>0.9236220530730729</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.977990450084716</v>
+        <v>4.118816034871929</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358294</v>
+        <v>3.674042696358299</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.470717157126916</v>
+        <v>3.565853337547029</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.0297269876389</v>
+        <v>-2.873799539673507</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.258469937757609</v>
+        <v>2.415977097363879</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.8474730457945715</v>
+        <v>0.9236220530730729</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.97920098460366</v>
+        <v>4.120026569390873</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637082</v>
+        <v>3.663523617637088</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.474838899354238</v>
+        <v>3.569975079774351</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.187271059368341</v>
+        <v>-3.031343611402948</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.199574051293154</v>
+        <v>2.357081210899424</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.7805712406542971</v>
+        <v>0.8567202479327984</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.943181643746817</v>
+        <v>4.08400722853403</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301339</v>
+        <v>3.652163313301344</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.469916752090427</v>
+        <v>3.56505293251054</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.316121610070387</v>
+        <v>-3.160194162104994</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.143111683748525</v>
+        <v>2.300618843354795</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.7395778318035755</v>
+        <v>0.8157268390820769</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.913663451172573</v>
+        <v>4.054489035959786</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.827608339930108</v>
+        <v>3.846415132844546</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.555054617469487</v>
+        <v>3.733190021059563</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.316121610070387</v>
+        <v>-3.160194162104994</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.143111683748525</v>
+        <v>2.300618843354795</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.7395778318035755</v>
+        <v>0.8157268390820769</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.548118414455855</v>
+        <v>3.726253818045931</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240712.xlsx
+++ b/tame_output/ON/bt/strategyON_20240712.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>63.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,17 +844,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>80.8%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-70.8%</t>
+          <t>-68.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.4%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.2%</t>
+          <t>121.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>96.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-65.7%</t>
+          <t>-63.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.5%</t>
+          <t>458.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-9.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-477.6%</t>
+          <t>-440.5%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-146.2%</t>
+          <t>-131.3%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-10.0%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>124.3%</t>
+          <t>118.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-123.5%</t>
+          <t>-129.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-142.4%</t>
+          <t>-117.3%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>73.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.7%</t>
+          <t>-24.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-18.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-73.4%</t>
+          <t>-54.2%</t>
         </is>
       </c>
     </row>
@@ -46608,16 +46608,16 @@
         <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.330640503013055</v>
+        <v>-2.959237800206242</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.173695774257006</v>
+        <v>1.322256855379731</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3269617589071764</v>
+        <v>0.5781991861259604</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.702485455120281</v>
+        <v>2.853227911451551</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.431838284450228</v>
+        <v>-3.060435581643414</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.132420583578638</v>
+        <v>1.280981664701363</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2585529453618572</v>
+        <v>0.5097903725806412</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.660644088889591</v>
+        <v>2.811386545220861</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.425327317835915</v>
+        <v>-3.053924615029102</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.13262493177868</v>
+        <v>1.281186012901405</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2585529453618572</v>
+        <v>0.5097903725806412</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.658244050443908</v>
+        <v>2.808986506775178</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.406289190128618</v>
+        <v>-3.034886487321804</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.136764902069843</v>
+        <v>1.285325983192569</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2003693340306627</v>
+        <v>0.4516067612494467</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.619858602853436</v>
+        <v>2.770601059184706</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.437415821279236</v>
+        <v>-3.066013118472422</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.301896118548277</v>
+        <v>1.450457199671002</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2003693340306627</v>
+        <v>0.4516067612494467</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.797440471792116</v>
+        <v>2.948182928123387</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.451282582613153</v>
+        <v>-3.07987987980634</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.297182743000843</v>
+        <v>1.445743824123569</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1625114172968398</v>
+        <v>0.4137488445156237</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.775559050737956</v>
+        <v>2.926301507069226</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.406478411073223</v>
+        <v>-3.03507570826641</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.321112942013741</v>
+        <v>1.469674023136467</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1625114172968398</v>
+        <v>0.4137488445156237</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.781567581134882</v>
+        <v>2.932310037466152</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.582010952033977</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.258735440838221</v>
+        <v>-2.887332738031408</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.278160351384942</v>
+        <v>1.426721432507667</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3303187745317229</v>
+        <v>0.5815562017505069</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.780202216753011</v>
+        <v>2.930944673084282</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.584804573565458</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.360750123369442</v>
+        <v>-2.989347420562629</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.240148099903934</v>
+        <v>1.38870918102666</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3303187745317229</v>
+        <v>0.5815562017505069</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.782995838284492</v>
+        <v>2.933738294615763</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.585466921957117</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.354597417316658</v>
+        <v>-2.983194714509844</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.243271530716706</v>
+        <v>1.391832611839432</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3364714805845072</v>
+        <v>0.5877089078032912</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.787349810307821</v>
+        <v>2.938092266639092</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.584547398697227</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.371406715467159</v>
+        <v>-3.000004012660346</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.235628288196616</v>
+        <v>1.384189369319341</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3196621824340056</v>
+        <v>0.5708996096527896</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.776344708157631</v>
+        <v>2.927087164488901</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.650882952494048</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.309108716691037</v>
+        <v>-2.937706013884224</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.326883041503886</v>
+        <v>1.475444122626611</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3196621824340056</v>
+        <v>0.5708996096527896</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.842680261954452</v>
+        <v>2.993422718285722</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.453174954208175</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.107318519025879</v>
+        <v>-2.735915816219066</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.209891122284076</v>
+        <v>1.358452203406801</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.51768037460316</v>
+        <v>0.768917801821944</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.763783178970071</v>
+        <v>2.914525635301342</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.52346518653035</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.942505515947032</v>
+        <v>-2.571102813140219</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.34610655583779</v>
+        <v>1.494667636960515</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6824933776820069</v>
+        <v>0.933730804900791</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.932961213139555</v>
+        <v>3.083703669470825</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.538092922646394</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.040246060572007</v>
+        <v>-2.668843357765193</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.321638074103844</v>
+        <v>1.470199155226569</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6666040995490268</v>
+        <v>0.9178415267678108</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.93805538237581</v>
+        <v>3.08879783870708</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.536628903471065</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.216583820694936</v>
+        <v>-2.845181117888123</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.249638950879344</v>
+        <v>1.398200032002069</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4902663394260973</v>
+        <v>0.7415037666448814</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.830788707126724</v>
+        <v>2.981531163457995</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.535120521510994</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.140161774263009</v>
+        <v>-2.768759071456196</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.278699387492043</v>
+        <v>1.427260468614769</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4902663394260973</v>
+        <v>0.7415037666448814</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.829280325166653</v>
+        <v>2.980022781497923</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.53498338894643</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.095788642624441</v>
+        <v>-2.724385939817627</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.296311507582907</v>
+        <v>1.444872588705632</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5346394710646659</v>
+        <v>0.78587689828345</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.85576707158523</v>
+        <v>3.0065095279165</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.529377183085021</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.972954421737273</v>
+        <v>-2.60155171893046</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.339838990076364</v>
+        <v>1.488400071199089</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5346394710646659</v>
+        <v>0.78587689828345</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.85016086572382</v>
+        <v>3.000903322055091</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.535758940112825</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.925298691176217</v>
+        <v>-2.553895988369404</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.365283039328591</v>
+        <v>1.513844120451316</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.5822952016257216</v>
+        <v>0.8335326288445056</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.885136061088259</v>
+        <v>3.035878517419529</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.54065131348755</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.824780532677463</v>
+        <v>-2.453377829870649</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.410382676102818</v>
+        <v>1.558943757225543</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6828133601244761</v>
+        <v>0.9340507873432602</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.950339329562236</v>
+        <v>3.101081785893506</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.527405985963422</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.885447123079852</v>
+        <v>-2.514044420273038</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.372870712417734</v>
+        <v>1.52143179354046</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6011150434059425</v>
+        <v>0.8523524706247265</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.888075012006988</v>
+        <v>3.038817468338259</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.531503688574051</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.840608721471454</v>
+        <v>-2.46920601866464</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.394903775671722</v>
+        <v>1.543464856794448</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6056584763508119</v>
+        <v>0.856895903569596</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.894898774384538</v>
+        <v>3.045641230715809</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.535664628205129</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.941367357228452</v>
+        <v>-2.569964654421639</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.358761261000001</v>
+        <v>1.507322342122726</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5168329076238065</v>
+        <v>0.7680703348425906</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.845764372779413</v>
+        <v>2.996506829110683</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.541544230732966</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.897164520142552</v>
+        <v>-2.525761817335738</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.382321998362198</v>
+        <v>1.530883079484924</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.561035744709707</v>
+        <v>0.812273171928491</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.87816567755879</v>
+        <v>3.028908133890061</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.539954231202214</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.934143547805995</v>
+        <v>-2.562740844999182</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.365940387766069</v>
+        <v>1.514501468888794</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.5980096465010375</v>
+        <v>0.8492470737198216</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.898760019102836</v>
+        <v>3.049502475434107</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.591201996385253</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.775852130266723</v>
+        <v>-2.404449427459909</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.480504719964817</v>
+        <v>1.629065801087542</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.5980096465010375</v>
+        <v>0.8492470737198216</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.950007784285876</v>
+        <v>3.100750240617146</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.589642700979506</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.568210126632247</v>
+        <v>-2.196807423825433</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.562002226012861</v>
+        <v>1.710563307135586</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8056516501355137</v>
+        <v>1.056889077354298</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.073033691060815</v>
+        <v>3.223776147392085</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.584590929217776</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.517178033909719</v>
+        <v>-2.145775331102905</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.577363291340142</v>
+        <v>1.725924372462867</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8566837428580416</v>
+        <v>1.107921170076826</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.098601174932602</v>
+        <v>3.249343631263872</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.601778333310481</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.451953852782513</v>
+        <v>-2.080551149975699</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.620640367883729</v>
+        <v>1.769201449006454</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9219079239852472</v>
+        <v>1.173145351204031</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.15492308770163</v>
+        <v>3.3056655440329</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.597739305609762</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.414526832711379</v>
+        <v>-2.043124129904565</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.631572148211463</v>
+        <v>1.780133229334188</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.9271594620144289</v>
+        <v>1.178396889233213</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.154034982818419</v>
+        <v>3.30477743914969</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.598996097941002</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.278711040780695</v>
+        <v>-1.907308337973882</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.687155257314977</v>
+        <v>1.835716338437702</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.01433581429035</v>
+        <v>1.265573241509134</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.207597586515212</v>
+        <v>3.358340042846482</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.759553868962213</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.22496622635349</v>
+        <v>-1.853563523546677</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.86921095410707</v>
+        <v>2.017772035229795</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.024399123730812</v>
+        <v>1.275636550949596</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.3741933432007</v>
+        <v>3.524935799531971</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.87966677818003</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.201174657747348</v>
+        <v>-1.829771954940535</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.998840490767344</v>
+        <v>2.147401571890069</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.048190692336954</v>
+        <v>1.299428119555738</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.508581193582203</v>
+        <v>3.659323649913473</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.871374754193889</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.17509057348354</v>
+        <v>-1.803687870676727</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.000982100486726</v>
+        <v>2.149543181609451</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.048190692336954</v>
+        <v>1.299428119555738</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.500289169596062</v>
+        <v>3.651031625927332</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.869567949777668</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.096959392634593</v>
+        <v>-1.72555668982778</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.030427768410084</v>
+        <v>2.178988849532809</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.122367503220639</v>
+        <v>1.373604930439423</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.542988451710052</v>
+        <v>3.693730908041323</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.88712235550446</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.08806693124131</v>
+        <v>-1.716664228434497</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.051539158694188</v>
+        <v>2.200100239816914</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.122367503220639</v>
+        <v>1.373604930439423</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.560542857436843</v>
+        <v>3.711285313768114</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.878977402909044</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.256543048211188</v>
+        <v>-1.885140345404375</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.976003759310821</v>
+        <v>2.124564840433547</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.094419667504058</v>
+        <v>1.345657094722842</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.535629203411479</v>
+        <v>3.686371659742749</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.860247100096906</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.558743519349605</v>
+        <v>-1.187340816542791</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.236393268043317</v>
+        <v>2.384954349166042</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.024071608133647</v>
+        <v>1.275309035352431</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.474690064977094</v>
+        <v>3.625432521308364</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.85091112259381</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.536022415666452</v>
+        <v>-1.164619712859639</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.236145732013482</v>
+        <v>2.384706813136207</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.024071608133647</v>
+        <v>1.275309035352431</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.465354087473999</v>
+        <v>3.616096543805269</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.009817248444979</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.534297372376409</v>
+        <v>-1.162894669569595</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.395741875180669</v>
+        <v>2.544302956303394</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.025796651423691</v>
+        <v>1.277034078642475</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.625295239299194</v>
+        <v>3.776037695630464</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.046895070938626</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.689078379154664</v>
+        <v>-1.317675676347851</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.370907294963013</v>
+        <v>2.519468376085738</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9924289773692148</v>
+        <v>1.243666404587999</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.642352457360155</v>
+        <v>3.793094913691425</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.043570426928171</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.637643045770004</v>
+        <v>-1.266240342963191</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.388156784306422</v>
+        <v>2.536717865429147</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.043864310753874</v>
+        <v>1.295101737972658</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.669889013380496</v>
+        <v>3.820631469711766</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.053576580572912</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.610691821443516</v>
+        <v>-1.239289118636703</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.408943427681759</v>
+        <v>2.557504508804484</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.058744656781593</v>
+        <v>1.309982084000378</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.688823374641869</v>
+        <v>3.839565830973139</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.237679712717872</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.746644829499832</v>
+        <v>-1.375242126693019</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.538665356604192</v>
+        <v>2.687226437726917</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.058744656781593</v>
+        <v>1.309982084000378</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.872926506786829</v>
+        <v>4.023668963118099</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.229796407620865</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.769052947304705</v>
+        <v>-1.397650244497891</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.521818804385236</v>
+        <v>2.670379885507962</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.058744656781593</v>
+        <v>1.309982084000378</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.865043201689822</v>
+        <v>4.015785658021092</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.231850407170503</v>
       </c>
       <c r="D2005" t="n">
-        <v>-1.917058714784104</v>
+        <v>-1.54565601197729</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.464670496943114</v>
+        <v>2.613231578065839</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.972017647918052</v>
+        <v>1.223255075136836</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.815060995921334</v>
+        <v>3.965803452252604</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.28810412489235</v>
       </c>
       <c r="D2006" t="n">
-        <v>-1.926499640672634</v>
+        <v>-1.55509693786582</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.517147844309549</v>
+        <v>2.665708925432275</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.094444765461443</v>
+        <v>1.345682192680227</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.944770984169216</v>
+        <v>4.095513440500486</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.290995219437651</v>
       </c>
       <c r="D2007" t="n">
-        <v>-1.925212877133077</v>
+        <v>-1.553810174326264</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.520553644270673</v>
+        <v>2.669114725393398</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.095731529001</v>
+        <v>1.346968956219784</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.948434136838251</v>
+        <v>4.099176593169521</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.289107032331426</v>
       </c>
       <c r="D2008" t="n">
-        <v>-1.926769931122368</v>
+        <v>-1.555367228315555</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.518042635568731</v>
+        <v>2.666603716691457</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.095731529001</v>
+        <v>1.346968956219784</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.946545949732026</v>
+        <v>4.097288406063297</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.283927261934288</v>
       </c>
       <c r="D2009" t="n">
-        <v>-1.934041816645833</v>
+        <v>-1.56263911383902</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.509954110962208</v>
+        <v>2.658515192084933</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.088459643477535</v>
+        <v>1.339697070696319</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.937003048020809</v>
+        <v>4.08774550435208</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.282361272144441</v>
       </c>
       <c r="D2010" t="n">
-        <v>-1.932200797587582</v>
+        <v>-1.560798094780768</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.509124528795661</v>
+        <v>2.657685609918386</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.089727870149003</v>
+        <v>1.340965297367787</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.936197994233843</v>
+        <v>4.086940450565113</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.295434679010359</v>
       </c>
       <c r="D2011" t="n">
-        <v>-1.939109503087262</v>
+        <v>-1.567706800280449</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.519434453461707</v>
+        <v>2.667995534584433</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.089727870149003</v>
+        <v>1.340965297367787</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.949271401099762</v>
+        <v>4.100013857431032</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.295434679010359</v>
       </c>
       <c r="D2012" t="n">
-        <v>-1.940671145902122</v>
+        <v>-1.569268443095309</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.518809796335763</v>
+        <v>2.667370877458489</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.089727870149003</v>
+        <v>1.340965297367787</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.949271401099762</v>
+        <v>4.100013857431032</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.293958720137361</v>
       </c>
       <c r="D2013" t="n">
-        <v>-1.968571933011595</v>
+        <v>-1.597169230204782</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.506173522618976</v>
+        <v>2.654734603741701</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.055130946006069</v>
+        <v>1.306368373224853</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.927037287741003</v>
+        <v>4.077779744072274</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.29072316411456</v>
       </c>
       <c r="D2014" t="n">
-        <v>-1.971604930524269</v>
+        <v>-1.600202227717455</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.501724767591105</v>
+        <v>2.650285848713831</v>
       </c>
       <c r="F2014" t="n">
-        <v>1.052097948493395</v>
+        <v>1.303335375712179</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.921981933210597</v>
+        <v>4.072724389541867</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.357429123705064</v>
       </c>
       <c r="D2015" t="n">
-        <v>-1.991666251800776</v>
+        <v>-1.620263548993963</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.560406198671006</v>
+        <v>2.708967279793732</v>
       </c>
       <c r="F2015" t="n">
-        <v>1.032036627216888</v>
+        <v>1.283274054435672</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.976651100035197</v>
+        <v>4.127393556366467</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.497740842706911</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.2483870697956</v>
+        <v>-1.876984366988786</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.598029590474924</v>
+        <v>2.746590671597649</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.9236220530730729</v>
+        <v>1.174859480291857</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.051914074550755</v>
+        <v>4.202656530882026</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.566721111852551</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.40237348757174</v>
+        <v>-2.030970784764927</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.605415292510108</v>
+        <v>2.753976373632833</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.9236220530730729</v>
+        <v>1.174859480291857</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.120894343696395</v>
+        <v>4.271636800027665</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.552772313972671</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.351851583744074</v>
+        <v>-1.980448880937261</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.611675256161294</v>
+        <v>2.76023633728402</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.9236220530730729</v>
+        <v>1.174859480291857</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.106945545816515</v>
+        <v>4.257688002147786</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.564642803028085</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.604326737751799</v>
+        <v>-2.232924034944985</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.522555683613619</v>
+        <v>2.671116764736344</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.9236220530730729</v>
+        <v>1.174859480291857</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.118816034871929</v>
+        <v>4.2695584912032</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.565853337547029</v>
       </c>
       <c r="D2020" t="n">
-        <v>-2.873799539673507</v>
+        <v>-2.502396836866693</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.415977097363879</v>
+        <v>2.564538178486605</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.9236220530730729</v>
+        <v>1.174859480291857</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.120026569390873</v>
+        <v>4.270769025722144</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.569975079774351</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.031343611402948</v>
+        <v>-2.659940908596135</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.357081210899424</v>
+        <v>2.505642292022149</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.8567202479327984</v>
+        <v>1.107957675151582</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.08400722853403</v>
+        <v>4.2347496848653</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.56505293251054</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.160194162104994</v>
+        <v>-2.788791459298181</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.300618843354795</v>
+        <v>2.44917992447752</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.8157268390820769</v>
+        <v>1.066964266300861</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.054489035959786</v>
+        <v>4.205231492291057</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.846415132844546</v>
+        <v>3.918601928327767</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.733190021059563</v>
+        <v>3.92473845743903</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.160194162104994</v>
+        <v>-2.788791459298181</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.300618843354795</v>
+        <v>2.44917992447752</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.8157268390820769</v>
+        <v>1.066964266300861</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.726253818045931</v>
+        <v>3.917802254425398</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240712.xlsx
+++ b/tame_output/ON/bt/strategyON_20240712.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>24.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,37 +844,37 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>71.1%</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>31.6%</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>67.0%</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>32.2%</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>69.4%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-68.6%</t>
+          <t>-70.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>109.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.2%</t>
+          <t>122.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.4%</t>
+          <t>97.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-49.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-63.1%</t>
+          <t>-65.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>458.5%</t>
+          <t>453.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-440.5%</t>
+          <t>-471.0%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,57 +1140,57 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.6%</t>
+          <t>-36.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-131.3%</t>
+          <t>-119.0%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>118.4%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-129.8%</t>
+          <t>-130.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-117.3%</t>
+          <t>-134.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>87.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,57 +1456,57 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.4%</t>
+          <t>-24.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>81.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.4%</t>
+          <t>-18.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-54.2%</t>
+          <t>-11.1%</t>
         </is>
       </c>
     </row>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.554990769168801</v>
+        <v>-7.337703673577133</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1291072421219868</v>
+        <v>0.2160220803586541</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.544882012681864</v>
+        <v>-1.327594917090197</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.224530766494136</v>
+        <v>2.354903023849137</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.391590898229438</v>
+        <v>-7.174303802637771</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1938340117184887</v>
+        <v>0.280748849955156</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.381482141742502</v>
+        <v>-1.164195046150834</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.321937510278511</v>
+        <v>2.452309767633511</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.15810967599984</v>
+        <v>-6.940822580408172</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2951509294481807</v>
+        <v>0.3820657676848476</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.148000919512903</v>
+        <v>-0.9307138239212358</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.469950672454122</v>
+        <v>2.600322929809122</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.008443284992325</v>
+        <v>-6.791156189400657</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3521252755382274</v>
+        <v>0.4390401137748947</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.055097428270367</v>
+        <v>-0.8378103326786999</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.522800556886684</v>
+        <v>2.653172814241685</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.876167811361438</v>
+        <v>-6.65888071576977</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4004029517376089</v>
+        <v>0.4873177899742762</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.9228219546394807</v>
+        <v>-0.7055348590478132</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.597533327812243</v>
+        <v>2.727905585167244</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.720429478801696</v>
+        <v>-6.503142383210029</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4655133454491427</v>
+        <v>0.5524281836858096</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.7670836220797391</v>
+        <v>-0.5497965264880716</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.693791388035725</v>
+        <v>2.824163645390726</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.471429680118115</v>
+        <v>-6.254142584526448</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5780196061462335</v>
+        <v>0.6649344443829008</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.7670836220797391</v>
+        <v>-0.5497965264880716</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.706697729259384</v>
+        <v>2.837069986614384</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.57701966989122</v>
+        <v>-6.359732574299552</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4078076806377733</v>
+        <v>0.4947225188744402</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.8726736118528435</v>
+        <v>-0.6553865162611761</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.515367805796302</v>
+        <v>2.645740063151303</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.595754572009817</v>
+        <v>-6.378467476418149</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4488580616674209</v>
+        <v>0.5357728999040878</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.8782696215129748</v>
+        <v>-0.6609825259213074</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.56055454187731</v>
+        <v>2.690926799232311</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.447814530602217</v>
+        <v>-6.23052743501055</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3881551555422931</v>
+        <v>0.47506999377896</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.8579487056044173</v>
+        <v>-0.6406616100127498</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.452868168734277</v>
+        <v>2.583240426089278</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.394845008348229</v>
+        <v>-6.177557912756561</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4006289781904102</v>
+        <v>0.4875438164270771</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.8049791833504284</v>
+        <v>-0.5876920877587609</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.475935895833192</v>
+        <v>2.606308153188193</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.351296601577539</v>
+        <v>-6.134009505985871</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4110877288035932</v>
+        <v>0.4980025670402601</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.8049791833504284</v>
+        <v>-0.5876920877587609</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.468975283738099</v>
+        <v>2.5993475410931</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.10914820812368</v>
+        <v>-5.891861112532013</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5224094405662796</v>
+        <v>0.6093242788029465</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.8049791833504284</v>
+        <v>-0.5876920877587609</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.483437638119242</v>
+        <v>2.613809895474243</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.000889071001159</v>
+        <v>-5.783601975409491</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5602452158744833</v>
+        <v>0.6471600541111502</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.8049791833504284</v>
+        <v>-0.5876920877587609</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.477969758578437</v>
+        <v>2.608342015933438</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.877597936184028</v>
+        <v>-5.66031084059236</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6070597638119124</v>
+        <v>0.6939746020485797</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.6816880485332979</v>
+        <v>-0.4644009529416304</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.549442533479292</v>
+        <v>2.679814790834293</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.856448737280584</v>
+        <v>-5.639161641688917</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6232204216106152</v>
+        <v>0.7101352598472821</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.6605388496298545</v>
+        <v>-0.4432517540381871</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.569833031058684</v>
+        <v>2.700205288413684</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.61268329529714</v>
+        <v>-5.395396199705472</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7165073067510432</v>
+        <v>0.8034221449877106</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.6605388496298545</v>
+        <v>-0.4432517540381871</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.565613739405734</v>
+        <v>2.695985996760735</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.510920475019845</v>
+        <v>-5.293633379428178</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7593367487819775</v>
+        <v>0.8462515870186444</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.6473197812374258</v>
+        <v>-0.4300326856457584</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.575669494361208</v>
+        <v>2.706041751716208</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.261070081070771</v>
+        <v>-5.043782985479103</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8520189813453092</v>
+        <v>0.9389338195819765</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.6473197812374258</v>
+        <v>-0.4300326856457584</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.56841156934491</v>
+        <v>2.69878382669991</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.085177988603338</v>
+        <v>-4.867890893011671</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9259749418529313</v>
+        <v>1.012889780089598</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.6473197812374258</v>
+        <v>-0.4300326856457584</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.572010692865558</v>
+        <v>2.702382950220559</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.913731525580874</v>
+        <v>-4.696444429989207</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.00788103311647</v>
+        <v>1.094795871353137</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.4758733182149627</v>
+        <v>-0.2585862226232952</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.68820607673359</v>
+        <v>2.818578334088591</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.839441959842535</v>
+        <v>-4.622154864250868</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.036617337028103</v>
+        <v>1.12353217526477</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.4015837524766234</v>
+        <v>-0.1842966568849559</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.731800293792891</v>
+        <v>2.862172551147891</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.775806217608601</v>
+        <v>-4.558519122016934</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.066766434975994</v>
+        <v>1.153681273212661</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.3379480102426889</v>
+        <v>-0.1206609146510214</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.774676540187568</v>
+        <v>2.905048797542569</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.664379458282681</v>
+        <v>-4.447092362691014</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.092531397490158</v>
+        <v>1.179446235726824</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.3379480102426889</v>
+        <v>-0.1206609146510214</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.755870798971364</v>
+        <v>2.886243056326365</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.79769488424229</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.42394896147782</v>
+        <v>-4.206661865886153</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.190446672836979</v>
+        <v>1.277361511073646</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.09751751343782861</v>
+        <v>0.1197695821538389</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.901872173679158</v>
+        <v>3.032244431034158</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.351706393306626</v>
+        <v>-4.134419297714959</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.223273013940277</v>
+        <v>1.310187852176944</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.09751751343782861</v>
+        <v>0.1197695821538389</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.905801487513978</v>
+        <v>3.036173744868978</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.298708071025238</v>
+        <v>-4.081420975433571</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.245150926770172</v>
+        <v>1.332065765006839</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.04218125443588977</v>
+        <v>0.1751058411557777</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.939681826832481</v>
+        <v>3.070054084187482</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502336</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.189903185545511</v>
+        <v>-3.972616089953844</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.285670952182057</v>
+        <v>1.372585790418723</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.04218125443588977</v>
+        <v>0.1751058411557777</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.936679898052475</v>
+        <v>3.067052155407475</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.9698823875085</v>
+        <v>-3.758096420540424</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.375258308407475</v>
+        <v>1.459972695194706</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.09903859063209047</v>
+        <v>0.258168537485034</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.022990842103877</v>
+        <v>3.118468810215643</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.837014698445222</v>
+        <v>-3.625228731477146</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.44429956683461</v>
+        <v>1.52901395362184</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.09903859063209047</v>
+        <v>0.258168537485034</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.0388850249057</v>
+        <v>3.134362993017466</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.716841615080723</v>
+        <v>-3.505055648112647</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.493514644620711</v>
+        <v>1.578229031407942</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.2192116739965894</v>
+        <v>0.378341620849533</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.112134719364701</v>
+        <v>3.207612687476467</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.572169469980985</v>
+        <v>-3.360383503012909</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.561471605222046</v>
+        <v>1.646185992009277</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.3638838190963268</v>
+        <v>0.5230137659492704</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.209026108985984</v>
+        <v>3.30450407709775</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.7358392229421</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.632044297338678</v>
+        <v>-3.420258330370602</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.523559165680395</v>
+        <v>1.608273552467625</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.3040089917386347</v>
+        <v>0.4631389385915783</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.159138703972794</v>
+        <v>3.25461667208456</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.51222406642784</v>
+        <v>-3.300438099459764</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.586776427278938</v>
+        <v>1.671490814066169</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.3040089917386347</v>
+        <v>0.4631389385915783</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.174427873207003</v>
+        <v>3.269905841318769</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430692</v>
+        <v>3.72914639843069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.514693772889646</v>
+        <v>-3.30290780592157</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.493432744016657</v>
+        <v>1.578147130803888</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.3015392852768286</v>
+        <v>0.4606692321297721</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.080590248652361</v>
+        <v>3.176068216764127</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.583063959213656</v>
+        <v>-3.37127799224558</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.385346530972355</v>
+        <v>1.470060917759586</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.3108149843130435</v>
+        <v>0.4699449311659871</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.005417529559391</v>
+        <v>3.100895497671157</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.596852012060703</v>
+        <v>-3.385066045092627</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.370268018465428</v>
+        <v>1.454982405252658</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.3108149843130435</v>
+        <v>0.4699449311659871</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.995854238191282</v>
+        <v>3.091332206303048</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.627845171389408</v>
+        <v>-3.416059204421332</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.182580319774332</v>
+        <v>1.267294706561563</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.3108149843130435</v>
+        <v>0.4699449311659871</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.820563803231669</v>
+        <v>2.916041771343435</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.452370911596939</v>
+        <v>-3.240584944628863</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.257337255683108</v>
+        <v>1.342051642470338</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.3108149843130435</v>
+        <v>0.4699449311659871</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.825131035223457</v>
+        <v>2.920609003335223</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.563307164238187</v>
+        <v>-3.351521197270111</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.188704783387815</v>
+        <v>1.273419170175046</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.3108149843130435</v>
+        <v>0.4699449311659871</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.800873063984664</v>
+        <v>2.89635103209643</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.617515458616743</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.529643618765906</v>
+        <v>-3.31785765179783</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.205301586796634</v>
+        <v>1.290015973583864</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.3444785297853253</v>
+        <v>0.5036084766382689</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.824202576487939</v>
+        <v>2.919680544599705</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.627687845048876</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.469790999562183</v>
+        <v>-3.258005032594106</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.239415020910255</v>
+        <v>1.324129407697486</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.3444785297853253</v>
+        <v>0.5036084766382689</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.834374962920071</v>
+        <v>2.929852931031837</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.622634115622736</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.383547536535805</v>
+        <v>-3.171761569567729</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.268858676694667</v>
+        <v>1.353573063481897</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.3444785297853253</v>
+        <v>0.5036084766382689</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.829321233493931</v>
+        <v>2.924799201605698</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.614409891067262</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.428854355934785</v>
+        <v>-3.217068388966709</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.2425117243796</v>
+        <v>1.327226111166831</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.3036683667760945</v>
+        <v>0.4627983136290381</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.796610911132919</v>
+        <v>2.892088879244685</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.614961764100363</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.457887460637087</v>
+        <v>-3.24610149366901</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.231450355531781</v>
+        <v>1.316164742319012</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.3036683667760945</v>
+        <v>0.4627983136290381</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.79716278416602</v>
+        <v>2.892640752277786</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.544234455991729</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.365076979186227</v>
+        <v>-3.153291012218151</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.197847240003491</v>
+        <v>1.282561626790721</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.3964788482269539</v>
+        <v>0.5556087950798975</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.782121764927902</v>
+        <v>2.877599733039667</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.54610793191633</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.409466448515655</v>
+        <v>-3.197680481547579</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.18196492819632</v>
+        <v>1.266679314983551</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.3520893788975262</v>
+        <v>0.5112193257504698</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.757361559254845</v>
+        <v>2.852839527366612</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.541183640428053</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.296795230279405</v>
+        <v>-3.085009263311329</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.222109124002543</v>
+        <v>1.306823510789774</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4647605971337764</v>
+        <v>0.6238905439867199</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.820039998708319</v>
+        <v>2.915517966820085</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.54667493625872</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.184418229096732</v>
+        <v>-2.972632262128656</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.27255122030628</v>
+        <v>1.35726560709351</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4647605971337764</v>
+        <v>0.6238905439867199</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.825531294538986</v>
+        <v>2.921009262650752</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.558172138027259</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.212198626998085</v>
+        <v>-3.000412660030009</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.272936262914278</v>
+        <v>1.357650649701508</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4369801992324234</v>
+        <v>0.5961101460853668</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.820360257566713</v>
+        <v>2.915838225678479</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.396527858027912</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.295199908023364</v>
+        <v>-3.083413941055288</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.078091470504819</v>
+        <v>1.16280585729205</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4184093147052496</v>
+        <v>0.5775392615581931</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.647573446851062</v>
+        <v>2.743051414962828</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.516677518747118</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.403813986466695</v>
+        <v>-3.192028019498619</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.154795499846692</v>
+        <v>1.239509886633923</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4184093147052496</v>
+        <v>0.5775392615581931</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.767723107570268</v>
+        <v>2.863201075682034</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.368404948218553</v>
+        <v>-3.156618981250476</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.183472141248272</v>
+        <v>1.268186528035503</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4184093147052496</v>
+        <v>0.5775392615581931</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.782236133672591</v>
+        <v>2.877714101784357</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913426</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.330021285660401</v>
+        <v>-3.118235318692325</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.196245047613901</v>
+        <v>1.280959434401132</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4567929772634008</v>
+        <v>0.6159229241163443</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.80268577254985</v>
+        <v>2.898163740661616</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.152904955625235</v>
+        <v>-2.941118988657159</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.26382060847327</v>
+        <v>1.348534995260501</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4567929772634008</v>
+        <v>0.6159229241163443</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.799414801395153</v>
+        <v>2.894892769506919</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.197997200458781</v>
+        <v>-2.986211233490705</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.246467102301765</v>
+        <v>1.331181489088996</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.394896934094011</v>
+        <v>0.5540268809469545</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.762960567255432</v>
+        <v>2.858438535367198</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.018621779220013</v>
+        <v>-2.806835812251937</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.312004246103687</v>
+        <v>1.396718632890917</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5516736922647296</v>
+        <v>0.7108036391176732</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.850813597464277</v>
+        <v>2.946291565576043</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.06363599274062</v>
+        <v>-2.851850025772543</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.274806016027034</v>
+        <v>1.359520402814264</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.521324796950125</v>
+        <v>0.6804547438030686</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.813411715607104</v>
+        <v>2.90888968371887</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509537</v>
+        <v>3.737026608509535</v>
       </c>
       <c r="C1959" t="n">
         <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-2.959237800206242</v>
+        <v>-3.118854536044979</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.322256855379731</v>
+        <v>1.258410161044236</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5781991861259604</v>
+        <v>0.48609170576012</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.853227911451551</v>
+        <v>2.797963423232047</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760813</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.060435581643414</v>
+        <v>-3.220052317482152</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.280981664701363</v>
+        <v>1.217134970365868</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5097903725806412</v>
+        <v>0.4176828922148008</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.811386545220861</v>
+        <v>2.756122057001357</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.053924615029102</v>
+        <v>-3.213541350867839</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.281186012901405</v>
+        <v>1.21733931856591</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5097903725806412</v>
+        <v>0.4176828922148008</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.808986506775178</v>
+        <v>2.753722018555674</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.034886487321804</v>
+        <v>-3.194503223160542</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.285325983192569</v>
+        <v>1.221479288857074</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4516067612494467</v>
+        <v>0.3594992808836063</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.770601059184706</v>
+        <v>2.715336570965202</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131249</v>
       </c>
       <c r="C1963" t="n">
         <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.066013118472422</v>
+        <v>-3.22562985431116</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.450457199671002</v>
+        <v>1.386610505335507</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4516067612494467</v>
+        <v>0.3594992808836063</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.948182928123387</v>
+        <v>2.892918439903883</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.07987987980634</v>
+        <v>-3.239496615645077</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.445743824123569</v>
+        <v>1.381897129788074</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.4137488445156237</v>
+        <v>0.3216413641497833</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.926301507069226</v>
+        <v>2.871037018849722</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.03507570826641</v>
+        <v>-3.194692444105147</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.469674023136467</v>
+        <v>1.405827328800972</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4137488445156237</v>
+        <v>0.3216413641497833</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.932310037466152</v>
+        <v>2.877045549246648</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.582010952033977</v>
       </c>
       <c r="D1966" t="n">
-        <v>-2.887332738031408</v>
+        <v>-3.046949473870145</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.426721432507667</v>
+        <v>1.362874738172172</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5815562017505069</v>
+        <v>0.4894487213846666</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.930944673084282</v>
+        <v>2.875680184864778</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.584804573565458</v>
       </c>
       <c r="D1967" t="n">
-        <v>-2.989347420562629</v>
+        <v>-3.148964156401366</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.38870918102666</v>
+        <v>1.324862486691165</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5815562017505069</v>
+        <v>0.4894487213846666</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.933738294615763</v>
+        <v>2.878473806396259</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.585466921957117</v>
       </c>
       <c r="D1968" t="n">
-        <v>-2.983194714509844</v>
+        <v>-3.142811450348582</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.391832611839432</v>
+        <v>1.327985917503937</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5877089078032912</v>
+        <v>0.4956014274374508</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.938092266639092</v>
+        <v>2.882827778419587</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.584547398697227</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.000004012660346</v>
+        <v>-3.159620748499083</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.384189369319341</v>
+        <v>1.320342674983846</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5708996096527896</v>
+        <v>0.4787921292869492</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.927087164488901</v>
+        <v>2.871822676269397</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.650882952494048</v>
       </c>
       <c r="D1970" t="n">
-        <v>-2.937706013884224</v>
+        <v>-3.097322749722961</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.475444122626611</v>
+        <v>1.411597428291116</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5708996096527896</v>
+        <v>0.4787921292869492</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.993422718285722</v>
+        <v>2.938158230066218</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.453174954208175</v>
       </c>
       <c r="D1971" t="n">
-        <v>-2.735915816219066</v>
+        <v>-2.895532552057803</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.358452203406801</v>
+        <v>1.294605509071306</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.768917801821944</v>
+        <v>0.6768103214561036</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.914525635301342</v>
+        <v>2.859261147081837</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.52346518653035</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.571102813140219</v>
+        <v>-2.730719548978956</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.494667636960515</v>
+        <v>1.43082094262502</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.933730804900791</v>
+        <v>0.8416233245349506</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.083703669470825</v>
+        <v>3.028439181251321</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.538092922646394</v>
       </c>
       <c r="D1973" t="n">
-        <v>-2.668843357765193</v>
+        <v>-2.828460093603931</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.470199155226569</v>
+        <v>1.406352460891074</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.9178415267678108</v>
+        <v>0.8257340464019705</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.08879783870708</v>
+        <v>3.033533350487576</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.536628903471065</v>
       </c>
       <c r="D1974" t="n">
-        <v>-2.845181117888123</v>
+        <v>-3.00479785372686</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.398200032002069</v>
+        <v>1.334353337666574</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7415037666448814</v>
+        <v>0.649396286279041</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.981531163457995</v>
+        <v>2.92626667523849</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.535120521510994</v>
       </c>
       <c r="D1975" t="n">
-        <v>-2.768759071456196</v>
+        <v>-2.928375807294933</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.427260468614769</v>
+        <v>1.363413774279274</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7415037666448814</v>
+        <v>0.649396286279041</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.980022781497923</v>
+        <v>2.924758293278419</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
         <v>2.53498338894643</v>
       </c>
       <c r="D1976" t="n">
-        <v>-2.724385939817627</v>
+        <v>-2.884002675656364</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.444872588705632</v>
+        <v>1.381025894370137</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.78587689828345</v>
+        <v>0.6937694179176096</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.0065095279165</v>
+        <v>2.951245039696996</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
         <v>2.529377183085021</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.60155171893046</v>
+        <v>-2.761168454769197</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.488400071199089</v>
+        <v>1.424553376863595</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.78587689828345</v>
+        <v>0.6937694179176096</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.000903322055091</v>
+        <v>2.945638833835587</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
         <v>2.535758940112825</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.553895988369404</v>
+        <v>-2.713512724208141</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.513844120451316</v>
+        <v>1.449997426115822</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8335326288445056</v>
+        <v>0.7414251484786653</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.035878517419529</v>
+        <v>2.980614029200025</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
         <v>2.54065131348755</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.453377829870649</v>
+        <v>-2.612994565709386</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.558943757225543</v>
+        <v>1.495097062890048</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9340507873432602</v>
+        <v>0.8419433069774198</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.101081785893506</v>
+        <v>3.045817297674002</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.82880887755729</v>
       </c>
       <c r="C1980" t="n">
         <v>2.527405985963422</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.514044420273038</v>
+        <v>-2.673661156111776</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.52143179354046</v>
+        <v>1.457585099204965</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8523524706247265</v>
+        <v>0.7602449902588861</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.038817468338259</v>
+        <v>2.983552980118754</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.531503688574051</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.46920601866464</v>
+        <v>-2.628822754503378</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.543464856794448</v>
+        <v>1.479618162458953</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.856895903569596</v>
+        <v>0.7647884232037556</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.045641230715809</v>
+        <v>2.990376742496305</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.81793235491705</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.535664628205129</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.569964654421639</v>
+        <v>-2.729581390260376</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.507322342122726</v>
+        <v>1.443475647787231</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7680703348425906</v>
+        <v>0.6759628544767502</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.996506829110683</v>
+        <v>2.941242340891179</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405957</v>
       </c>
       <c r="C1983" t="n">
         <v>2.541544230732966</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.525761817335738</v>
+        <v>-2.685378553174476</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.530883079484924</v>
+        <v>1.467036385149429</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.812273171928491</v>
+        <v>0.7201656915626506</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.028908133890061</v>
+        <v>2.973643645670557</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.539954231202214</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.562740844999182</v>
+        <v>-2.722357580837919</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.514501468888794</v>
+        <v>1.450654774553299</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8492470737198216</v>
+        <v>0.7571395933539812</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.049502475434107</v>
+        <v>2.994237987214603</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.591201996385253</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.404449427459909</v>
+        <v>-2.564066163298647</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.629065801087542</v>
+        <v>1.565219106752047</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8492470737198216</v>
+        <v>0.7571395933539812</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.100750240617146</v>
+        <v>3.045485752397642</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
         <v>2.589642700979506</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.196807423825433</v>
+        <v>-2.35642415966417</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.710563307135586</v>
+        <v>1.646716612800091</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.056889077354298</v>
+        <v>0.9647815969884573</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.223776147392085</v>
+        <v>3.168511659172581</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
         <v>2.584590929217776</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.145775331102905</v>
+        <v>-2.305392066941642</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.725924372462867</v>
+        <v>1.662077678127372</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.107921170076826</v>
+        <v>1.015813689710985</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.249343631263872</v>
+        <v>3.194079143044368</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.84254736040485</v>
       </c>
       <c r="C1988" t="n">
         <v>2.601778333310481</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.080551149975699</v>
+        <v>-2.240167885814436</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.769201449006454</v>
+        <v>1.70535475467096</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.173145351204031</v>
+        <v>1.081037870838191</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.3056655440329</v>
+        <v>3.250401055813396</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
         <v>2.597739305609762</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.043124129904565</v>
+        <v>-2.202740865743303</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.780133229334188</v>
+        <v>1.716286534998694</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.178396889233213</v>
+        <v>1.086289408867373</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.30477743914969</v>
+        <v>3.249512950930185</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
         <v>2.598996097941002</v>
       </c>
       <c r="D1990" t="n">
-        <v>-1.907308337973882</v>
+        <v>-2.222852521778011</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.835716338437702</v>
+        <v>1.70949866491605</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.265573241509134</v>
+        <v>1.097316753864792</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.358340042846482</v>
+        <v>3.257386150259877</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
         <v>2.759553868962213</v>
       </c>
       <c r="D1991" t="n">
-        <v>-1.853563523546677</v>
+        <v>-2.169107707350806</v>
       </c>
       <c r="E1991" t="n">
-        <v>2.017772035229795</v>
+        <v>1.891554361708143</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.275636550949596</v>
+        <v>1.107380063305254</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.524935799531971</v>
+        <v>3.423981906945365</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>2.87966677818003</v>
       </c>
       <c r="D1992" t="n">
-        <v>-1.829771954940535</v>
+        <v>-2.145316138744664</v>
       </c>
       <c r="E1992" t="n">
-        <v>2.147401571890069</v>
+        <v>2.021183898368417</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.299428119555738</v>
+        <v>1.131171631911396</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.659323649913473</v>
+        <v>3.558369757326868</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
         <v>2.871374754193889</v>
       </c>
       <c r="D1993" t="n">
-        <v>-1.803687870676727</v>
+        <v>-2.119232054480856</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.149543181609451</v>
+        <v>2.023325508087799</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.299428119555738</v>
+        <v>1.131171631911396</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.651031625927332</v>
+        <v>3.550077733340727</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896925</v>
       </c>
       <c r="C1994" t="n">
         <v>2.869567949777668</v>
       </c>
       <c r="D1994" t="n">
-        <v>-1.72555668982778</v>
+        <v>-2.041100873631909</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.178988849532809</v>
+        <v>2.052771176011158</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.373604930439423</v>
+        <v>1.205348442795081</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.693730908041323</v>
+        <v>3.592777015454717</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959854</v>
       </c>
       <c r="C1995" t="n">
         <v>2.88712235550446</v>
       </c>
       <c r="D1995" t="n">
-        <v>-1.716664228434497</v>
+        <v>-2.032208412238626</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.200100239816914</v>
+        <v>2.073882566295262</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.373604930439423</v>
+        <v>1.205348442795081</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.711285313768114</v>
+        <v>3.610331421181509</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>2.878977402909044</v>
       </c>
       <c r="D1996" t="n">
-        <v>-1.885140345404375</v>
+        <v>-2.200684529208504</v>
       </c>
       <c r="E1996" t="n">
-        <v>2.124564840433547</v>
+        <v>1.998347166911895</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.345657094722842</v>
+        <v>1.1774006070785</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.686371659742749</v>
+        <v>3.585417767156144</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782705</v>
       </c>
       <c r="C1997" t="n">
         <v>2.860247100096906</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.187340816542791</v>
+        <v>-1.502885000346921</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.384954349166042</v>
+        <v>2.25873667564439</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.275309035352431</v>
+        <v>1.107052547708089</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.625432521308364</v>
+        <v>3.524478628721759</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632636</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>2.85091112259381</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.164619712859639</v>
+        <v>-1.480163896663768</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.384706813136207</v>
+        <v>2.258489139614555</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.275309035352431</v>
+        <v>1.107052547708089</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.616096543805269</v>
+        <v>3.515142651218664</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
         <v>3.009817248444979</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.162894669569595</v>
+        <v>-1.478438853373724</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.544302956303394</v>
+        <v>2.418085282781742</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.277034078642475</v>
+        <v>1.108777590998133</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.776037695630464</v>
+        <v>3.675083803043859</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644413</v>
+        <v>3.779933725644409</v>
       </c>
       <c r="C2000" t="n">
         <v>3.046895070938626</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.317675676347851</v>
+        <v>-1.63321986015198</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.519468376085738</v>
+        <v>2.393250702564087</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.243666404587999</v>
+        <v>1.075409916943657</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.793094913691425</v>
+        <v>3.69214102110482</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799964</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>3.043570426928171</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.266240342963191</v>
+        <v>-1.58178452676732</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.536717865429147</v>
+        <v>2.410500191907496</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.295101737972658</v>
+        <v>1.126845250328317</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.820631469711766</v>
+        <v>3.719677577125161</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>3.053576580572912</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.239289118636703</v>
+        <v>-1.554833302440832</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.557504508804484</v>
+        <v>2.431286835282832</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.309982084000378</v>
+        <v>1.141725596356036</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.839565830973139</v>
+        <v>3.738611938386534</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.237679712717872</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.375242126693019</v>
+        <v>-1.690786310497148</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.687226437726917</v>
+        <v>2.561008764205265</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.309982084000378</v>
+        <v>1.141725596356036</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.023668963118099</v>
+        <v>3.922715070531494</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714426</v>
+        <v>3.743925505714422</v>
       </c>
       <c r="C2004" t="n">
         <v>3.229796407620865</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.397650244497891</v>
+        <v>-1.71319442830202</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.670379885507962</v>
+        <v>2.54416221198631</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.309982084000378</v>
+        <v>1.141725596356036</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.015785658021092</v>
+        <v>3.914831765434487</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155034</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
         <v>3.231850407170503</v>
       </c>
       <c r="D2005" t="n">
-        <v>-1.54565601197729</v>
+        <v>-1.86120019578142</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.613231578065839</v>
+        <v>2.487013904544188</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.223255075136836</v>
+        <v>1.054998587492494</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.965803452252604</v>
+        <v>3.864849559666</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161979</v>
+        <v>3.729452285161975</v>
       </c>
       <c r="C2006" t="n">
         <v>3.28810412489235</v>
       </c>
       <c r="D2006" t="n">
-        <v>-1.55509693786582</v>
+        <v>-1.870641121669949</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.665708925432275</v>
+        <v>2.539491251910623</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.345682192680227</v>
+        <v>1.177425705035886</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.095513440500486</v>
+        <v>3.994559547913882</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321636</v>
+        <v>3.714941193321632</v>
       </c>
       <c r="C2007" t="n">
         <v>3.290995219437651</v>
       </c>
       <c r="D2007" t="n">
-        <v>-1.553810174326264</v>
+        <v>-1.869354358130393</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.669114725393398</v>
+        <v>2.542897051871746</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.346968956219784</v>
+        <v>1.178712468575442</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.099176593169521</v>
+        <v>3.998222700582916</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347704</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.289107032331426</v>
       </c>
       <c r="D2008" t="n">
-        <v>-1.555367228315555</v>
+        <v>-1.870911412119684</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.666603716691457</v>
+        <v>2.540386043169805</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.346968956219784</v>
+        <v>1.178712468575442</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.097288406063297</v>
+        <v>3.996334513476691</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887748</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.283927261934288</v>
       </c>
       <c r="D2009" t="n">
-        <v>-1.56263911383902</v>
+        <v>-1.878183297643149</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.658515192084933</v>
+        <v>2.532297518563281</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.339697070696319</v>
+        <v>1.171440583051977</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.08774550435208</v>
+        <v>3.986791611765475</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343066</v>
+        <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
         <v>3.282361272144441</v>
       </c>
       <c r="D2010" t="n">
-        <v>-1.560798094780768</v>
+        <v>-1.876342278584898</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.657685609918386</v>
+        <v>2.531467936396735</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.340965297367787</v>
+        <v>1.172708809723446</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.086940450565113</v>
+        <v>3.985986557978508</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647107</v>
+        <v>3.754911907647103</v>
       </c>
       <c r="C2011" t="n">
         <v>3.295434679010359</v>
       </c>
       <c r="D2011" t="n">
-        <v>-1.567706800280449</v>
+        <v>-1.883250984084578</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.667995534584433</v>
+        <v>2.541777861062781</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.340965297367787</v>
+        <v>1.172708809723446</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.100013857431032</v>
+        <v>3.999059964844427</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763533</v>
+        <v>3.74989685176353</v>
       </c>
       <c r="C2012" t="n">
         <v>3.295434679010359</v>
       </c>
       <c r="D2012" t="n">
-        <v>-1.569268443095309</v>
+        <v>-1.884812626899438</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.667370877458489</v>
+        <v>2.541153203936837</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.340965297367787</v>
+        <v>1.172708809723446</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.100013857431032</v>
+        <v>3.999059964844427</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392117</v>
+        <v>3.715834055392113</v>
       </c>
       <c r="C2013" t="n">
         <v>3.293958720137361</v>
       </c>
       <c r="D2013" t="n">
-        <v>-1.597169230204782</v>
+        <v>-1.912713414008911</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.654734603741701</v>
+        <v>2.52851693022005</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.306368373224853</v>
+        <v>1.138111885580511</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.077779744072274</v>
+        <v>3.976825851485668</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172528</v>
+        <v>3.684909939172524</v>
       </c>
       <c r="C2014" t="n">
         <v>3.29072316411456</v>
       </c>
       <c r="D2014" t="n">
-        <v>-1.600202227717455</v>
+        <v>-1.915746411521585</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.650285848713831</v>
+        <v>2.524068175192179</v>
       </c>
       <c r="F2014" t="n">
-        <v>1.303335375712179</v>
+        <v>1.135078888067837</v>
       </c>
       <c r="G2014" t="n">
-        <v>4.072724389541867</v>
+        <v>3.971770496955262</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971081</v>
+        <v>3.619362241971077</v>
       </c>
       <c r="C2015" t="n">
         <v>3.357429123705064</v>
       </c>
       <c r="D2015" t="n">
-        <v>-1.620263548993963</v>
+        <v>-1.935807732798092</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.708967279793732</v>
+        <v>2.58274960627208</v>
       </c>
       <c r="F2015" t="n">
-        <v>1.283274054435672</v>
+        <v>1.11501756679133</v>
       </c>
       <c r="G2015" t="n">
-        <v>4.127393556366467</v>
+        <v>4.026439663779862</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199807</v>
+        <v>3.640764248199804</v>
       </c>
       <c r="C2016" t="n">
         <v>3.497740842706911</v>
       </c>
       <c r="D2016" t="n">
-        <v>-1.876984366988786</v>
+        <v>-2.192528550792916</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.746590671597649</v>
+        <v>2.620372998075998</v>
       </c>
       <c r="F2016" t="n">
-        <v>1.174859480291857</v>
+        <v>1.006602992647515</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.202656530882026</v>
+        <v>4.10170263829542</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622238</v>
+        <v>3.668303164622235</v>
       </c>
       <c r="C2017" t="n">
         <v>3.566721111852551</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.030970784764927</v>
+        <v>-2.346514968569056</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.753976373632833</v>
+        <v>2.627758700111181</v>
       </c>
       <c r="F2017" t="n">
-        <v>1.174859480291857</v>
+        <v>1.006602992647515</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.271636800027665</v>
+        <v>4.17068290744106</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808531</v>
+        <v>3.619937176808527</v>
       </c>
       <c r="C2018" t="n">
         <v>3.552772313972671</v>
       </c>
       <c r="D2018" t="n">
-        <v>-1.980448880937261</v>
+        <v>-2.29599306474139</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.76023633728402</v>
+        <v>2.634018663762368</v>
       </c>
       <c r="F2018" t="n">
-        <v>1.174859480291857</v>
+        <v>1.006602992647515</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.257688002147786</v>
+        <v>4.156734109561181</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994896</v>
+        <v>3.656346893994892</v>
       </c>
       <c r="C2019" t="n">
         <v>3.564642803028085</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.232924034944985</v>
+        <v>-2.548468218749115</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.671116764736344</v>
+        <v>2.544899091214693</v>
       </c>
       <c r="F2019" t="n">
-        <v>1.174859480291857</v>
+        <v>1.006602992647515</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.2695584912032</v>
+        <v>4.168604598616595</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358299</v>
+        <v>3.674042696358296</v>
       </c>
       <c r="C2020" t="n">
         <v>3.565853337547029</v>
       </c>
       <c r="D2020" t="n">
-        <v>-2.502396836866693</v>
+        <v>-2.817941020670823</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.564538178486605</v>
+        <v>2.438320504964953</v>
       </c>
       <c r="F2020" t="n">
-        <v>1.174859480291857</v>
+        <v>1.006602992647515</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.270769025722144</v>
+        <v>4.169815133135539</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637088</v>
+        <v>3.663523617637084</v>
       </c>
       <c r="C2021" t="n">
         <v>3.569975079774351</v>
       </c>
       <c r="D2021" t="n">
-        <v>-2.659940908596135</v>
+        <v>-2.975485092400264</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.505642292022149</v>
+        <v>2.379424618500498</v>
       </c>
       <c r="F2021" t="n">
-        <v>1.107957675151582</v>
+        <v>0.9397011875072407</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.2347496848653</v>
+        <v>4.133795792278695</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301344</v>
+        <v>3.65216331330134</v>
       </c>
       <c r="C2022" t="n">
         <v>3.56505293251054</v>
       </c>
       <c r="D2022" t="n">
-        <v>-2.788791459298181</v>
+        <v>-3.10433564310231</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.44917992447752</v>
+        <v>2.322962250955869</v>
       </c>
       <c r="F2022" t="n">
-        <v>1.066964266300861</v>
+        <v>0.8987077786565192</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.205231492291057</v>
+        <v>4.104277599704452</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.918601928327767</v>
+        <v>3.529228204705057</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.92473845743903</v>
+        <v>3.810319733515959</v>
       </c>
       <c r="D2023" t="n">
-        <v>-2.788791459298181</v>
+        <v>-3.094579842105174</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.44917992447752</v>
+        <v>2.572131372360142</v>
       </c>
       <c r="F2023" t="n">
-        <v>1.066964266300861</v>
+        <v>0.8987077786565192</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.917802254425398</v>
+        <v>4.34954440070987</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240712.xlsx
+++ b/tame_output/ON/bt/strategyON_20240712.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>45.0%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-70.6%</t>
+          <t>-71.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.8%</t>
+          <t>109.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.0%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-65.8%</t>
+          <t>-66.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.1%</t>
+          <t>453.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-471.0%</t>
+          <t>-490.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-36.7%</t>
+          <t>-35.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-119.0%</t>
+          <t>-151.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>112.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-130.0%</t>
+          <t>-120.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-134.1%</t>
+          <t>-155.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>87.6%</t>
+          <t>76.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>81.3%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-11.1%</t>
+          <t>-48.2%</t>
         </is>
       </c>
     </row>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.337703673577133</v>
+        <v>-7.554990769168801</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2160220803586541</v>
+        <v>0.1291072421219868</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.327594917090197</v>
+        <v>-1.544882012681864</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.354903023849137</v>
+        <v>2.224530766494136</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.174303802637771</v>
+        <v>-7.391590898229438</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.280748849955156</v>
+        <v>0.1938340117184887</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.164195046150834</v>
+        <v>-1.381482141742502</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.452309767633511</v>
+        <v>2.321937510278511</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.940822580408172</v>
+        <v>-7.15810967599984</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3820657676848476</v>
+        <v>0.2951509294481807</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.9307138239212358</v>
+        <v>-1.148000919512903</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.600322929809122</v>
+        <v>2.469950672454122</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.791156189400657</v>
+        <v>-7.008443284992325</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4390401137748947</v>
+        <v>0.3521252755382274</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.8378103326786999</v>
+        <v>-1.055097428270367</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.653172814241685</v>
+        <v>2.522800556886684</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.65888071576977</v>
+        <v>-6.876167811361438</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4873177899742762</v>
+        <v>0.4004029517376089</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.7055348590478132</v>
+        <v>-0.9228219546394807</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.727905585167244</v>
+        <v>2.597533327812243</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.503142383210029</v>
+        <v>-6.720429478801696</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5524281836858096</v>
+        <v>0.4655133454491427</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.5497965264880716</v>
+        <v>-0.7670836220797391</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.824163645390726</v>
+        <v>2.693791388035725</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.254142584526448</v>
+        <v>-6.471429680118115</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6649344443829008</v>
+        <v>0.5780196061462335</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.5497965264880716</v>
+        <v>-0.7670836220797391</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.837069986614384</v>
+        <v>2.706697729259384</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.359732574299552</v>
+        <v>-6.57701966989122</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4947225188744402</v>
+        <v>0.4078076806377733</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.6553865162611761</v>
+        <v>-0.8726736118528435</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.645740063151303</v>
+        <v>2.515367805796302</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.378467476418149</v>
+        <v>-6.595754572009817</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5357728999040878</v>
+        <v>0.4488580616674209</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.6609825259213074</v>
+        <v>-0.8782696215129748</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.690926799232311</v>
+        <v>2.56055454187731</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.23052743501055</v>
+        <v>-6.447814530602217</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.47506999377896</v>
+        <v>0.3881551555422931</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.6406616100127498</v>
+        <v>-0.8579487056044173</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.583240426089278</v>
+        <v>2.452868168734277</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.177557912756561</v>
+        <v>-6.394845008348229</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4875438164270771</v>
+        <v>0.4006289781904102</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5876920877587609</v>
+        <v>-0.8049791833504284</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.606308153188193</v>
+        <v>2.475935895833192</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.134009505985871</v>
+        <v>-6.351296601577539</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4980025670402601</v>
+        <v>0.4110877288035932</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5876920877587609</v>
+        <v>-0.8049791833504284</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.5993475410931</v>
+        <v>2.468975283738099</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-5.891861112532013</v>
+        <v>-6.10914820812368</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.6093242788029465</v>
+        <v>0.5224094405662796</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5876920877587609</v>
+        <v>-0.8049791833504284</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.613809895474243</v>
+        <v>2.483437638119242</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.783601975409491</v>
+        <v>-6.000889071001159</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.6471600541111502</v>
+        <v>0.5602452158744833</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5876920877587609</v>
+        <v>-0.8049791833504284</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.608342015933438</v>
+        <v>2.477969758578437</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.66031084059236</v>
+        <v>-5.877597936184028</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6939746020485797</v>
+        <v>0.6070597638119124</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.4644009529416304</v>
+        <v>-0.6816880485332979</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.679814790834293</v>
+        <v>2.549442533479292</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919906</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.639161641688917</v>
+        <v>-5.856448737280584</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.7101352598472821</v>
+        <v>0.6232204216106152</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.4432517540381871</v>
+        <v>-0.6605388496298545</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.700205288413684</v>
+        <v>2.569833031058684</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.395396199705472</v>
+        <v>-5.61268329529714</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.8034221449877106</v>
+        <v>0.7165073067510432</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.4432517540381871</v>
+        <v>-0.6605388496298545</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.695985996760735</v>
+        <v>2.565613739405734</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.293633379428178</v>
+        <v>-5.510920475019845</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.8462515870186444</v>
+        <v>0.7593367487819775</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.4300326856457584</v>
+        <v>-0.6473197812374258</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.706041751716208</v>
+        <v>2.575669494361208</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279183</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.043782985479103</v>
+        <v>-5.261070081070771</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.9389338195819765</v>
+        <v>0.8520189813453092</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.4300326856457584</v>
+        <v>-0.6473197812374258</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.69878382669991</v>
+        <v>2.56841156934491</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.867890893011671</v>
+        <v>-5.085177988603338</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.012889780089598</v>
+        <v>0.9259749418529313</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.4300326856457584</v>
+        <v>-0.6473197812374258</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.702382950220559</v>
+        <v>2.572010692865558</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.696444429989207</v>
+        <v>-4.913731525580874</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.094795871353137</v>
+        <v>1.00788103311647</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.2585862226232952</v>
+        <v>-0.4758733182149627</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.818578334088591</v>
+        <v>2.68820607673359</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.622154864250868</v>
+        <v>-4.839441959842535</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.12353217526477</v>
+        <v>1.036617337028103</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.1842966568849559</v>
+        <v>-0.4015837524766234</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.862172551147891</v>
+        <v>2.731800293792891</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.558519122016934</v>
+        <v>-4.775806217608601</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.153681273212661</v>
+        <v>1.066766434975994</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.1206609146510214</v>
+        <v>-0.3379480102426889</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.905048797542569</v>
+        <v>2.774676540187568</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074779</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.447092362691014</v>
+        <v>-4.664379458282681</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.179446235726824</v>
+        <v>1.092531397490158</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.1206609146510214</v>
+        <v>-0.3379480102426889</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.886243056326365</v>
+        <v>2.755870798971364</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769488424229</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.206661865886153</v>
+        <v>-4.42394896147782</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.277361511073646</v>
+        <v>1.190446672836979</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.1197695821538389</v>
+        <v>-0.09751751343782861</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.032244431034158</v>
+        <v>2.901872173679158</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.134419297714959</v>
+        <v>-4.351706393306626</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.310187852176944</v>
+        <v>1.223273013940277</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.1197695821538389</v>
+        <v>-0.09751751343782861</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.036173744868978</v>
+        <v>2.905801487513978</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.081420975433571</v>
+        <v>-4.298708071025238</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.332065765006839</v>
+        <v>1.245150926770172</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.1751058411557777</v>
+        <v>-0.04218125443588977</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.070054084187482</v>
+        <v>2.939681826832481</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502334</v>
+        <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-3.972616089953844</v>
+        <v>-4.189903185545511</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.372585790418723</v>
+        <v>1.285670952182057</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.1751058411557777</v>
+        <v>-0.04218125443588977</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.067052155407475</v>
+        <v>2.936679898052475</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675936</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.758096420540424</v>
+        <v>-3.955497653705708</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.459972695194706</v>
+        <v>1.381012201928592</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.258168537485034</v>
+        <v>0.04498710901710673</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.118468810215643</v>
+        <v>2.990559953134887</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539948</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.625228731477146</v>
+        <v>-3.82262996464243</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.52901395362184</v>
+        <v>1.450053460355727</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.258168537485034</v>
+        <v>0.04498710901710673</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.134362993017466</v>
+        <v>3.00645413593671</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496258</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.505055648112647</v>
+        <v>-3.70245688127793</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.578229031407942</v>
+        <v>1.499268538141828</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.378341620849533</v>
+        <v>0.1651601923816057</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.207612687476467</v>
+        <v>3.079703830395711</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576995</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.360383503012909</v>
+        <v>-3.557784736178193</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.646185992009277</v>
+        <v>1.567225498743163</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5230137659492704</v>
+        <v>0.3098323374813431</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.30450407709775</v>
+        <v>3.176595220016994</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.7358392229421</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.420258330370602</v>
+        <v>-3.617659563535885</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.608273552467625</v>
+        <v>1.529313059201512</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.4631389385915783</v>
+        <v>0.249957510123651</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.25461667208456</v>
+        <v>3.126707815003804</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.300438099459764</v>
+        <v>-3.497839332625048</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.671490814066169</v>
+        <v>1.592530320800055</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.4631389385915783</v>
+        <v>0.249957510123651</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.269905841318769</v>
+        <v>3.141996984238013</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914639843069</v>
+        <v>3.729146398430692</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.30290780592157</v>
+        <v>-3.500309039086854</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.578147130803888</v>
+        <v>1.499186637537774</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.4606692321297721</v>
+        <v>0.2474878036618448</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.176068216764127</v>
+        <v>3.048159359683371</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.37127799224558</v>
+        <v>-3.568679225410864</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.470060917759586</v>
+        <v>1.391100424493472</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.4699449311659871</v>
+        <v>0.2567635026980598</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.100895497671157</v>
+        <v>2.972986640590401</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.385066045092627</v>
+        <v>-3.58246727825791</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.454982405252658</v>
+        <v>1.376021911986545</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.4699449311659871</v>
+        <v>0.2567635026980598</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.091332206303048</v>
+        <v>2.963423349222292</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.416059204421332</v>
+        <v>-3.613460437586616</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.267294706561563</v>
+        <v>1.188334213295449</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.4699449311659871</v>
+        <v>0.2567635026980598</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.916041771343435</v>
+        <v>2.788132914262679</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.240584944628863</v>
+        <v>-3.437986177794147</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.342051642470338</v>
+        <v>1.263091149204225</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.4699449311659871</v>
+        <v>0.2567635026980598</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.920609003335223</v>
+        <v>2.792700146254467</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.351521197270111</v>
+        <v>-3.548922430435395</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.273419170175046</v>
+        <v>1.194458676908932</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.4699449311659871</v>
+        <v>0.2567635026980598</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.89635103209643</v>
+        <v>2.768442175015674</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.617515458616743</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.31785765179783</v>
+        <v>-3.515258884963113</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.290015973583864</v>
+        <v>1.211055480317751</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5036084766382689</v>
+        <v>0.2904270481703416</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.919680544599705</v>
+        <v>2.791771687518949</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.627687845048876</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.258005032594106</v>
+        <v>-3.45540626575939</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.324129407697486</v>
+        <v>1.245168914431372</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5036084766382689</v>
+        <v>0.2904270481703416</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.929852931031837</v>
+        <v>2.801944073951081</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.622634115622736</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.171761569567729</v>
+        <v>-3.369162802733013</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.353573063481897</v>
+        <v>1.274612570215784</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5036084766382689</v>
+        <v>0.2904270481703416</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.924799201605698</v>
+        <v>2.796890344524941</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.614409891067262</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.217068388966709</v>
+        <v>-3.414469622131993</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.327226111166831</v>
+        <v>1.248265617900717</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.4627983136290381</v>
+        <v>0.2496168851611108</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.892088879244685</v>
+        <v>2.764180022163928</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.614961764100363</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.24610149366901</v>
+        <v>-3.443502726834294</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.316164742319012</v>
+        <v>1.237204249052898</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.4627983136290381</v>
+        <v>0.2496168851611108</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.892640752277786</v>
+        <v>2.76473189519703</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.544234455991729</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.153291012218151</v>
+        <v>-3.350692245383435</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.282561626790721</v>
+        <v>1.203601133524608</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.5556087950798975</v>
+        <v>0.3424273666119702</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.877599733039667</v>
+        <v>2.749690875958911</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.54610793191633</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.197680481547579</v>
+        <v>-3.395081714712862</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.266679314983551</v>
+        <v>1.187718821717437</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5112193257504698</v>
+        <v>0.2980378972825425</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.852839527366612</v>
+        <v>2.724930670285855</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.541183640428053</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.085009263311329</v>
+        <v>-3.282410496476612</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.306823510789774</v>
+        <v>1.22786301752366</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6238905439867199</v>
+        <v>0.4107091155187927</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.915517966820085</v>
+        <v>2.787609109739329</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.54667493625872</v>
       </c>
       <c r="D1949" t="n">
-        <v>-2.972632262128656</v>
+        <v>-3.17003349529394</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.35726560709351</v>
+        <v>1.278305113827397</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6238905439867199</v>
+        <v>0.4107091155187927</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.921009262650752</v>
+        <v>2.793100405569996</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.558172138027259</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.000412660030009</v>
+        <v>-3.197813893195293</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.357650649701508</v>
+        <v>1.278690156435395</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.5961101460853668</v>
+        <v>0.3829287176174396</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.915838225678479</v>
+        <v>2.787929368597723</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
         <v>2.396527858027912</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.083413941055288</v>
+        <v>-3.280815174220572</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.16280585729205</v>
+        <v>1.083845364025936</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5775392615581931</v>
+        <v>0.3643578330902659</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.743051414962828</v>
+        <v>2.615142557882072</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.516677518747118</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.192028019498619</v>
+        <v>-3.389429252663903</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.239509886633923</v>
+        <v>1.160549393367809</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5775392615581931</v>
+        <v>0.3643578330902659</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.863201075682034</v>
+        <v>2.735292218601277</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.156618981250476</v>
+        <v>-3.35402021441576</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.268186528035503</v>
+        <v>1.189226034769389</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5775392615581931</v>
+        <v>0.3643578330902659</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.877714101784357</v>
+        <v>2.7498052447036</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
         <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.118235318692325</v>
+        <v>-3.315636551857609</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.280959434401132</v>
+        <v>1.201998941135018</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6159229241163443</v>
+        <v>0.402741495648417</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.898163740661616</v>
+        <v>2.77025488358086</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-2.941118988657159</v>
+        <v>-3.138520221822443</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.348534995260501</v>
+        <v>1.269574501994387</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6159229241163443</v>
+        <v>0.402741495648417</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.894892769506919</v>
+        <v>2.766983912426162</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-2.986211233490705</v>
+        <v>-3.183612466655989</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.331181489088996</v>
+        <v>1.252220995822882</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5540268809469545</v>
+        <v>0.3408454524790273</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.858438535367198</v>
+        <v>2.730529678286441</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-2.806835812251937</v>
+        <v>-3.004237045417221</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.396718632890917</v>
+        <v>1.317758139624804</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7108036391176732</v>
+        <v>0.4976222106497459</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.946291565576043</v>
+        <v>2.818382708495287</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-2.851850025772543</v>
+        <v>-3.049251258937827</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.359520402814264</v>
+        <v>1.280559909548151</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6804547438030686</v>
+        <v>0.4672733153351413</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.90888968371887</v>
+        <v>2.780980826638114</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509535</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.118854536044979</v>
+        <v>-3.316255769210263</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.258410161044236</v>
+        <v>1.179449667778123</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.48609170576012</v>
+        <v>0.2729102772921927</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.797963423232047</v>
+        <v>2.670054566151291</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.220052317482152</v>
+        <v>-3.417453550647435</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.217134970365868</v>
+        <v>1.138174477099755</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4176828922148008</v>
+        <v>0.2045014637468735</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.756122057001357</v>
+        <v>2.628213199920601</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.213541350867839</v>
+        <v>-3.410942584033123</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.21733931856591</v>
+        <v>1.138378825299797</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4176828922148008</v>
+        <v>0.2045014637468735</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.753722018555674</v>
+        <v>2.625813161474917</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.194503223160542</v>
+        <v>-3.391904456325825</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.221479288857074</v>
+        <v>1.14251879559096</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3594992808836063</v>
+        <v>0.146317852415679</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.715336570965202</v>
+        <v>2.587427713884446</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131249</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.22562985431116</v>
+        <v>-3.423031087476443</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.386610505335507</v>
+        <v>1.307650012069394</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3594992808836063</v>
+        <v>0.146317852415679</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.892918439903883</v>
+        <v>2.765009582823126</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.239496615645077</v>
+        <v>-3.436897848810361</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.381897129788074</v>
+        <v>1.30293663652196</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3216413641497833</v>
+        <v>0.108459935681856</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.871037018849722</v>
+        <v>2.743128161768966</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
         <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.194692444105147</v>
+        <v>-3.392093677270431</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.405827328800972</v>
+        <v>1.326866835534858</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3216413641497833</v>
+        <v>0.108459935681856</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.877045549246648</v>
+        <v>2.749136692165892</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.582010952033977</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.046949473870145</v>
+        <v>-3.244350707035429</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.362874738172172</v>
+        <v>1.283914244906059</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4894487213846666</v>
+        <v>0.2762672929167392</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.875680184864778</v>
+        <v>2.747771327784021</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.584804573565458</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.148964156401366</v>
+        <v>-3.34636538956665</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.324862486691165</v>
+        <v>1.245901993425051</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4894487213846666</v>
+        <v>0.2762672929167392</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.878473806396259</v>
+        <v>2.750564949315502</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
         <v>2.585466921957117</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.142811450348582</v>
+        <v>-3.340212683513865</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.327985917503937</v>
+        <v>1.249025424237823</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4956014274374508</v>
+        <v>0.2824199989695235</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.882827778419587</v>
+        <v>2.754918921338831</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.584547398697227</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.159620748499083</v>
+        <v>-3.357021981664367</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.320342674983846</v>
+        <v>1.241382181717733</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4787921292869492</v>
+        <v>0.2656107008190218</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.871822676269397</v>
+        <v>2.743913819188641</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>2.650882952494048</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.097322749722961</v>
+        <v>-3.294723982888245</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.411597428291116</v>
+        <v>1.332636935025003</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4787921292869492</v>
+        <v>0.2656107008190218</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.938158230066218</v>
+        <v>2.810249372985461</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
         <v>2.453174954208175</v>
       </c>
       <c r="D1971" t="n">
-        <v>-2.895532552057803</v>
+        <v>-3.092933785223087</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.294605509071306</v>
+        <v>1.215645015805193</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6768103214561036</v>
+        <v>0.4636288929881762</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.859261147081837</v>
+        <v>2.731352290001081</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
         <v>2.52346518653035</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.730719548978956</v>
+        <v>-2.92812078214424</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.43082094262502</v>
+        <v>1.351860449358907</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.8416233245349506</v>
+        <v>0.6284418960670232</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.028439181251321</v>
+        <v>2.900530324170564</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
         <v>2.538092922646394</v>
       </c>
       <c r="D1973" t="n">
-        <v>-2.828460093603931</v>
+        <v>-3.025861326769214</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.406352460891074</v>
+        <v>1.327391967624961</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8257340464019705</v>
+        <v>0.612552617934043</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.033533350487576</v>
+        <v>2.90562449340682</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
         <v>2.536628903471065</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.00479785372686</v>
+        <v>-3.202199086892143</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.334353337666574</v>
+        <v>1.255392844400461</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.649396286279041</v>
+        <v>0.4362148578111136</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.92626667523849</v>
+        <v>2.798357818157734</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.535120521510994</v>
       </c>
       <c r="D1975" t="n">
-        <v>-2.928375807294933</v>
+        <v>-3.125777040460217</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.363413774279274</v>
+        <v>1.28445328101316</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.649396286279041</v>
+        <v>0.4362148578111136</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.924758293278419</v>
+        <v>2.796849436197662</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316248</v>
       </c>
       <c r="C1976" t="n">
         <v>2.53498338894643</v>
       </c>
       <c r="D1976" t="n">
-        <v>-2.884002675656364</v>
+        <v>-3.081403908821648</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.381025894370137</v>
+        <v>1.302065401104024</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.6937694179176096</v>
+        <v>0.4805879894496822</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.951245039696996</v>
+        <v>2.82333618261624</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.529377183085021</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.761168454769197</v>
+        <v>-2.958569687934481</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.424553376863595</v>
+        <v>1.345592883597481</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.6937694179176096</v>
+        <v>0.4805879894496822</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.945638833835587</v>
+        <v>2.81772997675483</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190322</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
         <v>2.535758940112825</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.713512724208141</v>
+        <v>-2.910913957373425</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.449997426115822</v>
+        <v>1.371036932849708</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.7414251484786653</v>
+        <v>0.5282437200107379</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.980614029200025</v>
+        <v>2.852705172119268</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569615</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
         <v>2.54065131348755</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.612994565709386</v>
+        <v>-2.81039579887467</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.495097062890048</v>
+        <v>1.416136569623935</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8419433069774198</v>
+        <v>0.6287618785094925</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.045817297674002</v>
+        <v>2.917908440593246</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.82880887755729</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
         <v>2.527405985963422</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.673661156111776</v>
+        <v>-2.871062389277059</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.457585099204965</v>
+        <v>1.378624605938851</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7602449902588861</v>
+        <v>0.5470635617909588</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.983552980118754</v>
+        <v>2.855644123037998</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.531503688574051</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.628822754503378</v>
+        <v>-2.826223987668661</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.479618162458953</v>
+        <v>1.400657669192839</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.7647884232037556</v>
+        <v>0.5516069947358283</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.990376742496305</v>
+        <v>2.862467885415548</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.81793235491705</v>
       </c>
       <c r="C1982" t="n">
         <v>2.535664628205129</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.729581390260376</v>
+        <v>-2.92698262342566</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.443475647787231</v>
+        <v>1.364515154521118</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6759628544767502</v>
+        <v>0.4627814260088229</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.941242340891179</v>
+        <v>2.813333483810423</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405957</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.541544230732966</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.685378553174476</v>
+        <v>-2.882779786339759</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.467036385149429</v>
+        <v>1.388075891883315</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7201656915626506</v>
+        <v>0.5069842630947233</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.973643645670557</v>
+        <v>2.8457347885898</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.539954231202214</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.722357580837919</v>
+        <v>-2.919758814003202</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.450654774553299</v>
+        <v>1.371694281287186</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7571395933539812</v>
+        <v>0.5439581648860539</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.994237987214603</v>
+        <v>2.866329130133846</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.591201996385253</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.564066163298647</v>
+        <v>-2.76146739646393</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.565219106752047</v>
+        <v>1.486258613485934</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7571395933539812</v>
+        <v>0.5439581648860539</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.045485752397642</v>
+        <v>2.917576895316886</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321019</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.589642700979506</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.35642415966417</v>
+        <v>-2.553825392829454</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.646716612800091</v>
+        <v>1.567756119533978</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9647815969884573</v>
+        <v>0.75160016852053</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.168511659172581</v>
+        <v>3.040602802091825</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.584590929217776</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.305392066941642</v>
+        <v>-2.502793300106926</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.662077678127372</v>
+        <v>1.583117184861259</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.015813689710985</v>
+        <v>0.802632261243058</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.194079143044368</v>
+        <v>3.066170285963612</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84254736040485</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.601778333310481</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.240167885814436</v>
+        <v>-2.43756911897972</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.70535475467096</v>
+        <v>1.626394261404846</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.081037870838191</v>
+        <v>0.8678564423702636</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.250401055813396</v>
+        <v>3.12249219873264</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.597739305609762</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.202740865743303</v>
+        <v>-2.400142098908586</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.716286534998694</v>
+        <v>1.63732604173258</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.086289408867373</v>
+        <v>0.8731079803994453</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.249512950930185</v>
+        <v>3.121604093849429</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
         <v>2.598996097941002</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.222852521778011</v>
+        <v>-2.420253754943295</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.70949866491605</v>
+        <v>1.630538171649937</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.097316753864792</v>
+        <v>0.8841353253968645</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.257386150259877</v>
+        <v>3.129477293179121</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636284</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.759553868962213</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.169107707350806</v>
+        <v>-2.36650894051609</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.891554361708143</v>
+        <v>1.81259386844203</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.107380063305254</v>
+        <v>0.8941986348373264</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.423981906945365</v>
+        <v>3.296073049864609</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957623</v>
       </c>
       <c r="C1992" t="n">
         <v>2.87966677818003</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.145316138744664</v>
+        <v>-2.342717371909948</v>
       </c>
       <c r="E1992" t="n">
-        <v>2.021183898368417</v>
+        <v>1.942223405102304</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.131171631911396</v>
+        <v>0.9179902034434687</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.558369757326868</v>
+        <v>3.430460900246111</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998751</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
         <v>2.871374754193889</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.119232054480856</v>
+        <v>-2.31663328764614</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.023325508087799</v>
+        <v>1.944365014821686</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.131171631911396</v>
+        <v>0.9179902034434687</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.550077733340727</v>
+        <v>3.42216887625997</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896925</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.869567949777668</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.041100873631909</v>
+        <v>-2.238502106797193</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.052771176011158</v>
+        <v>1.973810682745044</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.205348442795081</v>
+        <v>0.9921670143271533</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.592777015454717</v>
+        <v>3.464868158373961</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959854</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
         <v>2.88712235550446</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.032208412238626</v>
+        <v>-2.22960964540391</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.073882566295262</v>
+        <v>1.994922073029149</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.205348442795081</v>
+        <v>0.9921670143271533</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.610331421181509</v>
+        <v>3.482422564100752</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>2.878977402909044</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.200684529208504</v>
+        <v>-2.398085762373788</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.998347166911895</v>
+        <v>1.919386673645782</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.1774006070785</v>
+        <v>0.9642191786105725</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.585417767156144</v>
+        <v>3.457508910075387</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782705</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.860247100096906</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.502885000346921</v>
+        <v>-1.700286233512204</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.25873667564439</v>
+        <v>2.179776182378276</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.107052547708089</v>
+        <v>0.8938711192401618</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.524478628721759</v>
+        <v>3.396569771641003</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632636</v>
       </c>
       <c r="C1998" t="n">
         <v>2.85091112259381</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.480163896663768</v>
+        <v>-1.677565129829052</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.258489139614555</v>
+        <v>2.179528646348442</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.107052547708089</v>
+        <v>0.8938711192401618</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.515142651218664</v>
+        <v>3.387233794137908</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>3.009817248444979</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.478438853373724</v>
+        <v>-1.675840086539008</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.418085282781742</v>
+        <v>2.339124789515629</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.108777590998133</v>
+        <v>0.8955961625302056</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.675083803043859</v>
+        <v>3.547174945963103</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644409</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
         <v>3.046895070938626</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.63321986015198</v>
+        <v>-1.830621093317264</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.393250702564087</v>
+        <v>2.314290209297973</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.075409916943657</v>
+        <v>0.8622284884757294</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.69214102110482</v>
+        <v>3.564232164024064</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>3.043570426928171</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.58178452676732</v>
+        <v>-1.779185759932604</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.410500191907496</v>
+        <v>2.331539698641382</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.126845250328317</v>
+        <v>0.9136638218603891</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.719677577125161</v>
+        <v>3.591768720044405</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>3.053576580572912</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.554833302440832</v>
+        <v>-1.752234535606116</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.431286835282832</v>
+        <v>2.352326342016719</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.141725596356036</v>
+        <v>0.9285441678881082</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.738611938386534</v>
+        <v>3.610703081305778</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784107</v>
       </c>
       <c r="C2003" t="n">
         <v>3.237679712717872</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.690786310497148</v>
+        <v>-1.888187543662432</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.561008764205265</v>
+        <v>2.482048270939152</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.141725596356036</v>
+        <v>0.9285441678881082</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.922715070531494</v>
+        <v>3.794806213450737</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714422</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.229796407620865</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.71319442830202</v>
+        <v>-1.910595661467304</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.54416221198631</v>
+        <v>2.465201718720197</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.141725596356036</v>
+        <v>0.9285441678881082</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.914831765434487</v>
+        <v>3.786922908353731</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>3.719118627155032</v>
       </c>
       <c r="C2005" t="n">
         <v>3.231850407170503</v>
       </c>
       <c r="D2005" t="n">
-        <v>-1.86120019578142</v>
+        <v>-2.058601428946703</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.487013904544188</v>
+        <v>2.408053411278074</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.054998587492494</v>
+        <v>0.8418171590245668</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.864849559666</v>
+        <v>3.736940702585243</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161975</v>
+        <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
         <v>3.28810412489235</v>
       </c>
       <c r="D2006" t="n">
-        <v>-1.870641121669949</v>
+        <v>-2.068042354835233</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.539491251910623</v>
+        <v>2.460530758644509</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.177425705035886</v>
+        <v>0.9642442765679582</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.994559547913882</v>
+        <v>3.866650690833125</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321632</v>
+        <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
         <v>3.290995219437651</v>
       </c>
       <c r="D2007" t="n">
-        <v>-1.869354358130393</v>
+        <v>-2.066755591295677</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.542897051871746</v>
+        <v>2.463936558605633</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.178712468575442</v>
+        <v>0.9655310401075148</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.998222700582916</v>
+        <v>3.87031384350216</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
         <v>3.289107032331426</v>
       </c>
       <c r="D2008" t="n">
-        <v>-1.870911412119684</v>
+        <v>-2.068312645284968</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.540386043169805</v>
+        <v>2.461425549903692</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.178712468575442</v>
+        <v>0.9655310401075148</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.996334513476691</v>
+        <v>3.868425656395935</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.283927261934288</v>
       </c>
       <c r="D2009" t="n">
-        <v>-1.878183297643149</v>
+        <v>-2.075584530808433</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.532297518563281</v>
+        <v>2.453337025297168</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.171440583051977</v>
+        <v>0.95825915458405</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.986791611765475</v>
+        <v>3.858882754684719</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
         <v>3.282361272144441</v>
       </c>
       <c r="D2010" t="n">
-        <v>-1.876342278584898</v>
+        <v>-2.073743511750182</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.531467936396735</v>
+        <v>2.452507443130621</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.172708809723446</v>
+        <v>0.9595273812555184</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.985986557978508</v>
+        <v>3.858077700897752</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647103</v>
+        <v>3.754911907647105</v>
       </c>
       <c r="C2011" t="n">
         <v>3.295434679010359</v>
       </c>
       <c r="D2011" t="n">
-        <v>-1.883250984084578</v>
+        <v>-2.080652217249862</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.541777861062781</v>
+        <v>2.462817367796667</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.172708809723446</v>
+        <v>0.9595273812555184</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.999059964844427</v>
+        <v>3.871151107763671</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74989685176353</v>
+        <v>3.749896851763532</v>
       </c>
       <c r="C2012" t="n">
         <v>3.295434679010359</v>
       </c>
       <c r="D2012" t="n">
-        <v>-1.884812626899438</v>
+        <v>-2.082213860064722</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.541153203936837</v>
+        <v>2.462192710670723</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.172708809723446</v>
+        <v>0.9595273812555184</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.999059964844427</v>
+        <v>3.871151107763671</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392113</v>
+        <v>3.715834055392115</v>
       </c>
       <c r="C2013" t="n">
         <v>3.293958720137361</v>
       </c>
       <c r="D2013" t="n">
-        <v>-1.912713414008911</v>
+        <v>-2.110114647174195</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.52851693022005</v>
+        <v>2.449556436953936</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.138111885580511</v>
+        <v>0.9249304571125836</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.976825851485668</v>
+        <v>3.848916994404912</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172524</v>
+        <v>3.684909939172526</v>
       </c>
       <c r="C2014" t="n">
         <v>3.29072316411456</v>
       </c>
       <c r="D2014" t="n">
-        <v>-1.915746411521585</v>
+        <v>-2.113147644686869</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.524068175192179</v>
+        <v>2.445107681926065</v>
       </c>
       <c r="F2014" t="n">
-        <v>1.135078888067837</v>
+        <v>0.9218974595999097</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.971770496955262</v>
+        <v>3.843861639874506</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971077</v>
+        <v>3.619362241971079</v>
       </c>
       <c r="C2015" t="n">
         <v>3.357429123705064</v>
       </c>
       <c r="D2015" t="n">
-        <v>-1.935807732798092</v>
+        <v>-2.133208965963376</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.58274960627208</v>
+        <v>2.503789113005966</v>
       </c>
       <c r="F2015" t="n">
-        <v>1.11501756679133</v>
+        <v>0.9018361383234026</v>
       </c>
       <c r="G2015" t="n">
-        <v>4.026439663779862</v>
+        <v>3.898530806699106</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199804</v>
+        <v>3.640764248199805</v>
       </c>
       <c r="C2016" t="n">
         <v>3.497740842706911</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.192528550792916</v>
+        <v>-2.3899297839582</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.620372998075998</v>
+        <v>2.541412504809884</v>
       </c>
       <c r="F2016" t="n">
-        <v>1.006602992647515</v>
+        <v>0.7934215641795878</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.10170263829542</v>
+        <v>3.973793781214663</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622235</v>
+        <v>3.668303164622237</v>
       </c>
       <c r="C2017" t="n">
         <v>3.566721111852551</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.346514968569056</v>
+        <v>-2.54391620173434</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.627758700111181</v>
+        <v>2.548798206845067</v>
       </c>
       <c r="F2017" t="n">
-        <v>1.006602992647515</v>
+        <v>0.7934215641795878</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.17068290744106</v>
+        <v>4.042774050360303</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808527</v>
+        <v>3.619937176808529</v>
       </c>
       <c r="C2018" t="n">
         <v>3.552772313972671</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.29599306474139</v>
+        <v>-2.493394297906674</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.634018663762368</v>
+        <v>2.555058170496254</v>
       </c>
       <c r="F2018" t="n">
-        <v>1.006602992647515</v>
+        <v>0.7934215641795878</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.156734109561181</v>
+        <v>4.028825252480424</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994892</v>
+        <v>3.656346893994894</v>
       </c>
       <c r="C2019" t="n">
         <v>3.564642803028085</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.548468218749115</v>
+        <v>-2.745869451914399</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.544899091214693</v>
+        <v>2.465938597948579</v>
       </c>
       <c r="F2019" t="n">
-        <v>1.006602992647515</v>
+        <v>0.7934215641795878</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.168604598616595</v>
+        <v>4.040695741535838</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358296</v>
+        <v>3.674042696358297</v>
       </c>
       <c r="C2020" t="n">
         <v>3.565853337547029</v>
       </c>
       <c r="D2020" t="n">
-        <v>-2.817941020670823</v>
+        <v>-3.015342253836107</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.438320504964953</v>
+        <v>2.359360011698839</v>
       </c>
       <c r="F2020" t="n">
-        <v>1.006602992647515</v>
+        <v>0.7934215641795878</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.169815133135539</v>
+        <v>4.041906276054782</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637084</v>
+        <v>3.663523617637086</v>
       </c>
       <c r="C2021" t="n">
         <v>3.569975079774351</v>
       </c>
       <c r="D2021" t="n">
-        <v>-2.975485092400264</v>
+        <v>-3.172886325565548</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.379424618500498</v>
+        <v>2.300464125234384</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.9397011875072407</v>
+        <v>0.7265197590393133</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.133795792278695</v>
+        <v>4.005886935197939</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.65216331330134</v>
+        <v>3.652163313301343</v>
       </c>
       <c r="C2022" t="n">
         <v>3.56505293251054</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.10433564310231</v>
+        <v>-3.301736876267595</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.322962250955869</v>
+        <v>2.244001757689755</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.8987077786565192</v>
+        <v>0.6855263501885918</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.104277599704452</v>
+        <v>3.976368742623695</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.529228204705057</v>
+        <v>3.529228204705058</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.810319733515959</v>
+        <v>3.566743994151006</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.094579842105174</v>
+        <v>-3.292486163122804</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.572131372360142</v>
+        <v>2.249393104588137</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.8987077786565192</v>
+        <v>0.6855263501885918</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.34954440070987</v>
+        <v>3.978059804264161</v>
       </c>
     </row>
   </sheetData>
